--- a/financial_models/opportunities/2020.HK_Valuation.xlsx
+++ b/financial_models/opportunities/2020.HK_Valuation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kamanl/PycharmProjects/Invest_Proc/financial_models/opportunities/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC89B664-58C4-B246-B167-1B57AEFA496A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8F95AA5-9A64-4785-BB92-459596D54957}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1470" yWindow="1470" windowWidth="12690" windowHeight="7643" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -39,17 +39,6 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
     <ext uri="GoogleSheetsCustomDataVersion1">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId10" roundtripDataSignature="AMtx7mi73Cg0ax9bLfpeUuF69nNRn7idDQ=="/>
@@ -3286,27 +3275,27 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="19">
-    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00;[Red]\-&quot;$&quot;#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="166" formatCode="#,##0&quot;mm&quot;"/>
-    <numFmt numFmtId="167" formatCode="#,##0.00&quot;x&quot;"/>
-    <numFmt numFmtId="168" formatCode="0.00\x"/>
-    <numFmt numFmtId="169" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="170" formatCode="#,##0.0000"/>
-    <numFmt numFmtId="171" formatCode="#,##0_ "/>
-    <numFmt numFmtId="172" formatCode="#,##0.0000_);\(#,##0.0000\)"/>
-    <numFmt numFmtId="173" formatCode="#,##0.0000_ "/>
-    <numFmt numFmtId="174" formatCode="&quot;in &quot;#,##0&quot;s&quot;"/>
-    <numFmt numFmtId="175" formatCode="#,##0.00_ "/>
-    <numFmt numFmtId="176" formatCode="0&quot; yrs&quot;"/>
-    <numFmt numFmtId="177" formatCode="0.000_ "/>
-    <numFmt numFmtId="178" formatCode="&quot;every&quot;\ 0\ &quot;Months&quot;"/>
-    <numFmt numFmtId="179" formatCode="0.0\x"/>
-    <numFmt numFmtId="180" formatCode="0\x"/>
-    <numFmt numFmtId="181" formatCode="0.000000000000000%"/>
-    <numFmt numFmtId="182" formatCode="#,##0_);\(#,##0\);0;@"/>
+    <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00;[Red]\-&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="165" formatCode="#,##0&quot;mm&quot;"/>
+    <numFmt numFmtId="166" formatCode="#,##0.00&quot;x&quot;"/>
+    <numFmt numFmtId="167" formatCode="0.00\x"/>
+    <numFmt numFmtId="168" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="169" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="170" formatCode="#,##0_ "/>
+    <numFmt numFmtId="171" formatCode="#,##0.0000_);\(#,##0.0000\)"/>
+    <numFmt numFmtId="172" formatCode="#,##0.0000_ "/>
+    <numFmt numFmtId="173" formatCode="&quot;in &quot;#,##0&quot;s&quot;"/>
+    <numFmt numFmtId="174" formatCode="#,##0.00_ "/>
+    <numFmt numFmtId="175" formatCode="0&quot; yrs&quot;"/>
+    <numFmt numFmtId="176" formatCode="0.000_ "/>
+    <numFmt numFmtId="177" formatCode="&quot;every&quot;\ 0\ &quot;Months&quot;"/>
+    <numFmt numFmtId="178" formatCode="0.0\x"/>
+    <numFmt numFmtId="179" formatCode="0\x"/>
+    <numFmt numFmtId="180" formatCode="0.000000000000000%"/>
+    <numFmt numFmtId="181" formatCode="#,##0_);\(#,##0\);0;@"/>
   </numFmts>
-  <fonts count="72" x14ac:knownFonts="1">
+  <fonts count="72">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -4058,7 +4047,7 @@
     <xf numFmtId="3" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -4100,17 +4089,17 @@
     <xf numFmtId="3" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="169" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="169" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="170" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4119,7 +4108,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4193,10 +4182,10 @@
     </xf>
     <xf numFmtId="10" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="172" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="171" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -4207,7 +4196,7 @@
     <xf numFmtId="10" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="169" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -4245,7 +4234,7 @@
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4255,7 +4244,7 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="169" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4266,19 +4255,19 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="169" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="174" fontId="17" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="173" fontId="17" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="174" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="173" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="174" fontId="23" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="173" fontId="23" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -4286,8 +4275,8 @@
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="39" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="173" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="173" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="172" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="172" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="37" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="38" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -4310,29 +4299,29 @@
     </xf>
     <xf numFmtId="9" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="171" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="170" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="39" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="175" fontId="24" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="24" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="10" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="176" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="176" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="175" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="175" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="175" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="174" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="176" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="175" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -4349,15 +4338,15 @@
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="175" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="174" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="176" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="175" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -4368,11 +4357,11 @@
     <xf numFmtId="0" fontId="27" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="3" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="175" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4433,14 +4422,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="175" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="174" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="177" fontId="42" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="176" fontId="42" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="40" fontId="41" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -4453,7 +4442,7 @@
     </xf>
     <xf numFmtId="0" fontId="44" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="39" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="175" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="8" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -4490,7 +4479,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="176" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -4507,7 +4496,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="179" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="178" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
@@ -4553,7 +4542,7 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="49" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="180" fontId="46" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="179" fontId="46" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -4568,13 +4557,13 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="175" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="175" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="181" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="180" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -4590,53 +4579,53 @@
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="182" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="181" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="182" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="182" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="182" fontId="3" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="182" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="3" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="181" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="182" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="182" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="182" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="182" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="182" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="181" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="182" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="182" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="182" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="182" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="182" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="3" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -4653,7 +4642,7 @@
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -4666,21 +4655,21 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="182" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="176" fontId="25" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="25" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="25" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="182" fontId="32" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="32" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
@@ -4690,14 +4679,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="182" fontId="24" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="24" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="175" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="174" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="40" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -4706,8 +4695,8 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="10" fontId="29" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="176" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="175" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="175" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="174" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="29" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="51" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4719,7 +4708,7 @@
     </xf>
     <xf numFmtId="39" fontId="24" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="39" fontId="42" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="175" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="174" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -4727,7 +4716,7 @@
     <xf numFmtId="9" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="179" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4766,7 +4755,7 @@
     <xf numFmtId="4" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="166" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4780,39 +4769,39 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="64" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="176" fontId="64" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="64" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="175" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="175" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="10" fontId="56" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="66" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="174" fontId="67" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="173" fontId="67" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="182" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="181" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="37" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="182" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="10" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="181" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="180" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -4823,7 +4812,7 @@
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="10" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="167" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -4834,10 +4823,10 @@
     <xf numFmtId="9" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="179" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="182" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="181" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="10" fontId="60" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4846,7 +4835,7 @@
     <xf numFmtId="10" fontId="56" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="56" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="56" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="39" fontId="54" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4859,7 +4848,7 @@
     <xf numFmtId="10" fontId="56" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="56" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="56" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="10" fontId="54" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4868,8 +4857,8 @@
     <xf numFmtId="40" fontId="65" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="176" fontId="56" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="177" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="175" fontId="56" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="176" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -4877,10 +4866,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="39" fontId="54" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="175" fontId="65" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="174" fontId="65" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="54" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="68" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="10" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4889,10 +4878,10 @@
     <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="178" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="69" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4909,16 +4898,16 @@
     <xf numFmtId="4" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="178" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4939,7 +4928,7 @@
     <xf numFmtId="0" fontId="59" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="56" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="56" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4957,7 +4946,7 @@
     <xf numFmtId="40" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="176" fontId="70" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="70" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="10" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -4967,10 +4956,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="174" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="173" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="182" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -4985,7 +4974,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="168" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="10" fontId="71" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4999,34 +4988,34 @@
     <xf numFmtId="10" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="182" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5036,6 +5025,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5045,21 +5043,12 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
     <cellStyle name="常规 2 2" xfId="1" xr:uid="{A35F4541-DCCE-4554-A311-39480A36979A}"/>
   </cellStyles>
   <dxfs count="7">
@@ -5341,7 +5330,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:I167"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="32.6640625" style="1" customWidth="1"/>
@@ -5350,7 +5339,7 @@
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:9" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" ht="13.9">
       <c r="A2" s="200" t="s">
         <v>225</v>
       </c>
@@ -5363,7 +5352,7 @@
       <c r="H2" s="21"/>
       <c r="I2" s="21"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:9">
       <c r="E3" s="428" t="s">
         <v>538</v>
       </c>
@@ -5371,7 +5360,7 @@
         <v>46038</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="14" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:9" ht="12.4">
       <c r="B4" s="421" t="s">
         <v>533</v>
       </c>
@@ -5385,7 +5374,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:9">
       <c r="B5" s="1" t="s">
         <v>349</v>
       </c>
@@ -5399,7 +5388,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:9">
       <c r="B6" s="2" t="s">
         <v>53</v>
       </c>
@@ -5409,7 +5398,7 @@
       <c r="D6" s="45"/>
       <c r="E6" s="45"/>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:9">
       <c r="B7" s="1" t="s">
         <v>351</v>
       </c>
@@ -5419,16 +5408,16 @@
       <c r="D7" s="45"/>
       <c r="E7" s="45"/>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:9">
       <c r="B8" s="4" t="s">
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>78.25</v>
+        <v>78.45</v>
       </c>
       <c r="E8" s="32"/>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:9">
       <c r="B9" s="4" t="s">
         <v>346</v>
       </c>
@@ -5436,43 +5425,43 @@
         <v>2770499587</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:9">
       <c r="B10" s="4" t="s">
         <v>352</v>
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>216791.59268274999</v>
+        <v>217345.69260014998</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>528</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>6.025755964683787E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.15">
+        <v>6.1359469686947478E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
       <c r="D11" s="5"/>
       <c r="E11" s="5"/>
     </row>
-    <row r="12" spans="1:9" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B12" s="462" t="s">
+    <row r="12" spans="1:9" ht="24.5" customHeight="1">
+      <c r="B12" s="460" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="462"/>
-      <c r="D12" s="462"/>
-      <c r="E12" s="462"/>
-      <c r="F12" s="462"/>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="C12" s="460"/>
+      <c r="D12" s="460"/>
+      <c r="E12" s="460"/>
+      <c r="F12" s="460"/>
+    </row>
+    <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
         <f>Scenarios!B39&amp;" Valuation Conclusion"</f>
         <v>2-stage DCF Valuation Conclusion</v>
       </c>
       <c r="C14" s="43"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:9">
       <c r="B15" s="1" t="s">
         <v>319</v>
       </c>
@@ -5487,7 +5476,7 @@
         <v>CNY/HKD</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:9">
       <c r="B16" s="1" t="s">
         <v>320</v>
       </c>
@@ -5498,10 +5487,10 @@
         <v>354</v>
       </c>
       <c r="E16" s="416">
-        <v>1.1200000000000001</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.15">
+        <v>1.1268191807746888</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
       <c r="B17" s="1" t="s">
         <v>532</v>
       </c>
@@ -5515,14 +5504,14 @@
         <v>556</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:6">
       <c r="B18" s="1" t="str">
         <f>"Expected Equity Value ("&amp;C7&amp;") :"</f>
         <v>Expected Equity Value (HKD) :</v>
       </c>
       <c r="C18" s="252">
         <f>C125</f>
-        <v>85.749761133441666</v>
+        <v>86.271853207151764</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5531,7 +5520,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:6">
       <c r="B19" s="2" t="s">
         <v>275</v>
       </c>
@@ -5547,11 +5536,11 @@
         <v>46081</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:6">
       <c r="D20" s="5"/>
       <c r="E20" s="5"/>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:6">
       <c r="B21" s="42" t="s">
         <v>404</v>
       </c>
@@ -5566,43 +5555,43 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:6">
       <c r="B22" s="1" t="s">
         <v>312</v>
       </c>
       <c r="C22" s="255">
         <f>E140</f>
-        <v>43.834468675122963</v>
+        <v>44.075064100795821</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>406</v>
       </c>
       <c r="E22" s="79">
-        <v>0.29465259038036601</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.15">
+        <v>0.29465259038036606</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
       <c r="B23" s="1" t="s">
         <v>313</v>
       </c>
       <c r="C23" s="256">
         <f>E141</f>
-        <v>54.49599726266937</v>
+        <v>54.797566691527187</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>407</v>
       </c>
       <c r="E23" s="443">
-        <v>0.20075184365903001</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.15">
+        <v>0.20075184365903009</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
       <c r="B24" s="1" t="s">
         <v>315</v>
       </c>
       <c r="C24" s="256">
         <f>E144</f>
-        <v>67.155775868146307</v>
+        <v>67.529990788088668</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>408</v>
@@ -5611,13 +5600,13 @@
         <v>0.1174</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:6">
       <c r="B25" s="1" t="s">
         <v>314</v>
       </c>
       <c r="C25" s="256">
         <f>E145</f>
-        <v>75.674201669797</v>
+        <v>76.097410964531491</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>409</v>
@@ -5626,11 +5615,11 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:6">
       <c r="D26" s="5"/>
       <c r="E26" s="5"/>
     </row>
-    <row r="27" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" ht="13.9">
       <c r="A27" s="200" t="s">
         <v>280</v>
       </c>
@@ -5640,25 +5629,25 @@
       <c r="E27" s="34"/>
       <c r="F27" s="34"/>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B29" s="462" t="s">
+    <row r="29" spans="1:6">
+      <c r="B29" s="460" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="462"/>
-      <c r="D29" s="462"/>
-      <c r="E29" s="462"/>
-      <c r="F29" s="462"/>
-    </row>
-    <row r="30" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B30" s="466" t="s">
+      <c r="C29" s="460"/>
+      <c r="D29" s="460"/>
+      <c r="E29" s="460"/>
+      <c r="F29" s="460"/>
+    </row>
+    <row r="30" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B30" s="462" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="466"/>
-      <c r="D30" s="466"/>
-      <c r="E30" s="466"/>
-      <c r="F30" s="466"/>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C30" s="462"/>
+      <c r="D30" s="462"/>
+      <c r="E30" s="462"/>
+      <c r="F30" s="462"/>
+    </row>
+    <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
         <v>195</v>
       </c>
@@ -5667,16 +5656,16 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="33" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B33" s="463" t="s">
+    <row r="33" spans="2:6" ht="24.5" customHeight="1">
+      <c r="B33" s="461" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="463"/>
-      <c r="D33" s="463"/>
-      <c r="E33" s="463"/>
-      <c r="F33" s="463"/>
-    </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C33" s="461"/>
+      <c r="D33" s="461"/>
+      <c r="E33" s="461"/>
+      <c r="F33" s="461"/>
+    </row>
+    <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
         <v>197</v>
       </c>
@@ -5689,20 +5678,20 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="35" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:6">
       <c r="B35" s="44"/>
       <c r="C35" s="73"/>
     </row>
-    <row r="36" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B36" s="463" t="s">
+    <row r="36" spans="2:6" ht="24.5" customHeight="1">
+      <c r="B36" s="461" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="463"/>
-      <c r="D36" s="463"/>
-      <c r="E36" s="463"/>
-      <c r="F36" s="463"/>
-    </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C36" s="461"/>
+      <c r="D36" s="461"/>
+      <c r="E36" s="461"/>
+      <c r="F36" s="461"/>
+    </row>
+    <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
         <v>199</v>
       </c>
@@ -5715,7 +5704,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="38" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:6">
       <c r="B38" s="49" t="s">
         <v>200</v>
       </c>
@@ -5728,16 +5717,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="40" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B40" s="463" t="s">
+    <row r="40" spans="2:6">
+      <c r="B40" s="461" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="463"/>
-      <c r="D40" s="463"/>
-      <c r="E40" s="463"/>
-      <c r="F40" s="463"/>
-    </row>
-    <row r="41" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C40" s="461"/>
+      <c r="D40" s="461"/>
+      <c r="E40" s="461"/>
+      <c r="F40" s="461"/>
+    </row>
+    <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
         <v>202</v>
       </c>
@@ -5750,16 +5739,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="43" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B43" s="463" t="s">
+    <row r="43" spans="2:6">
+      <c r="B43" s="461" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="463"/>
-      <c r="D43" s="463"/>
-      <c r="E43" s="463"/>
-      <c r="F43" s="463"/>
-    </row>
-    <row r="44" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C43" s="461"/>
+      <c r="D43" s="461"/>
+      <c r="E43" s="461"/>
+      <c r="F43" s="461"/>
+    </row>
+    <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
         <v>267</v>
       </c>
@@ -5774,7 +5763,7 @@
       <c r="E44" s="244"/>
       <c r="F44" s="244"/>
     </row>
-    <row r="45" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:6">
       <c r="B45" s="44" t="s">
         <v>268</v>
       </c>
@@ -5789,7 +5778,7 @@
       <c r="E45" s="244"/>
       <c r="F45" s="244"/>
     </row>
-    <row r="46" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:6">
       <c r="B46" s="44" t="s">
         <v>203</v>
       </c>
@@ -5802,12 +5791,12 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="48" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:6">
       <c r="B48" s="1" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="49" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="49" spans="2:6">
       <c r="B49" s="44" t="s">
         <v>223</v>
       </c>
@@ -5820,16 +5809,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="51" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B51" s="463" t="s">
+    <row r="51" spans="2:6">
+      <c r="B51" s="461" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="463"/>
-      <c r="D51" s="463"/>
-      <c r="E51" s="463"/>
-      <c r="F51" s="463"/>
-    </row>
-    <row r="52" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C51" s="461"/>
+      <c r="D51" s="461"/>
+      <c r="E51" s="461"/>
+      <c r="F51" s="461"/>
+    </row>
+    <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
         <v>204</v>
       </c>
@@ -5842,8 +5831,8 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="54" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B54" s="463" t="s">
+    <row r="54" spans="2:6">
+      <c r="B54" s="461" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="464"/>
@@ -5851,7 +5840,7 @@
       <c r="E54" s="464"/>
       <c r="F54" s="464"/>
     </row>
-    <row r="55" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:6">
       <c r="B55" s="44" t="s">
         <v>207</v>
       </c>
@@ -5864,25 +5853,25 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="57" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B57" s="462" t="s">
+    <row r="57" spans="2:6" ht="24.5" customHeight="1">
+      <c r="B57" s="460" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="462"/>
-      <c r="D57" s="462"/>
-      <c r="E57" s="462"/>
-      <c r="F57" s="462"/>
-    </row>
-    <row r="58" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B58" s="462" t="s">
+      <c r="C57" s="460"/>
+      <c r="D57" s="460"/>
+      <c r="E57" s="460"/>
+      <c r="F57" s="460"/>
+    </row>
+    <row r="58" spans="2:6" ht="24.5" customHeight="1">
+      <c r="B58" s="460" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="462"/>
-      <c r="D58" s="462"/>
-      <c r="E58" s="462"/>
-      <c r="F58" s="462"/>
-    </row>
-    <row r="60" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C58" s="460"/>
+      <c r="D58" s="460"/>
+      <c r="E58" s="460"/>
+      <c r="F58" s="460"/>
+    </row>
+    <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
         <v>227</v>
       </c>
@@ -5895,7 +5884,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="61" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="61" spans="2:6">
       <c r="B61" s="44" t="s">
         <v>213</v>
       </c>
@@ -5908,23 +5897,23 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="62" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:6">
       <c r="B62" s="204" t="s">
         <v>302</v>
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>4.3243586177853198E-2</v>
+        <v>4.3395960904822804E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
-    <row r="63" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="63" spans="2:6">
       <c r="B63" s="204" t="s">
         <v>332</v>
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>3.0159744408945685E-2</v>
+        <v>3.0082855321861054E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -5934,7 +5923,7 @@
         <v>0.78113118553795446</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:6">
       <c r="B65" s="192" t="s">
         <v>325</v>
       </c>
@@ -5945,7 +5934,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:6">
       <c r="B66" s="44" t="s">
         <v>326</v>
       </c>
@@ -5958,7 +5947,7 @@
         <v>0.18355873621409211</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:6">
       <c r="B67" s="229" t="str">
         <f>Normalized_FCF!B116</f>
         <v>Pre-tax Profit/Sales</v>
@@ -5972,7 +5961,7 @@
         <v>0.18071047355490921</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:6">
       <c r="B68" s="229" t="str">
         <f>Normalized_FCF!B117</f>
         <v>Sales/Total Assets</v>
@@ -5986,7 +5975,7 @@
         <v>0.59902736076457896</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:6">
       <c r="B69" s="229" t="str">
         <f>Normalized_FCF!B118</f>
         <v>Total Assets/Equity</v>
@@ -6000,7 +5989,7 @@
         <v>1.6956845985056004</v>
       </c>
     </row>
-    <row r="71" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:6" ht="13.9">
       <c r="A71" s="200" t="s">
         <v>477</v>
       </c>
@@ -6010,45 +5999,45 @@
       <c r="E71" s="34"/>
       <c r="F71" s="34"/>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:6">
       <c r="A72" s="191"/>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="462" t="s">
+      <c r="B73" s="460" t="s">
         <v>478</v>
       </c>
-      <c r="C73" s="462"/>
-      <c r="D73" s="462"/>
-      <c r="E73" s="462"/>
-      <c r="F73" s="462"/>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C73" s="460"/>
+      <c r="D73" s="460"/>
+      <c r="E73" s="460"/>
+      <c r="F73" s="460"/>
+    </row>
+    <row r="74" spans="1:6">
       <c r="A74" s="191"/>
       <c r="B74" s="1" t="s">
         <v>465</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:6">
       <c r="A75" s="191"/>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:6">
       <c r="A76" s="191"/>
       <c r="B76" s="192" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="462" t="s">
+      <c r="B77" s="460" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="462"/>
-      <c r="D77" s="462"/>
-      <c r="E77" s="462"/>
-      <c r="F77" s="462"/>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C77" s="460"/>
+      <c r="D77" s="460"/>
+      <c r="E77" s="460"/>
+      <c r="F77" s="460"/>
+    </row>
+    <row r="78" spans="1:6">
       <c r="A78" s="191"/>
       <c r="B78" s="1" t="s">
         <v>215</v>
@@ -6062,21 +6051,21 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:6">
       <c r="A79" s="191"/>
       <c r="B79" s="44" t="s">
         <v>234</v>
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-12.770144477195332</v>
+        <v>-12.847896194792556</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:6">
       <c r="A80" s="191"/>
       <c r="B80" s="229" t="s">
         <v>309</v>
@@ -6086,7 +6075,7 @@
         <v>0.45303827785506334</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:6">
       <c r="A81" s="191"/>
       <c r="B81" s="229" t="s">
         <v>311</v>
@@ -6096,16 +6085,16 @@
         <v>2.1271064799169817</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:6">
       <c r="A82" s="191"/>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:6">
       <c r="A83" s="191"/>
       <c r="B83" s="1" t="s">
         <v>466</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:6">
       <c r="A84" s="191"/>
       <c r="B84" s="1" t="s">
         <v>224</v>
@@ -6119,7 +6108,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:6">
       <c r="A85" s="191"/>
       <c r="B85" s="229" t="s">
         <v>222</v>
@@ -6133,30 +6122,30 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:6">
       <c r="A86" s="191"/>
       <c r="B86" s="44" t="s">
         <v>235</v>
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>18.256367328050825</v>
+        <v>18.367522211175022</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:6">
       <c r="A87" s="191"/>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:6">
       <c r="A88" s="191"/>
       <c r="B88" s="1" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="89" spans="1:6">
       <c r="A89" s="191"/>
       <c r="B89" s="1" t="s">
         <v>217</v>
@@ -6170,38 +6159,38 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:6">
       <c r="A90" s="191"/>
       <c r="B90" s="44" t="s">
         <v>236</v>
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>2.0160003005263039</v>
+        <v>2.028274827750514</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:6">
       <c r="A91" s="191"/>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:6">
       <c r="A92" s="191"/>
       <c r="B92" s="44" t="s">
         <v>469</v>
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>7.502223151381795</v>
+        <v>7.5479008441329798</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="94" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:6" ht="13.9">
       <c r="A94" s="200" t="s">
         <v>470</v>
       </c>
@@ -6211,42 +6200,42 @@
       <c r="E94" s="34"/>
       <c r="F94" s="34"/>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:6">
       <c r="A95" s="191"/>
     </row>
-    <row r="96" spans="1:6" ht="11.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B96" s="462" t="s">
+    <row r="96" spans="1:6" ht="11.75" customHeight="1">
+      <c r="B96" s="460" t="s">
         <v>485</v>
       </c>
-      <c r="C96" s="462"/>
-      <c r="D96" s="462"/>
-      <c r="E96" s="462"/>
-      <c r="F96" s="462"/>
-    </row>
-    <row r="97" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B97" s="466" t="s">
+      <c r="C96" s="460"/>
+      <c r="D96" s="460"/>
+      <c r="E96" s="460"/>
+      <c r="F96" s="460"/>
+    </row>
+    <row r="97" spans="2:6">
+      <c r="B97" s="462" t="s">
         <v>484</v>
       </c>
-      <c r="C97" s="466"/>
-      <c r="D97" s="466"/>
-      <c r="E97" s="466"/>
-      <c r="F97" s="466"/>
-    </row>
-    <row r="98" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B98" s="466" t="s">
+      <c r="C97" s="462"/>
+      <c r="D97" s="462"/>
+      <c r="E97" s="462"/>
+      <c r="F97" s="462"/>
+    </row>
+    <row r="98" spans="2:6">
+      <c r="B98" s="462" t="s">
         <v>483</v>
       </c>
-      <c r="C98" s="466"/>
-      <c r="D98" s="466"/>
-      <c r="E98" s="466"/>
-      <c r="F98" s="466"/>
-    </row>
-    <row r="100" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C98" s="462"/>
+      <c r="D98" s="462"/>
+      <c r="E98" s="462"/>
+      <c r="F98" s="462"/>
+    </row>
+    <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="101" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="101" spans="2:6">
       <c r="B101" s="49" t="s">
         <v>467</v>
       </c>
@@ -6255,7 +6244,7 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="102" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="102" spans="2:6">
       <c r="B102" s="229" t="s">
         <v>318</v>
       </c>
@@ -6264,7 +6253,7 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="103" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="103" spans="2:6">
       <c r="B103" s="229" t="s">
         <v>317</v>
       </c>
@@ -6273,7 +6262,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="104" spans="2:6">
       <c r="B104" s="44" t="s">
         <v>214</v>
       </c>
@@ -6282,76 +6271,76 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="106" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="106" spans="2:6">
       <c r="B106" s="250" t="s">
         <v>281</v>
       </c>
       <c r="C106" s="116"/>
     </row>
-    <row r="107" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B107" s="462" t="s">
+    <row r="107" spans="2:6">
+      <c r="B107" s="460" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="462"/>
-      <c r="D107" s="462"/>
-      <c r="E107" s="462"/>
-      <c r="F107" s="462"/>
-    </row>
-    <row r="108" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B108" s="462" t="s">
+      <c r="C107" s="460"/>
+      <c r="D107" s="460"/>
+      <c r="E107" s="460"/>
+      <c r="F107" s="460"/>
+    </row>
+    <row r="108" spans="2:6">
+      <c r="B108" s="460" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="462"/>
-      <c r="D108" s="462"/>
-      <c r="E108" s="462"/>
-      <c r="F108" s="462"/>
-    </row>
-    <row r="110" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C108" s="460"/>
+      <c r="D108" s="460"/>
+      <c r="E108" s="460"/>
+      <c r="F108" s="460"/>
+    </row>
+    <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
         <v>487</v>
       </c>
     </row>
-    <row r="111" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="111" spans="2:6">
       <c r="B111" s="49" t="s">
         <v>468</v>
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>3.6148050867765735</v>
+        <v>3.6368140236979967</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="112" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="112" spans="2:6">
       <c r="B112" s="44" t="s">
         <v>323</v>
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>73.2448294520552</v>
+        <v>73.690784570666622</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="114" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B114" s="462" t="s">
+    <row r="114" spans="2:6" ht="24.5" customHeight="1">
+      <c r="B114" s="460" t="s">
         <v>491</v>
       </c>
-      <c r="C114" s="462"/>
-      <c r="D114" s="462"/>
-      <c r="E114" s="462"/>
-      <c r="F114" s="462"/>
-    </row>
-    <row r="116" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C114" s="460"/>
+      <c r="D114" s="460"/>
+      <c r="E114" s="460"/>
+      <c r="F114" s="460"/>
+    </row>
+    <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="117" spans="2:6" ht="14" x14ac:dyDescent="0.2">
+    <row r="117" spans="2:6" ht="12.4">
       <c r="B117" s="342" t="s">
         <v>101</v>
       </c>
@@ -6368,7 +6357,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="118" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="118" spans="2:6">
       <c r="B118" s="205" t="str">
         <f>DCF!B90&amp;" ("&amp;DCF!D90&amp;"yrs)"</f>
         <v>Snowball Scenario (15yrs)</v>
@@ -6379,7 +6368,7 @@
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>148.43 HKD</v>
+        <v>149.33 HKD</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6387,10 +6376,10 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>-0.14788322549872357</v>
-      </c>
-    </row>
-    <row r="119" spans="2:6" x14ac:dyDescent="0.15">
+        <v>-0.14799940995386343</v>
+      </c>
+    </row>
+    <row r="119" spans="2:6">
       <c r="B119" s="205" t="str">
         <f>DCF!B91&amp;" ("&amp;DCF!D91&amp;"yrs)"</f>
         <v>Optimistic (15yrs)</v>
@@ -6401,7 +6390,7 @@
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>89.8 HKD</v>
+        <v>90.35 HKD</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
@@ -6409,10 +6398,10 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>1.1409060833640761E-2</v>
-      </c>
-    </row>
-    <row r="120" spans="2:6" x14ac:dyDescent="0.15">
+        <v>1.1247629903638768E-2</v>
+      </c>
+    </row>
+    <row r="120" spans="2:6">
       <c r="B120" s="205" t="str">
         <f>DCF!B92&amp;" ("&amp;DCF!D92&amp;"yrs)"</f>
         <v>Base (15yrs)</v>
@@ -6423,7 +6412,7 @@
       </c>
       <c r="D120" s="207" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>74.33 HKD</v>
+        <v>74.78 HKD</v>
       </c>
       <c r="E120" s="199">
         <f>DCF!F92</f>
@@ -6431,10 +6420,10 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>7.9120059699736095E-2</v>
-      </c>
-    </row>
-    <row r="121" spans="2:6" x14ac:dyDescent="0.15">
+        <v>7.8936386559110575E-2</v>
+      </c>
+    </row>
+    <row r="121" spans="2:6">
       <c r="B121" s="205" t="str">
         <f>DCF!B93&amp;" ("&amp;DCF!D93&amp;"yrs)"</f>
         <v>Pessimistic (15yrs)</v>
@@ -6445,7 +6434,7 @@
       </c>
       <c r="D121" s="207" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>67.84 HKD</v>
+        <v>68.25 HKD</v>
       </c>
       <c r="E121" s="199">
         <f>DCF!F93</f>
@@ -6453,10 +6442,10 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>0.113526850226492</v>
-      </c>
-    </row>
-    <row r="122" spans="2:6" x14ac:dyDescent="0.15">
+        <v>0.11333114772291825</v>
+      </c>
+    </row>
+    <row r="122" spans="2:6">
       <c r="B122" s="205" t="str">
         <f>DCF!B94&amp;" ("&amp;DCF!D94&amp;"yrs)"</f>
         <v>Devil's advocate (15yrs)</v>
@@ -6467,7 +6456,7 @@
       </c>
       <c r="D122" s="207" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>56.91 HKD</v>
+        <v>57.25 HKD</v>
       </c>
       <c r="E122" s="199">
         <f>DCF!F94</f>
@@ -6475,32 +6464,32 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>0.18296306290642167</v>
-      </c>
-    </row>
-    <row r="124" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B124" s="463" t="s">
+        <v>0.18274154010547949</v>
+      </c>
+    </row>
+    <row r="124" spans="2:6">
+      <c r="B124" s="461" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="463"/>
-      <c r="D124" s="463"/>
-      <c r="E124" s="463"/>
-      <c r="F124" s="463"/>
-    </row>
-    <row r="125" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C124" s="461"/>
+      <c r="D124" s="461"/>
+      <c r="E124" s="461"/>
+      <c r="F124" s="461"/>
+    </row>
+    <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
         <v>218</v>
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>85.749761133441666</v>
+        <v>86.271853207151764</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="127" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="127" spans="2:6" ht="24.5" customHeight="1">
       <c r="B127" s="465" t="s">
         <v>358</v>
       </c>
@@ -6509,7 +6498,7 @@
       <c r="E127" s="465"/>
       <c r="F127" s="465"/>
     </row>
-    <row r="129" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="200" t="s">
         <v>474</v>
       </c>
@@ -6519,30 +6508,30 @@
       <c r="E129" s="34"/>
       <c r="F129" s="34"/>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B131" s="467" t="s">
+    <row r="131" spans="1:6">
+      <c r="B131" s="463" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="467"/>
-      <c r="D131" s="467"/>
-      <c r="E131" s="467"/>
-      <c r="F131" s="467"/>
-    </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B132" s="462" t="s">
+      <c r="C131" s="463"/>
+      <c r="D131" s="463"/>
+      <c r="E131" s="463"/>
+      <c r="F131" s="463"/>
+    </row>
+    <row r="132" spans="1:6">
+      <c r="B132" s="460" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="462"/>
-      <c r="D132" s="462"/>
-      <c r="E132" s="462"/>
-      <c r="F132" s="462"/>
-    </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C132" s="460"/>
+      <c r="D132" s="460"/>
+      <c r="E132" s="460"/>
+      <c r="F132" s="460"/>
+    </row>
+    <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="135" spans="1:6">
       <c r="B135" s="1" t="s">
         <v>221</v>
       </c>
@@ -6551,7 +6540,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="136" spans="1:6">
       <c r="B136" s="194" t="s">
         <v>220</v>
       </c>
@@ -6564,14 +6553,14 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="138" spans="1:6">
       <c r="B138" s="192" t="s">
         <v>494</v>
       </c>
       <c r="C138" s="214"/>
       <c r="D138" s="215"/>
     </row>
-    <row r="139" spans="1:6" ht="14" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:6" ht="12.4">
       <c r="B139" s="340" t="s">
         <v>462</v>
       </c>
@@ -6590,56 +6579,56 @@
         <v>472</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="140" spans="1:6">
       <c r="B140" s="336" t="s">
         <v>312</v>
       </c>
       <c r="C140" s="333">
         <f>Scenarios!C62</f>
-        <v>4.318449719619883</v>
+        <v>4.3184497196198821</v>
       </c>
       <c r="D140" s="333">
         <f>Scenarios!D62</f>
-        <v>39.516018955503078</v>
+        <v>39.756614381175936</v>
       </c>
       <c r="E140" s="334">
         <f>Scenarios!E62</f>
-        <v>43.834468675122963</v>
+        <v>44.075064100795821</v>
       </c>
       <c r="F140" s="335">
         <f>E22</f>
-        <v>0.29465259038036601</v>
-      </c>
-    </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.15">
+        <v>0.29465259038036606</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6">
       <c r="B141" s="336" t="s">
         <v>313</v>
       </c>
       <c r="C141" s="333">
         <f>Scenarios!C63</f>
-        <v>4.9654493155550261</v>
+        <v>4.9654493155550243</v>
       </c>
       <c r="D141" s="333">
         <f>Scenarios!D63</f>
-        <v>49.530547947114343</v>
+        <v>49.83211737597216</v>
       </c>
       <c r="E141" s="334">
         <f>Scenarios!E63</f>
-        <v>54.49599726266937</v>
+        <v>54.797566691527187</v>
       </c>
       <c r="F141" s="335">
         <f>Scenarios!F63</f>
-        <v>0.20075184365903001</v>
-      </c>
-    </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.15">
+        <v>0.20075184365903009</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6">
       <c r="B142" s="194"/>
       <c r="C142" s="194"/>
       <c r="D142" s="194"/>
       <c r="E142" s="194"/>
       <c r="F142" s="194"/>
     </row>
-    <row r="143" spans="1:6" ht="14" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:6" ht="12.4">
       <c r="B143" s="340" t="s">
         <v>463</v>
       </c>
@@ -6658,7 +6647,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="144" spans="1:6">
       <c r="B144" s="336" t="s">
         <v>315</v>
       </c>
@@ -6668,18 +6657,18 @@
       </c>
       <c r="D144" s="333">
         <f>Scenarios!D66</f>
-        <v>61.462032490931094</v>
+        <v>61.836247410873455</v>
       </c>
       <c r="E144" s="334">
         <f>Scenarios!E66</f>
-        <v>67.155775868146307</v>
+        <v>67.529990788088668</v>
       </c>
       <c r="F144" s="335">
         <f>E24</f>
         <v>0.1174</v>
       </c>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="145" spans="1:6">
       <c r="B145" s="336" t="s">
         <v>314</v>
       </c>
@@ -6689,18 +6678,18 @@
       </c>
       <c r="D145" s="333">
         <f>Scenarios!D67</f>
-        <v>69.508996133668688</v>
+        <v>69.932205428403179</v>
       </c>
       <c r="E145" s="334">
         <f>Scenarios!E67</f>
-        <v>75.674201669797</v>
+        <v>76.097410964531491</v>
       </c>
       <c r="F145" s="335">
         <f>Scenarios!F67</f>
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="147" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:6" ht="13.9">
       <c r="A147" s="200" t="s">
         <v>475</v>
       </c>
@@ -6710,21 +6699,21 @@
       <c r="E147" s="34"/>
       <c r="F147" s="34"/>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B149" s="461" t="s">
+    <row r="149" spans="1:6">
+      <c r="B149" s="467" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="462"/>
-      <c r="D149" s="462"/>
-      <c r="E149" s="462"/>
-      <c r="F149" s="462"/>
-    </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C149" s="460"/>
+      <c r="D149" s="460"/>
+      <c r="E149" s="460"/>
+      <c r="F149" s="460"/>
+    </row>
+    <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="152" spans="1:6">
       <c r="B152" s="464" t="s">
         <v>293</v>
       </c>
@@ -6733,80 +6722,92 @@
       <c r="E152" s="464"/>
       <c r="F152" s="464"/>
     </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="153" spans="1:6">
       <c r="B153" s="196" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="154" spans="1:6">
       <c r="B154" s="196" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="155" spans="1:6">
       <c r="B155" s="196" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="157" spans="1:6">
       <c r="B157" s="1" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="158" spans="1:6" ht="34.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B158" s="463" t="s">
+    <row r="158" spans="1:6" ht="34.25" customHeight="1">
+      <c r="B158" s="461" t="s">
         <v>438</v>
       </c>
-      <c r="C158" s="463"/>
-      <c r="D158" s="463"/>
-      <c r="E158" s="463"/>
-      <c r="F158" s="463"/>
-    </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C158" s="461"/>
+      <c r="D158" s="461"/>
+      <c r="E158" s="461"/>
+      <c r="F158" s="461"/>
+    </row>
+    <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="161" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B161" s="460" t="s">
+    <row r="161" spans="2:6" ht="24.5" customHeight="1">
+      <c r="B161" s="466" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="460"/>
-      <c r="D161" s="460"/>
-      <c r="E161" s="460"/>
-      <c r="F161" s="460"/>
-    </row>
-    <row r="162" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B162" s="460" t="s">
+      <c r="C161" s="466"/>
+      <c r="D161" s="466"/>
+      <c r="E161" s="466"/>
+      <c r="F161" s="466"/>
+    </row>
+    <row r="162" spans="2:6" ht="24.5" customHeight="1">
+      <c r="B162" s="466" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="460"/>
-      <c r="D162" s="460"/>
-      <c r="E162" s="460"/>
-      <c r="F162" s="460"/>
-    </row>
-    <row r="164" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C162" s="466"/>
+      <c r="D162" s="466"/>
+      <c r="E162" s="466"/>
+      <c r="F162" s="466"/>
+    </row>
+    <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="165" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="165" spans="2:6">
       <c r="B165" s="196" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="166" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="166" spans="2:6">
       <c r="B166" s="196" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="167" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="167" spans="2:6">
       <c r="B167" s="196" t="s">
         <v>300</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6823,18 +6824,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -6862,15 +6851,15 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:M80"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="3" style="1" customWidth="1"/>
     <col min="2" max="2" width="27.33203125" style="1" customWidth="1"/>
     <col min="3" max="13" width="20.6640625" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="8.83203125" style="1"/>
+    <col min="14" max="16384" width="8.796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="1" spans="2:13">
       <c r="B1" s="87" t="str">
         <f>Thesis!E17</f>
         <v>CNY</v>
@@ -6919,7 +6908,7 @@
         <v>42094</v>
       </c>
     </row>
-    <row r="2" spans="2:13" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:13" ht="13.9">
       <c r="B2" s="34" t="s">
         <v>93</v>
       </c>
@@ -6935,7 +6924,7 @@
       <c r="L2" s="35"/>
       <c r="M2" s="35"/>
     </row>
-    <row r="3" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:13">
       <c r="B3" s="16" t="s">
         <v>25</v>
       </c>
@@ -6943,7 +6932,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:13">
       <c r="B4" s="31" t="s">
         <v>0</v>
       </c>
@@ -6963,7 +6952,7 @@
       <c r="L4" s="287"/>
       <c r="M4" s="287"/>
     </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:13">
       <c r="B5" s="38" t="s">
         <v>40</v>
       </c>
@@ -6983,7 +6972,7 @@
       <c r="L5" s="287"/>
       <c r="M5" s="287"/>
     </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:13">
       <c r="B6" s="38" t="s">
         <v>51</v>
       </c>
@@ -7005,7 +6994,7 @@
       <c r="L6" s="287"/>
       <c r="M6" s="287"/>
     </row>
-    <row r="7" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:13">
       <c r="B7" s="66" t="s">
         <v>58</v>
       </c>
@@ -7025,7 +7014,7 @@
       <c r="L7" s="288"/>
       <c r="M7" s="288"/>
     </row>
-    <row r="8" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:13">
       <c r="B8" s="38" t="s">
         <v>46</v>
       </c>
@@ -7041,7 +7030,7 @@
       <c r="L8" s="287"/>
       <c r="M8" s="287"/>
     </row>
-    <row r="9" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:13">
       <c r="B9" s="38" t="s">
         <v>134</v>
       </c>
@@ -7057,7 +7046,7 @@
       <c r="L9" s="287"/>
       <c r="M9" s="287"/>
     </row>
-    <row r="10" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:13">
       <c r="B10" s="38" t="s">
         <v>138</v>
       </c>
@@ -7073,7 +7062,7 @@
       <c r="L10" s="287"/>
       <c r="M10" s="287"/>
     </row>
-    <row r="11" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:13">
       <c r="B11" s="38" t="s">
         <v>133</v>
       </c>
@@ -7089,7 +7078,7 @@
       <c r="L11" s="287"/>
       <c r="M11" s="287"/>
     </row>
-    <row r="12" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:13">
       <c r="B12" s="38" t="s">
         <v>37</v>
       </c>
@@ -7109,7 +7098,7 @@
       <c r="L12" s="287"/>
       <c r="M12" s="287"/>
     </row>
-    <row r="13" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:13">
       <c r="B13" s="38" t="s">
         <v>64</v>
       </c>
@@ -7125,7 +7114,7 @@
       <c r="L13" s="287"/>
       <c r="M13" s="287"/>
     </row>
-    <row r="14" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:13">
       <c r="B14" s="38" t="s">
         <v>47</v>
       </c>
@@ -7145,7 +7134,7 @@
       <c r="L14" s="287"/>
       <c r="M14" s="287"/>
     </row>
-    <row r="15" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="15" spans="2:13">
       <c r="B15" s="41" t="s">
         <v>39</v>
       </c>
@@ -7165,7 +7154,7 @@
       <c r="L15" s="289"/>
       <c r="M15" s="289"/>
     </row>
-    <row r="16" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:13">
       <c r="B16" s="27" t="s">
         <v>41</v>
       </c>
@@ -7185,13 +7174,13 @@
       <c r="L16" s="287"/>
       <c r="M16" s="287"/>
     </row>
-    <row r="18" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:13">
       <c r="B18" s="16" t="s">
         <v>48</v>
       </c>
       <c r="C18" s="9"/>
     </row>
-    <row r="19" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:13">
       <c r="B19" s="26" t="s">
         <v>44</v>
       </c>
@@ -7207,7 +7196,7 @@
       <c r="L19" s="287"/>
       <c r="M19" s="287"/>
     </row>
-    <row r="20" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:13">
       <c r="B20" s="26" t="s">
         <v>50</v>
       </c>
@@ -7223,7 +7212,7 @@
       <c r="L20" s="287"/>
       <c r="M20" s="287"/>
     </row>
-    <row r="21" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:13">
       <c r="B21" s="26" t="s">
         <v>49</v>
       </c>
@@ -7239,7 +7228,7 @@
       <c r="L21" s="287"/>
       <c r="M21" s="287"/>
     </row>
-    <row r="22" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:13">
       <c r="B22" s="26" t="s">
         <v>286</v>
       </c>
@@ -7259,7 +7248,7 @@
       <c r="L22" s="287"/>
       <c r="M22" s="287"/>
     </row>
-    <row r="23" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:13">
       <c r="B23" s="26" t="s">
         <v>288</v>
       </c>
@@ -7279,7 +7268,7 @@
       <c r="L23" s="287"/>
       <c r="M23" s="287"/>
     </row>
-    <row r="24" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:13">
       <c r="B24" s="26" t="s">
         <v>287</v>
       </c>
@@ -7299,7 +7288,7 @@
       <c r="L24" s="287"/>
       <c r="M24" s="287"/>
     </row>
-    <row r="25" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:13">
       <c r="B25" s="23" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
         <v>Dividend per share (HKD)</v>
@@ -7322,7 +7311,7 @@
       <c r="L25" s="37"/>
       <c r="M25" s="37"/>
     </row>
-    <row r="27" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:13">
       <c r="B27" s="16" t="s">
         <v>26</v>
       </c>
@@ -7330,7 +7319,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="28" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:13">
       <c r="B28" s="25" t="s">
         <v>22</v>
       </c>
@@ -7351,7 +7340,7 @@
       <c r="L28" s="287"/>
       <c r="M28" s="287"/>
     </row>
-    <row r="29" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:13">
       <c r="B29" s="25" t="s">
         <v>30</v>
       </c>
@@ -7372,7 +7361,7 @@
       <c r="L29" s="287"/>
       <c r="M29" s="287"/>
     </row>
-    <row r="30" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:13">
       <c r="B30" s="28" t="s">
         <v>38</v>
       </c>
@@ -7393,7 +7382,7 @@
       <c r="L30" s="289"/>
       <c r="M30" s="289"/>
     </row>
-    <row r="31" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:13">
       <c r="B31" s="28" t="s">
         <v>28</v>
       </c>
@@ -7414,7 +7403,7 @@
       <c r="L31" s="289"/>
       <c r="M31" s="289"/>
     </row>
-    <row r="32" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:13">
       <c r="B32" s="25" t="s">
         <v>143</v>
       </c>
@@ -7435,7 +7424,7 @@
       <c r="L32" s="287"/>
       <c r="M32" s="287"/>
     </row>
-    <row r="34" spans="2:13" ht="16" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:13" ht="13.9">
       <c r="B34" s="34" t="s">
         <v>78</v>
       </c>
@@ -7451,12 +7440,12 @@
       <c r="L34" s="35"/>
       <c r="M34" s="35"/>
     </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:13">
       <c r="B35" s="16" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="36" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:13">
       <c r="B36" s="31" t="s">
         <v>0</v>
       </c>
@@ -7505,7 +7494,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:13">
       <c r="B37" s="38" t="s">
         <v>40</v>
       </c>
@@ -7554,7 +7543,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:13">
       <c r="B38" s="30" t="s">
         <v>55</v>
       </c>
@@ -7603,7 +7592,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:13">
       <c r="B39" s="38" t="s">
         <v>51</v>
       </c>
@@ -7652,7 +7641,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:13">
       <c r="B40" s="66" t="s">
         <v>58</v>
       </c>
@@ -7701,7 +7690,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:13">
       <c r="B41" s="66" t="s">
         <v>61</v>
       </c>
@@ -7750,7 +7739,7 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:13">
       <c r="B42" s="38" t="s">
         <v>46</v>
       </c>
@@ -7799,7 +7788,7 @@
         <v/>
       </c>
     </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="43" spans="2:13">
       <c r="B43" s="41" t="s">
         <v>127</v>
       </c>
@@ -7848,7 +7837,7 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:13">
       <c r="B44" s="41" t="s">
         <v>139</v>
       </c>
@@ -7897,7 +7886,7 @@
         <v/>
       </c>
     </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:13">
       <c r="B45" s="38" t="s">
         <v>65</v>
       </c>
@@ -7946,7 +7935,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:13">
       <c r="B46" s="38" t="s">
         <v>47</v>
       </c>
@@ -7995,7 +7984,7 @@
         <v/>
       </c>
     </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:13">
       <c r="B47" s="41" t="s">
         <v>39</v>
       </c>
@@ -8044,7 +8033,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:13">
       <c r="B48" s="27" t="s">
         <v>41</v>
       </c>
@@ -8093,12 +8082,12 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="50" spans="2:13">
       <c r="B50" s="16" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="51" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:13">
       <c r="B51" s="38" t="s">
         <v>37</v>
       </c>
@@ -8147,7 +8136,7 @@
         <v/>
       </c>
     </row>
-    <row r="52" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:13">
       <c r="B52" s="38" t="s">
         <v>64</v>
       </c>
@@ -8196,12 +8185,12 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="54" spans="2:13">
       <c r="B54" s="156" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="55" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:13">
       <c r="B55" s="38" t="s">
         <v>134</v>
       </c>
@@ -8250,7 +8239,7 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:13">
       <c r="B56" s="38" t="s">
         <v>138</v>
       </c>
@@ -8299,7 +8288,7 @@
         <v/>
       </c>
     </row>
-    <row r="57" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="57" spans="2:13">
       <c r="B57" s="38" t="s">
         <v>133</v>
       </c>
@@ -8348,7 +8337,7 @@
         <v/>
       </c>
     </row>
-    <row r="58" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:13">
       <c r="B58" s="38" t="s">
         <v>135</v>
       </c>
@@ -8397,13 +8386,13 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="60" spans="2:13">
       <c r="B60" s="16" t="s">
         <v>48</v>
       </c>
       <c r="C60" s="9"/>
     </row>
-    <row r="61" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="61" spans="2:13">
       <c r="B61" s="26" t="s">
         <v>44</v>
       </c>
@@ -8452,7 +8441,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:13">
       <c r="B62" s="26" t="s">
         <v>50</v>
       </c>
@@ -8501,7 +8490,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="63" spans="2:13">
       <c r="B63" s="26" t="s">
         <v>49</v>
       </c>
@@ -8550,7 +8539,7 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="64" spans="2:13">
       <c r="B64" s="26" t="s">
         <v>305</v>
       </c>
@@ -8599,7 +8588,7 @@
         <v/>
       </c>
     </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="65" spans="2:13">
       <c r="B65" s="23" t="s">
         <v>34</v>
       </c>
@@ -8648,12 +8637,12 @@
         <v/>
       </c>
     </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="67" spans="2:13">
       <c r="B67" s="88" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="68" spans="2:13">
       <c r="B68" s="1" t="str">
         <f>B36</f>
         <v>Sales</v>
@@ -8703,7 +8692,7 @@
         <v/>
       </c>
     </row>
-    <row r="69" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="69" spans="2:13">
       <c r="B69" s="30" t="s">
         <v>55</v>
       </c>
@@ -8752,7 +8741,7 @@
         <v/>
       </c>
     </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="70" spans="2:13">
       <c r="B70" s="77" t="str">
         <f>B43</f>
         <v>Operating EBIT</v>
@@ -8802,7 +8791,7 @@
         <v/>
       </c>
     </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="71" spans="2:13">
       <c r="B71" s="41" t="s">
         <v>139</v>
       </c>
@@ -8851,7 +8840,7 @@
         <v/>
       </c>
     </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="72" spans="2:13">
       <c r="B72" s="77" t="str">
         <f>B47</f>
         <v>Reported Net Income</v>
@@ -8901,7 +8890,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="2:13" ht="16" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:13" ht="13.9">
       <c r="B74" s="34" t="s">
         <v>79</v>
       </c>
@@ -8917,13 +8906,13 @@
       <c r="L74" s="35"/>
       <c r="M74" s="35"/>
     </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="75" spans="2:13">
       <c r="B75" s="16" t="s">
         <v>26</v>
       </c>
       <c r="C75" s="9"/>
     </row>
-    <row r="76" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="76" spans="2:13">
       <c r="B76" s="25" t="s">
         <v>1</v>
       </c>
@@ -8972,7 +8961,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="77" spans="2:13">
       <c r="B77" s="90" t="s">
         <v>82</v>
       </c>
@@ -9006,7 +8995,7 @@
       <c r="L77" s="291"/>
       <c r="M77" s="291"/>
     </row>
-    <row r="78" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="78" spans="2:13">
       <c r="B78" s="90" t="s">
         <v>83</v>
       </c>
@@ -9040,7 +9029,7 @@
       <c r="L78" s="291"/>
       <c r="M78" s="291"/>
     </row>
-    <row r="79" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="79" spans="2:13">
       <c r="B79" s="25" t="s">
         <v>38</v>
       </c>
@@ -9089,7 +9078,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="80" spans="2:13">
       <c r="B80" s="25" t="s">
         <v>28</v>
       </c>
@@ -9170,7 +9159,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:H89"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="2.33203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="34" style="1" bestFit="1" customWidth="1"/>
@@ -9181,7 +9170,7 @@
     <col min="9" max="16384" width="12.33203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="2:8" ht="15" customHeight="1">
       <c r="B1" s="17" t="s">
         <v>35</v>
       </c>
@@ -9197,7 +9186,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="2" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="2:8" ht="15" customHeight="1">
       <c r="B2" s="76" t="s">
         <v>131</v>
       </c>
@@ -9208,7 +9197,7 @@
       <c r="G2" s="35"/>
       <c r="H2" s="35"/>
     </row>
-    <row r="3" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:8" ht="15" customHeight="1">
       <c r="B3" s="16" t="s">
         <v>154</v>
       </c>
@@ -9228,7 +9217,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:8" ht="15" customHeight="1">
       <c r="B4" s="4" t="s">
         <v>22</v>
       </c>
@@ -9251,7 +9240,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="5" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:8" ht="15" customHeight="1">
       <c r="B5" s="1" t="s">
         <v>31</v>
       </c>
@@ -9272,7 +9261,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="6" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:8" ht="15" customHeight="1">
       <c r="B6" s="4" t="s">
         <v>8</v>
       </c>
@@ -9293,7 +9282,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="7" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:8" ht="15" customHeight="1">
       <c r="B7" s="1" t="s">
         <v>66</v>
       </c>
@@ -9314,7 +9303,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="8" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:8" ht="15" customHeight="1">
       <c r="B8" s="1" t="s">
         <v>144</v>
       </c>
@@ -9335,7 +9324,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="9" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:8" ht="15" customHeight="1">
       <c r="B9" s="4" t="s">
         <v>23</v>
       </c>
@@ -9356,7 +9345,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="10" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:8" ht="15" customHeight="1">
       <c r="B10" s="4" t="s">
         <v>9</v>
       </c>
@@ -9376,7 +9365,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="11" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:8" ht="15" customHeight="1">
       <c r="B11" s="4" t="s">
         <v>10</v>
       </c>
@@ -9388,7 +9377,7 @@
       </c>
       <c r="H11" s="232"/>
     </row>
-    <row r="12" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:8" ht="15" customHeight="1">
       <c r="B12" s="77" t="s">
         <v>69</v>
       </c>
@@ -9412,12 +9401,12 @@
         <v>28042.2</v>
       </c>
     </row>
-    <row r="13" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:8" ht="15" customHeight="1">
       <c r="F13" s="77"/>
       <c r="G13" s="78"/>
       <c r="H13" s="19"/>
     </row>
-    <row r="14" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:8" ht="15" customHeight="1">
       <c r="B14" s="16" t="s">
         <v>153</v>
       </c>
@@ -9437,7 +9426,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="15" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="2:8" ht="15" customHeight="1">
       <c r="B15" s="4" t="s">
         <v>329</v>
       </c>
@@ -9458,7 +9447,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="16" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:8" ht="15" customHeight="1">
       <c r="B16" s="1" t="s">
         <v>32</v>
       </c>
@@ -9478,7 +9467,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="17" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:8" ht="15" customHeight="1">
       <c r="B17" s="1" t="s">
         <v>66</v>
       </c>
@@ -9499,7 +9488,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="18" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:8" ht="15" customHeight="1">
       <c r="B18" s="4" t="s">
         <v>144</v>
       </c>
@@ -9519,7 +9508,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="19" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:8" ht="15" customHeight="1">
       <c r="B19" s="4" t="s">
         <v>24</v>
       </c>
@@ -9540,7 +9529,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="20" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:8" ht="15" customHeight="1">
       <c r="B20" s="4" t="s">
         <v>16</v>
       </c>
@@ -9560,7 +9549,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="21" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:8" ht="15" customHeight="1">
       <c r="B21" s="4" t="s">
         <v>17</v>
       </c>
@@ -9580,7 +9569,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="22" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:8" ht="15" customHeight="1">
       <c r="B22" s="4" t="s">
         <v>18</v>
       </c>
@@ -9592,7 +9581,7 @@
       </c>
       <c r="H22" s="232"/>
     </row>
-    <row r="23" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:8" ht="15" customHeight="1">
       <c r="B23" s="4" t="s">
         <v>19</v>
       </c>
@@ -9605,7 +9594,7 @@
       </c>
       <c r="H23" s="232"/>
     </row>
-    <row r="24" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:8" ht="15" customHeight="1">
       <c r="B24" s="77" t="s">
         <v>70</v>
       </c>
@@ -9629,7 +9618,7 @@
         <v>24326.5</v>
       </c>
     </row>
-    <row r="26" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:8" ht="15" customHeight="1">
       <c r="B26" s="16" t="s">
         <v>169</v>
       </c>
@@ -9646,7 +9635,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="27" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:8" ht="15" customHeight="1">
       <c r="B27" s="4" t="s">
         <v>3</v>
       </c>
@@ -9665,7 +9654,7 @@
         <v>14899.799999999996</v>
       </c>
     </row>
-    <row r="28" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:8" ht="15" customHeight="1">
       <c r="B28" s="4" t="s">
         <v>4</v>
       </c>
@@ -9680,7 +9669,7 @@
       </c>
       <c r="H28" s="170"/>
     </row>
-    <row r="29" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:8" ht="15" customHeight="1">
       <c r="B29" s="4" t="s">
         <v>5</v>
       </c>
@@ -9699,7 +9688,7 @@
         <v>8941.7999999999956</v>
       </c>
     </row>
-    <row r="30" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:8" ht="15" customHeight="1">
       <c r="B30" s="2" t="s">
         <v>6</v>
       </c>
@@ -9715,7 +9704,7 @@
       </c>
       <c r="H30" s="170"/>
     </row>
-    <row r="31" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:8" ht="15" customHeight="1">
       <c r="B31" s="77" t="s">
         <v>172</v>
       </c>
@@ -9732,7 +9721,7 @@
       </c>
       <c r="H31" s="170"/>
     </row>
-    <row r="32" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:8" ht="15" customHeight="1">
       <c r="B32" s="4" t="s">
         <v>7</v>
       </c>
@@ -9752,7 +9741,7 @@
         <v>63407.799999999996</v>
       </c>
     </row>
-    <row r="33" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:8" ht="15" customHeight="1">
       <c r="B33" s="80" t="s">
         <v>2</v>
       </c>
@@ -9763,7 +9752,7 @@
       <c r="G33" s="2"/>
       <c r="H33" s="177"/>
     </row>
-    <row r="34" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:8" ht="15" customHeight="1">
       <c r="B34" s="80"/>
       <c r="C34" s="81"/>
       <c r="F34" s="178" t="s">
@@ -9776,7 +9765,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="35" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:8" ht="15" customHeight="1">
       <c r="B35" s="16" t="s">
         <v>170</v>
       </c>
@@ -9795,7 +9784,7 @@
         <v>11039.1</v>
       </c>
     </row>
-    <row r="36" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:8" ht="15" customHeight="1">
       <c r="B36" s="4" t="s">
         <v>11</v>
       </c>
@@ -9811,7 +9800,7 @@
       </c>
       <c r="H36" s="177"/>
     </row>
-    <row r="37" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:8" ht="15" customHeight="1">
       <c r="B37" s="4" t="s">
         <v>12</v>
       </c>
@@ -9827,7 +9816,7 @@
       </c>
       <c r="H37" s="177"/>
     </row>
-    <row r="38" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:8" ht="15" customHeight="1">
       <c r="B38" s="4" t="s">
         <v>13</v>
       </c>
@@ -9843,7 +9832,7 @@
       </c>
       <c r="H38" s="177"/>
     </row>
-    <row r="39" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:8" ht="15" customHeight="1">
       <c r="B39" s="2" t="s">
         <v>14</v>
       </c>
@@ -9862,7 +9851,7 @@
         <v>1725.5</v>
       </c>
     </row>
-    <row r="40" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:8" ht="15" customHeight="1">
       <c r="B40" s="77" t="s">
         <v>173</v>
       </c>
@@ -9882,7 +9871,7 @@
         <v>52368.7</v>
       </c>
     </row>
-    <row r="41" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:8" ht="15" customHeight="1">
       <c r="B41" s="4" t="s">
         <v>15</v>
       </c>
@@ -9902,7 +9891,7 @@
         <v>47381.799999999996</v>
       </c>
     </row>
-    <row r="42" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:8" ht="15" customHeight="1">
       <c r="B42" s="80" t="s">
         <v>20</v>
       </c>
@@ -9921,7 +9910,7 @@
         <v>4986.8999999999996</v>
       </c>
     </row>
-    <row r="44" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:8" ht="15" customHeight="1">
       <c r="B44" s="76" t="s">
         <v>92</v>
       </c>
@@ -9932,7 +9921,7 @@
       <c r="G44" s="35"/>
       <c r="H44" s="35"/>
     </row>
-    <row r="45" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:8" ht="15" customHeight="1">
       <c r="B45" s="16" t="s">
         <v>228</v>
       </c>
@@ -9946,7 +9935,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="46" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:8" ht="15" customHeight="1">
       <c r="B46" s="1" t="s">
         <v>230</v>
       </c>
@@ -9960,25 +9949,25 @@
       </c>
       <c r="F46" s="223"/>
     </row>
-    <row r="47" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:8" ht="15" customHeight="1">
       <c r="B47" s="1" t="str">
         <f>"Equity per share ("&amp;Market_currency&amp;")"</f>
         <v>Equity per share (HKD)</v>
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>25.779206152973163</v>
+        <v>25.936164248495565</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>3.6148050867765735</v>
+        <v>3.6368140236979967</v>
       </c>
       <c r="F47" s="223"/>
     </row>
-    <row r="48" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:8" ht="15" customHeight="1">
       <c r="F48" s="223"/>
     </row>
-    <row r="49" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="2:8" ht="15" customHeight="1">
       <c r="B49" s="143" t="s">
         <v>120</v>
       </c>
@@ -9991,7 +9980,7 @@
       <c r="E49" s="2"/>
       <c r="F49" s="223"/>
     </row>
-    <row r="50" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="50" spans="2:8" ht="15" customHeight="1">
       <c r="B50" s="8" t="s">
         <v>90</v>
       </c>
@@ -10005,7 +9994,7 @@
       </c>
       <c r="F50" s="223"/>
     </row>
-    <row r="51" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:8" ht="15" customHeight="1">
       <c r="B51" s="1" t="s">
         <v>146</v>
       </c>
@@ -10016,10 +10005,10 @@
       </c>
       <c r="F51" s="223"/>
     </row>
-    <row r="52" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:8" ht="15" customHeight="1">
       <c r="F52" s="223"/>
     </row>
-    <row r="53" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="53" spans="2:8" ht="15" customHeight="1">
       <c r="B53" s="143" t="s">
         <v>119</v>
       </c>
@@ -10031,7 +10020,7 @@
       </c>
       <c r="F53" s="223"/>
     </row>
-    <row r="54" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="54" spans="2:8" ht="15" customHeight="1">
       <c r="B54" s="1" t="s">
         <v>116</v>
       </c>
@@ -10045,7 +10034,7 @@
       </c>
       <c r="F54" s="223"/>
     </row>
-    <row r="55" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:8" ht="15" customHeight="1">
       <c r="B55" s="1" t="s">
         <v>118</v>
       </c>
@@ -10059,10 +10048,10 @@
       </c>
       <c r="F55" s="223"/>
     </row>
-    <row r="56" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:8" ht="15" customHeight="1">
       <c r="F56" s="223"/>
     </row>
-    <row r="57" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="57" spans="2:8" ht="15" customHeight="1">
       <c r="B57" s="143" t="s">
         <v>145</v>
       </c>
@@ -10074,7 +10063,7 @@
       </c>
       <c r="F57" s="223"/>
     </row>
-    <row r="58" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:8" ht="15" customHeight="1">
       <c r="B58" s="2" t="s">
         <v>86</v>
       </c>
@@ -10085,7 +10074,7 @@
       </c>
       <c r="F58" s="5"/>
     </row>
-    <row r="59" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="59" spans="2:8" ht="15" customHeight="1">
       <c r="B59" s="1" t="s">
         <v>89</v>
       </c>
@@ -10096,10 +10085,10 @@
       </c>
       <c r="F59" s="223"/>
     </row>
-    <row r="60" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="60" spans="2:8" ht="15" customHeight="1">
       <c r="F60" s="223"/>
     </row>
-    <row r="61" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="61" spans="2:8" ht="15" customHeight="1">
       <c r="B61" s="143" t="s">
         <v>231</v>
       </c>
@@ -10111,7 +10100,7 @@
       </c>
       <c r="F61" s="223"/>
     </row>
-    <row r="62" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:8" ht="15" customHeight="1">
       <c r="B62" s="1" t="s">
         <v>210</v>
       </c>
@@ -10127,7 +10116,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="64" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="2:8" ht="15" customHeight="1">
       <c r="B64" s="76" t="s">
         <v>162</v>
       </c>
@@ -10138,7 +10127,7 @@
       <c r="G64" s="35"/>
       <c r="H64" s="35"/>
     </row>
-    <row r="65" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="65" spans="2:6" ht="15" customHeight="1">
       <c r="B65" s="16" t="s">
         <v>158</v>
       </c>
@@ -10152,7 +10141,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="66" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="66" spans="2:6" ht="15" customHeight="1">
       <c r="B66" s="102" t="s">
         <v>157</v>
       </c>
@@ -10168,7 +10157,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="67" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="67" spans="2:6" ht="15" customHeight="1">
       <c r="B67" s="102" t="s">
         <v>147</v>
       </c>
@@ -10178,7 +10167,7 @@
       </c>
       <c r="F67" s="223"/>
     </row>
-    <row r="68" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="68" spans="2:6" ht="15" customHeight="1">
       <c r="B68" s="102" t="s">
         <v>151</v>
       </c>
@@ -10188,7 +10177,7 @@
       </c>
       <c r="F68" s="223"/>
     </row>
-    <row r="69" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="69" spans="2:6" ht="15" customHeight="1">
       <c r="B69" s="102" t="s">
         <v>149</v>
       </c>
@@ -10198,7 +10187,7 @@
       </c>
       <c r="F69" s="223"/>
     </row>
-    <row r="70" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="70" spans="2:6" ht="15" customHeight="1">
       <c r="B70" s="77" t="s">
         <v>158</v>
       </c>
@@ -10208,10 +10197,10 @@
       </c>
       <c r="F70" s="223"/>
     </row>
-    <row r="71" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="71" spans="2:6" ht="15" customHeight="1">
       <c r="F71" s="223"/>
     </row>
-    <row r="72" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="72" spans="2:6" ht="15" customHeight="1">
       <c r="B72" s="225" t="s">
         <v>256</v>
       </c>
@@ -10223,7 +10212,7 @@
       </c>
       <c r="F72" s="223"/>
     </row>
-    <row r="73" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="73" spans="2:6" ht="15" customHeight="1">
       <c r="B73" s="102" t="s">
         <v>255</v>
       </c>
@@ -10239,7 +10228,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="74" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="74" spans="2:6" ht="15" customHeight="1">
       <c r="B74" s="227" t="s">
         <v>259</v>
       </c>
@@ -10255,7 +10244,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="75" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="75" spans="2:6" ht="15" customHeight="1">
       <c r="B75" s="77" t="s">
         <v>258</v>
       </c>
@@ -10268,7 +10257,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="76" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="76" spans="2:6" ht="15" customHeight="1">
       <c r="B76" s="229" t="s">
         <v>260</v>
       </c>
@@ -10281,10 +10270,10 @@
         <v>261</v>
       </c>
     </row>
-    <row r="77" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="77" spans="2:6" ht="15" customHeight="1">
       <c r="F77" s="223"/>
     </row>
-    <row r="78" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="78" spans="2:6" ht="15" customHeight="1">
       <c r="B78" s="16" t="s">
         <v>159</v>
       </c>
@@ -10296,7 +10285,7 @@
       </c>
       <c r="F78" s="223"/>
     </row>
-    <row r="79" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="79" spans="2:6" ht="15" customHeight="1">
       <c r="B79" s="102" t="s">
         <v>148</v>
       </c>
@@ -10310,7 +10299,7 @@
       </c>
       <c r="F79" s="223"/>
     </row>
-    <row r="80" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="80" spans="2:6" ht="15" customHeight="1">
       <c r="B80" s="102" t="s">
         <v>152</v>
       </c>
@@ -10324,7 +10313,7 @@
       </c>
       <c r="F80" s="223"/>
     </row>
-    <row r="81" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="81" spans="2:8" ht="15" customHeight="1">
       <c r="B81" s="102" t="s">
         <v>150</v>
       </c>
@@ -10338,7 +10327,7 @@
       </c>
       <c r="F81" s="223"/>
     </row>
-    <row r="82" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="82" spans="2:8" ht="15" customHeight="1">
       <c r="B82" s="77" t="s">
         <v>159</v>
       </c>
@@ -10352,7 +10341,7 @@
       </c>
       <c r="F82" s="223"/>
     </row>
-    <row r="84" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="84" spans="2:8" ht="15" customHeight="1">
       <c r="B84" s="76" t="s">
         <v>241</v>
       </c>
@@ -10363,7 +10352,7 @@
       <c r="G84" s="35"/>
       <c r="H84" s="35"/>
     </row>
-    <row r="85" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="85" spans="2:8" ht="15" customHeight="1">
       <c r="B85" s="16" t="s">
         <v>242</v>
       </c>
@@ -10371,68 +10360,68 @@
         <v>243</v>
       </c>
     </row>
-    <row r="86" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="86" spans="2:8" ht="15" customHeight="1">
       <c r="B86" s="212" t="s">
         <v>239</v>
       </c>
       <c r="C86" s="73">
         <f>DCF!F4*Exchange_Rate</f>
-        <v>-35379.68</v>
+        <v>-35595.091101491642</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-12.770144477195332</v>
+        <v>-12.847896194792552</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="87" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="87" spans="2:8" ht="15" customHeight="1">
       <c r="B87" s="212" t="s">
         <v>240</v>
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>50579.258142485101</v>
+        <v>50887.212700273718</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>18.256367328050825</v>
+        <v>18.367522211175022</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="88" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="88" spans="2:8" ht="15" customHeight="1">
       <c r="B88" s="213" t="s">
         <v>159</v>
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>5585.3280000000004</v>
+        <v>5619.3345726052949</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>2.0160003005263034</v>
+        <v>2.028274827750514</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="89" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="89" spans="2:8" ht="15" customHeight="1">
       <c r="B89" s="77" t="s">
         <v>244</v>
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>20784.906142485102</v>
+        <v>20911.45617138737</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>7.5022231513817959</v>
+        <v>7.5479008441329833</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -10458,19 +10447,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Q807"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="1.33203125" style="2" customWidth="1"/>
     <col min="2" max="2" width="26.33203125" style="2" customWidth="1"/>
     <col min="3" max="3" width="20.6640625" style="2" customWidth="1"/>
     <col min="4" max="4" width="2.6640625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="25.1640625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="25.1328125" style="2" customWidth="1"/>
     <col min="6" max="6" width="2.6640625" style="2" customWidth="1"/>
     <col min="7" max="17" width="20.6640625" style="2" customWidth="1"/>
     <col min="18" max="16384" width="12.33203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:17" ht="15.75" customHeight="1">
       <c r="A1" s="3"/>
       <c r="B1" s="87" t="str">
         <f>Thesis!E17</f>
@@ -10527,7 +10516,7 @@
         <v>42094</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" ht="15.75" customHeight="1">
       <c r="A2" s="3"/>
       <c r="B2" s="51" t="s">
         <v>95</v>
@@ -10550,7 +10539,7 @@
       <c r="P2" s="35"/>
       <c r="Q2" s="35"/>
     </row>
-    <row r="3" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:17" ht="15.75" customHeight="1">
       <c r="A3" s="10"/>
       <c r="B3" s="16" t="s">
         <v>393</v>
@@ -10570,7 +10559,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="4" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:17" ht="15.75" customHeight="1">
       <c r="A4" s="10"/>
       <c r="B4" s="25" t="s">
         <v>0</v>
@@ -10627,7 +10616,7 @@
         <v/>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:17" ht="15.75" customHeight="1">
       <c r="A5" s="10"/>
       <c r="B5" s="2" t="s">
         <v>43</v>
@@ -10682,7 +10671,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:17" ht="15.75" customHeight="1">
       <c r="A6" s="10"/>
       <c r="B6" s="30" t="s">
         <v>45</v>
@@ -10737,7 +10726,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:17" ht="15.75" customHeight="1">
       <c r="A7" s="10"/>
       <c r="B7" s="8" t="s">
         <v>42</v>
@@ -10792,7 +10781,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:17" ht="15.75" customHeight="1">
       <c r="A8" s="10"/>
       <c r="B8" s="28" t="s">
         <v>127</v>
@@ -10849,7 +10838,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:17" ht="15.75" customHeight="1">
       <c r="A9" s="10"/>
       <c r="B9" s="26" t="s">
         <v>415</v>
@@ -10906,7 +10895,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:17" ht="15.75" customHeight="1">
       <c r="A10" s="10"/>
       <c r="B10" s="2" t="s">
         <v>65</v>
@@ -10961,7 +10950,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:17" ht="15.75" customHeight="1">
       <c r="A11" s="10"/>
       <c r="B11" s="67" t="s">
         <v>137</v>
@@ -11016,7 +11005,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:17" ht="15.75" customHeight="1">
       <c r="A12" s="10"/>
       <c r="B12" s="2" t="s">
         <v>60</v>
@@ -11071,7 +11060,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:17" ht="15.75" customHeight="1">
       <c r="A13" s="10"/>
       <c r="B13" s="38" t="s">
         <v>208</v>
@@ -11128,7 +11117,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:17" ht="15.75" customHeight="1">
       <c r="A14" s="10"/>
       <c r="B14" s="39" t="s">
         <v>129</v>
@@ -11185,7 +11174,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:17" ht="15.75" customHeight="1">
       <c r="A15" s="10"/>
       <c r="B15" s="2" t="s">
         <v>62</v>
@@ -11240,7 +11229,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:17" ht="15.75" customHeight="1">
       <c r="A16" s="10"/>
       <c r="B16" s="2" t="s">
         <v>398</v>
@@ -11295,7 +11284,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:17" ht="15.75" customHeight="1">
       <c r="A17" s="10"/>
       <c r="B17" s="26" t="s">
         <v>49</v>
@@ -11321,7 +11310,7 @@
       <c r="P17" s="272"/>
       <c r="Q17" s="272"/>
     </row>
-    <row r="18" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:17" ht="15.75" customHeight="1">
       <c r="A18" s="10"/>
       <c r="B18" s="26" t="s">
         <v>94</v>
@@ -11346,7 +11335,7 @@
       <c r="P18" s="273"/>
       <c r="Q18" s="273"/>
     </row>
-    <row r="19" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:17" ht="15.75" customHeight="1">
       <c r="A19" s="10"/>
       <c r="B19" s="30" t="s">
         <v>63</v>
@@ -11403,7 +11392,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:17" ht="15.75" customHeight="1">
       <c r="A20" s="10"/>
       <c r="B20" s="26"/>
       <c r="C20" s="59"/>
@@ -11422,7 +11411,7 @@
       <c r="P20" s="12"/>
       <c r="Q20" s="12"/>
     </row>
-    <row r="21" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:17" ht="15.75" customHeight="1">
       <c r="A21" s="10"/>
       <c r="B21" s="51" t="s">
         <v>174</v>
@@ -11445,7 +11434,7 @@
       <c r="P21" s="35"/>
       <c r="Q21" s="35"/>
     </row>
-    <row r="22" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:17" ht="15.75" customHeight="1">
       <c r="A22" s="10"/>
       <c r="B22" s="61" t="s">
         <v>43</v>
@@ -11466,7 +11455,7 @@
       <c r="P22" s="12"/>
       <c r="Q22" s="12"/>
     </row>
-    <row r="23" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:17" ht="15.75" customHeight="1">
       <c r="A23" s="10"/>
       <c r="B23" s="26" t="s">
         <v>40</v>
@@ -11523,7 +11512,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:17" ht="15.75" customHeight="1">
       <c r="A24" s="10"/>
       <c r="B24" s="65" t="s">
         <v>59</v>
@@ -11580,7 +11569,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:17" ht="15.75" customHeight="1">
       <c r="A25" s="10"/>
       <c r="B25" s="26" t="s">
         <v>46</v>
@@ -11637,7 +11626,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:17" ht="15.75" customHeight="1">
       <c r="A26" s="10"/>
       <c r="B26" s="67" t="s">
         <v>43</v>
@@ -11694,18 +11683,18 @@
         <v/>
       </c>
     </row>
-    <row r="27" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:17" ht="15.75" customHeight="1">
       <c r="A27" s="10"/>
       <c r="E27" s="237"/>
     </row>
-    <row r="28" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:17" ht="15.75" customHeight="1">
       <c r="A28" s="10"/>
       <c r="B28" s="61" t="s">
         <v>175</v>
       </c>
       <c r="E28" s="237"/>
     </row>
-    <row r="29" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:17" ht="15.75" customHeight="1">
       <c r="A29" s="10"/>
       <c r="B29" s="25" t="s">
         <v>40</v>
@@ -11762,7 +11751,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:17" ht="15.75" customHeight="1">
       <c r="A30" s="10"/>
       <c r="B30" s="65" t="str">
         <f>B24</f>
@@ -11820,7 +11809,7 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:17" ht="15.75" customHeight="1">
       <c r="A31" s="10"/>
       <c r="B31" s="26" t="str">
         <f>B25</f>
@@ -11877,7 +11866,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:17" ht="15.75" customHeight="1">
       <c r="A32" s="10"/>
       <c r="B32" s="67" t="s">
         <v>43</v>
@@ -11932,18 +11921,18 @@
         <v/>
       </c>
     </row>
-    <row r="33" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:17" ht="15.75" customHeight="1">
       <c r="A33" s="10"/>
       <c r="E33" s="237"/>
     </row>
-    <row r="34" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:17" ht="15.75" customHeight="1">
       <c r="A34" s="10"/>
       <c r="B34" s="61" t="s">
         <v>42</v>
       </c>
       <c r="E34" s="237"/>
     </row>
-    <row r="35" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:17" ht="15.75" customHeight="1">
       <c r="A35" s="10"/>
       <c r="B35" s="298" t="s">
         <v>396</v>
@@ -12000,18 +11989,18 @@
         <v/>
       </c>
     </row>
-    <row r="36" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:17" ht="15.75" customHeight="1">
       <c r="A36" s="10"/>
       <c r="E36" s="237"/>
     </row>
-    <row r="37" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:17" ht="15.75" customHeight="1">
       <c r="A37" s="10"/>
       <c r="B37" s="61" t="s">
         <v>176</v>
       </c>
       <c r="E37" s="237"/>
     </row>
-    <row r="38" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:17" ht="15.75" customHeight="1">
       <c r="A38" s="10"/>
       <c r="B38" s="298" t="s">
         <v>396</v>
@@ -12066,18 +12055,18 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:17" ht="15.75" customHeight="1">
       <c r="A39" s="10"/>
       <c r="E39" s="237"/>
     </row>
-    <row r="40" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:17" ht="15.75" customHeight="1">
       <c r="A40" s="10"/>
       <c r="B40" s="61" t="s">
         <v>177</v>
       </c>
       <c r="E40" s="237"/>
     </row>
-    <row r="41" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:17" ht="15.75" customHeight="1">
       <c r="A41" s="10"/>
       <c r="B41" s="26" t="s">
         <v>142</v>
@@ -12135,10 +12124,10 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:17" ht="15.75" customHeight="1">
       <c r="A42" s="10"/>
     </row>
-    <row r="43" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:17" ht="15.75" customHeight="1">
       <c r="A43" s="10"/>
       <c r="B43" s="51" t="s">
         <v>178</v>
@@ -12161,14 +12150,14 @@
       <c r="P43" s="35"/>
       <c r="Q43" s="35"/>
     </row>
-    <row r="44" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:17" ht="15.75" customHeight="1">
       <c r="A44" s="10"/>
       <c r="B44" s="61" t="s">
         <v>57</v>
       </c>
       <c r="E44" s="237"/>
     </row>
-    <row r="45" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:17" ht="15.75" customHeight="1">
       <c r="A45" s="10"/>
       <c r="B45" s="2" t="s">
         <v>37</v>
@@ -12223,7 +12212,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:17" ht="15.75" customHeight="1">
       <c r="A46" s="10"/>
       <c r="B46" s="2" t="s">
         <v>272</v>
@@ -12278,7 +12267,7 @@
         <v/>
       </c>
     </row>
-    <row r="47" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:17" ht="15.75" customHeight="1">
       <c r="A47" s="10"/>
       <c r="B47" s="245" t="s">
         <v>269</v>
@@ -12335,7 +12324,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:17" ht="15.75" customHeight="1">
       <c r="A48" s="10"/>
       <c r="B48" s="67" t="s">
         <v>65</v>
@@ -12390,11 +12379,11 @@
         <v/>
       </c>
     </row>
-    <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:17" ht="15.75" customHeight="1">
       <c r="A49" s="10"/>
       <c r="E49" s="237"/>
     </row>
-    <row r="50" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:17" ht="15.75" customHeight="1">
       <c r="A50" s="10"/>
       <c r="B50" s="69" t="s">
         <v>130</v>
@@ -12404,7 +12393,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="51" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:17" ht="15.75" customHeight="1">
       <c r="A51" s="10"/>
       <c r="B51" s="8" t="s">
         <v>85</v>
@@ -12428,7 +12417,7 @@
       <c r="P51" s="151"/>
       <c r="Q51" s="151"/>
     </row>
-    <row r="52" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:17" ht="15.75" customHeight="1">
       <c r="A52" s="10"/>
       <c r="B52" s="8" t="s">
         <v>84</v>
@@ -12452,7 +12441,7 @@
       <c r="P52" s="151"/>
       <c r="Q52" s="151"/>
     </row>
-    <row r="53" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:17" ht="15.75" customHeight="1">
       <c r="A53" s="10"/>
       <c r="B53" s="25" t="s">
         <v>87</v>
@@ -12507,11 +12496,11 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:17" ht="15.75" customHeight="1">
       <c r="A54" s="10"/>
       <c r="E54" s="237"/>
     </row>
-    <row r="55" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:17" ht="15.75" customHeight="1">
       <c r="A55" s="10"/>
       <c r="B55" s="61" t="s">
         <v>139</v>
@@ -12521,7 +12510,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="56" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:17" ht="15.75" customHeight="1">
       <c r="A56" s="10"/>
       <c r="B56" s="38" t="s">
         <v>138</v>
@@ -12576,7 +12565,7 @@
         <v/>
       </c>
     </row>
-    <row r="57" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:17" ht="15.75" customHeight="1">
       <c r="A57" s="10"/>
       <c r="B57" s="38" t="s">
         <v>134</v>
@@ -12631,7 +12620,7 @@
         <v/>
       </c>
     </row>
-    <row r="58" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:17" ht="15.75" customHeight="1">
       <c r="A58" s="10"/>
       <c r="B58" s="38" t="s">
         <v>133</v>
@@ -12686,7 +12675,7 @@
         <v/>
       </c>
     </row>
-    <row r="59" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:17" ht="15.75" customHeight="1">
       <c r="A59" s="10"/>
       <c r="B59" s="30" t="s">
         <v>163</v>
@@ -12741,7 +12730,7 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:17" ht="15.75" customHeight="1">
       <c r="A60" s="10"/>
       <c r="B60" s="38" t="s">
         <v>135</v>
@@ -12797,7 +12786,7 @@
         <v/>
       </c>
     </row>
-    <row r="61" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:17" ht="15.75" customHeight="1">
       <c r="A61" s="10"/>
       <c r="B61" s="30" t="s">
         <v>164</v>
@@ -12852,11 +12841,11 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:17" ht="15.75" customHeight="1">
       <c r="A62" s="10"/>
       <c r="E62" s="237"/>
     </row>
-    <row r="63" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:17" ht="15.75" customHeight="1">
       <c r="A63" s="10"/>
       <c r="B63" s="93" t="s">
         <v>140</v>
@@ -12866,7 +12855,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="64" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:17" ht="15.75" customHeight="1">
       <c r="A64" s="10"/>
       <c r="B64" s="38" t="s">
         <v>138</v>
@@ -12891,7 +12880,7 @@
       <c r="P64" s="157"/>
       <c r="Q64" s="157"/>
     </row>
-    <row r="65" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:17" ht="15.75" customHeight="1">
       <c r="A65" s="10"/>
       <c r="B65" s="102" t="s">
         <v>132</v>
@@ -12916,7 +12905,7 @@
       <c r="P65" s="157"/>
       <c r="Q65" s="157"/>
     </row>
-    <row r="66" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:17" ht="15.75" customHeight="1">
       <c r="A66" s="10"/>
       <c r="B66" s="102" t="s">
         <v>133</v>
@@ -12941,7 +12930,7 @@
       <c r="P66" s="157"/>
       <c r="Q66" s="157"/>
     </row>
-    <row r="67" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:17" ht="15.75" customHeight="1">
       <c r="A67" s="10"/>
       <c r="B67" s="30" t="s">
         <v>163</v>
@@ -12968,10 +12957,10 @@
       <c r="P67" s="157"/>
       <c r="Q67" s="157"/>
     </row>
-    <row r="68" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:17" ht="15.75" customHeight="1">
       <c r="A68" s="10"/>
     </row>
-    <row r="69" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:17" ht="15.75" customHeight="1">
       <c r="A69" s="10"/>
       <c r="B69" s="51" t="s">
         <v>181</v>
@@ -12994,7 +12983,7 @@
       <c r="P69" s="35"/>
       <c r="Q69" s="35"/>
     </row>
-    <row r="70" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:17" ht="15.75" customHeight="1">
       <c r="A70" s="10"/>
       <c r="B70" s="69" t="s">
         <v>185</v>
@@ -13015,7 +13004,7 @@
       <c r="P70" s="12"/>
       <c r="Q70" s="12"/>
     </row>
-    <row r="71" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:17" ht="15.75" customHeight="1">
       <c r="A71" s="10"/>
       <c r="B71" s="2" t="s">
         <v>43</v>
@@ -13072,7 +13061,7 @@
         <v/>
       </c>
     </row>
-    <row r="72" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:17" ht="15.75" customHeight="1">
       <c r="A72" s="10"/>
       <c r="B72" s="30" t="s">
         <v>45</v>
@@ -13129,7 +13118,7 @@
         <v/>
       </c>
     </row>
-    <row r="73" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:17" ht="15.75" customHeight="1">
       <c r="A73" s="10"/>
       <c r="B73" s="8" t="s">
         <v>42</v>
@@ -13186,7 +13175,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:17" ht="15.75" customHeight="1">
       <c r="A74" s="10"/>
       <c r="B74" s="28" t="s">
         <v>127</v>
@@ -13243,7 +13232,7 @@
         <v/>
       </c>
     </row>
-    <row r="75" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:17" ht="15.75" customHeight="1">
       <c r="A75" s="10"/>
       <c r="B75" s="26" t="s">
         <v>128</v>
@@ -13300,7 +13289,7 @@
         <v/>
       </c>
     </row>
-    <row r="76" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:17" ht="15.75" customHeight="1">
       <c r="A76" s="10"/>
       <c r="B76" s="2" t="s">
         <v>65</v>
@@ -13357,7 +13346,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:17" ht="15.75" customHeight="1">
       <c r="A77" s="10"/>
       <c r="B77" s="67" t="s">
         <v>137</v>
@@ -13414,7 +13403,7 @@
         <v/>
       </c>
     </row>
-    <row r="78" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:17" ht="15.75" customHeight="1">
       <c r="A78" s="10"/>
       <c r="B78" s="2" t="s">
         <v>60</v>
@@ -13471,7 +13460,7 @@
         <v/>
       </c>
     </row>
-    <row r="79" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:17" ht="15.75" customHeight="1">
       <c r="A79" s="10"/>
       <c r="B79" s="38" t="str">
         <f>B13</f>
@@ -13529,7 +13518,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:17" ht="15.75" customHeight="1">
       <c r="A80" s="10"/>
       <c r="B80" s="39" t="s">
         <v>129</v>
@@ -13586,7 +13575,7 @@
         <v/>
       </c>
     </row>
-    <row r="81" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:17" ht="15.75" customHeight="1">
       <c r="A81" s="10"/>
       <c r="B81" s="2" t="s">
         <v>62</v>
@@ -13643,7 +13632,7 @@
         <v/>
       </c>
     </row>
-    <row r="82" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:17" ht="15.75" customHeight="1">
       <c r="A82" s="10"/>
       <c r="B82" s="2" t="s">
         <v>77</v>
@@ -13702,7 +13691,7 @@
         <v/>
       </c>
     </row>
-    <row r="83" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:17" ht="15.75" customHeight="1">
       <c r="A83" s="10"/>
       <c r="B83" s="26" t="s">
         <v>49</v>
@@ -13728,7 +13717,7 @@
       <c r="P83" s="203"/>
       <c r="Q83" s="203"/>
     </row>
-    <row r="84" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:17" ht="15.75" customHeight="1">
       <c r="A84" s="10"/>
       <c r="B84" s="8" t="s">
         <v>94</v>
@@ -13752,7 +13741,7 @@
       <c r="P84" s="151"/>
       <c r="Q84" s="151"/>
     </row>
-    <row r="85" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:17" ht="15.75" customHeight="1">
       <c r="A85" s="10"/>
       <c r="B85" s="30" t="s">
         <v>117</v>
@@ -13809,18 +13798,18 @@
         <v/>
       </c>
     </row>
-    <row r="86" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:17" ht="15.75" customHeight="1">
       <c r="A86" s="10"/>
       <c r="E86" s="237"/>
     </row>
-    <row r="87" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:17" ht="15.75" customHeight="1">
       <c r="A87" s="10"/>
       <c r="B87" s="61" t="s">
         <v>183</v>
       </c>
       <c r="E87" s="237"/>
     </row>
-    <row r="88" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:17" ht="15.75" customHeight="1">
       <c r="A88" s="10"/>
       <c r="B88" s="2" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
@@ -13876,7 +13865,7 @@
         <v/>
       </c>
     </row>
-    <row r="89" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="89" spans="1:17" ht="15.75" customHeight="1">
       <c r="A89" s="10"/>
       <c r="B89" s="2" t="str">
         <f>"Dividend ("&amp;Market_currency&amp;")"</f>
@@ -13932,7 +13921,7 @@
         <v/>
       </c>
     </row>
-    <row r="90" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:17" ht="15.75" customHeight="1">
       <c r="A90" s="10"/>
       <c r="B90" s="2" t="s">
         <v>182</v>
@@ -13987,7 +13976,7 @@
         <v/>
       </c>
     </row>
-    <row r="91" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:17" ht="15.75" customHeight="1">
       <c r="A91" s="10"/>
       <c r="B91" s="2" t="s">
         <v>331</v>
@@ -14008,23 +13997,23 @@
       <c r="P91" s="293"/>
       <c r="Q91" s="293"/>
     </row>
-    <row r="92" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:17" ht="15.75" customHeight="1">
       <c r="A92" s="10"/>
       <c r="B92" s="2" t="s">
         <v>330</v>
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>3.0159744408945685E-2</v>
+        <v>3.0082855321861054E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>3.0159744408945685E-2</v>
+        <v>3.0082855321861054E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>2.5175718849840253E-2</v>
+        <v>2.5111536010197576E-2</v>
       </c>
       <c r="I92" s="22" t="str">
         <f t="shared" si="38"/>
@@ -14063,11 +14052,11 @@
         <v/>
       </c>
     </row>
-    <row r="93" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:17" ht="15.75" customHeight="1">
       <c r="A93" s="10"/>
       <c r="E93" s="237"/>
     </row>
-    <row r="94" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:17" ht="15.75" customHeight="1">
       <c r="A94" s="10"/>
       <c r="B94" s="143" t="s">
         <v>81</v>
@@ -14088,7 +14077,7 @@
       <c r="P94" s="12"/>
       <c r="Q94" s="12"/>
     </row>
-    <row r="95" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:17" ht="15.75" customHeight="1">
       <c r="A95" s="10"/>
       <c r="B95" s="26" t="s">
         <v>121</v>
@@ -14145,7 +14134,7 @@
         <v/>
       </c>
     </row>
-    <row r="96" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:17" ht="15.75" customHeight="1">
       <c r="A96" s="10"/>
       <c r="B96" s="67" t="s">
         <v>137</v>
@@ -14202,10 +14191,10 @@
         <v/>
       </c>
     </row>
-    <row r="97" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="97" spans="1:17" ht="15.75" customHeight="1">
       <c r="A97" s="10"/>
     </row>
-    <row r="98" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:17" ht="15.75" customHeight="1">
       <c r="A98" s="3"/>
       <c r="B98" s="51" t="s">
         <v>184</v>
@@ -14228,7 +14217,7 @@
       <c r="P98" s="35"/>
       <c r="Q98" s="35"/>
     </row>
-    <row r="99" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="99" spans="1:17" ht="15.75" customHeight="1">
       <c r="A99" s="10"/>
       <c r="B99" s="61" t="s">
         <v>26</v>
@@ -14238,7 +14227,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="100" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="100" spans="1:17" ht="15.75" customHeight="1">
       <c r="A100" s="10"/>
       <c r="B100" s="25" t="s">
         <v>1</v>
@@ -14295,7 +14284,7 @@
         <v/>
       </c>
     </row>
-    <row r="101" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="101" spans="1:17" ht="15.75" customHeight="1">
       <c r="A101" s="10"/>
       <c r="B101" s="90" t="s">
         <v>179</v>
@@ -14352,7 +14341,7 @@
         <v/>
       </c>
     </row>
-    <row r="102" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="102" spans="1:17" ht="15.75" customHeight="1">
       <c r="A102" s="10"/>
       <c r="B102" s="90" t="s">
         <v>180</v>
@@ -14409,7 +14398,7 @@
         <v/>
       </c>
     </row>
-    <row r="103" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="103" spans="1:17" ht="15.75" customHeight="1">
       <c r="A103" s="10"/>
       <c r="B103" s="25" t="s">
         <v>38</v>
@@ -14466,7 +14455,7 @@
         <v/>
       </c>
     </row>
-    <row r="104" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="104" spans="1:17" ht="15.75" customHeight="1">
       <c r="A104" s="10"/>
       <c r="B104" s="25" t="s">
         <v>28</v>
@@ -14523,11 +14512,11 @@
         <v/>
       </c>
     </row>
-    <row r="105" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="105" spans="1:17" ht="15.75" customHeight="1">
       <c r="A105" s="10"/>
       <c r="E105" s="237"/>
     </row>
-    <row r="106" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="106" spans="1:17" ht="15.75" customHeight="1">
       <c r="A106" s="10"/>
       <c r="B106" s="88" t="s">
         <v>189</v>
@@ -14550,7 +14539,7 @@
       <c r="P106" s="12"/>
       <c r="Q106" s="12"/>
     </row>
-    <row r="107" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="107" spans="1:17" ht="15.75" customHeight="1">
       <c r="A107" s="10"/>
       <c r="B107" s="25" t="s">
         <v>186</v>
@@ -14607,7 +14596,7 @@
         <v/>
       </c>
     </row>
-    <row r="108" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="108" spans="1:17" ht="15.75" customHeight="1">
       <c r="A108" s="10"/>
       <c r="B108" s="25" t="s">
         <v>187</v>
@@ -14664,7 +14653,7 @@
         <v/>
       </c>
     </row>
-    <row r="109" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="109" spans="1:17" ht="15.75" customHeight="1">
       <c r="A109" s="10"/>
       <c r="B109" s="25" t="s">
         <v>66</v>
@@ -14691,18 +14680,18 @@
       <c r="P109" s="186"/>
       <c r="Q109" s="186"/>
     </row>
-    <row r="110" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="110" spans="1:17" ht="15.75" customHeight="1">
       <c r="A110" s="10"/>
       <c r="E110" s="237"/>
     </row>
-    <row r="111" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="111" spans="1:17" ht="15.75" customHeight="1">
       <c r="A111" s="10"/>
       <c r="B111" s="61" t="s">
         <v>48</v>
       </c>
       <c r="E111" s="237"/>
     </row>
-    <row r="112" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="112" spans="1:17" ht="15.75" customHeight="1">
       <c r="A112" s="10"/>
       <c r="B112" s="2" t="s">
         <v>303</v>
@@ -14756,7 +14745,7 @@
         <v/>
       </c>
     </row>
-    <row r="113" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="113" spans="1:17" ht="15.75" customHeight="1">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
         <v>304</v>
@@ -14811,11 +14800,11 @@
         <v/>
       </c>
     </row>
-    <row r="114" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="114" spans="1:17" ht="15.75" customHeight="1">
       <c r="A114" s="10"/>
       <c r="E114" s="237"/>
     </row>
-    <row r="115" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="115" spans="1:17" ht="15.75" customHeight="1">
       <c r="A115" s="10"/>
       <c r="B115" s="88" t="s">
         <v>36</v>
@@ -14874,7 +14863,7 @@
         <v/>
       </c>
     </row>
-    <row r="116" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="116" spans="1:17" ht="15.75" customHeight="1">
       <c r="A116" s="10"/>
       <c r="B116" s="7" t="s">
         <v>190</v>
@@ -14932,7 +14921,7 @@
         <v/>
       </c>
     </row>
-    <row r="117" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="117" spans="1:17" ht="15.75" customHeight="1">
       <c r="B117" s="7" t="s">
         <v>80</v>
       </c>
@@ -14989,7 +14978,7 @@
         <v/>
       </c>
     </row>
-    <row r="118" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="118" spans="1:17" ht="15.75" customHeight="1">
       <c r="B118" s="7" t="s">
         <v>88</v>
       </c>
@@ -15048,7 +15037,7 @@
         <v/>
       </c>
     </row>
-    <row r="119" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="119" spans="1:17" ht="15.75" customHeight="1">
       <c r="A119" s="10"/>
       <c r="B119" s="67" t="s">
         <v>191</v>
@@ -15107,7 +15096,7 @@
         <v/>
       </c>
     </row>
-    <row r="120" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="120" spans="1:17" ht="15.75" customHeight="1">
       <c r="A120" s="10"/>
       <c r="B120" s="26"/>
       <c r="C120" s="59"/>
@@ -15126,7 +15115,7 @@
       <c r="P120" s="12"/>
       <c r="Q120" s="12"/>
     </row>
-    <row r="121" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:17" ht="15.75" customHeight="1">
       <c r="A121" s="10"/>
       <c r="B121" s="51" t="s">
         <v>192</v>
@@ -15149,7 +15138,7 @@
       <c r="P121" s="35"/>
       <c r="Q121" s="35"/>
     </row>
-    <row r="122" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="122" spans="1:17" ht="15.75" customHeight="1">
       <c r="A122" s="10"/>
       <c r="B122" s="160" t="s">
         <v>141</v>
@@ -15170,7 +15159,7 @@
       <c r="P122" s="12"/>
       <c r="Q122" s="12"/>
     </row>
-    <row r="123" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="123" spans="1:17" ht="15.75" customHeight="1">
       <c r="A123" s="10"/>
       <c r="B123" s="26" t="str">
         <f>"FCFE per share ("&amp;Market_currency&amp;")"</f>
@@ -15178,18 +15167,18 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>3.3838106184170127</v>
+        <v>3.4044131329833491</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="234"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>2.6321317766000449</v>
+        <v>2.6481576537495433</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>2.936943227921875</v>
+        <v>2.9548249661327648</v>
       </c>
       <c r="I123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15228,25 +15217,25 @@
         <v/>
       </c>
     </row>
-    <row r="124" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="124" spans="1:17" ht="15.75" customHeight="1">
       <c r="A124" s="10"/>
       <c r="B124" s="26" t="s">
         <v>226</v>
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>4.3243586177853198E-2</v>
+        <v>4.3395960904822804E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>3.36374667936108E-2</v>
+        <v>3.3755993036960398E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>3.7532820804113416E-2</v>
+        <v>3.7665072863387696E-2</v>
       </c>
       <c r="I124" s="74" t="str">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
@@ -15285,18 +15274,18 @@
         <v/>
       </c>
     </row>
-    <row r="125" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="125" spans="1:17" ht="15.75" customHeight="1">
       <c r="B125" s="2" t="s">
         <v>306</v>
       </c>
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.8365585075346911E-2</v>
+        <v>7.8165800282293127E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.2017699858419399E-2</v>
+        <v>5.1885086219519663E-2</v>
       </c>
       <c r="I125" s="22" t="str">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -15335,688 +15324,688 @@
         <v/>
       </c>
     </row>
-    <row r="126" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="127" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="128" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="126" spans="1:17" ht="15.75" customHeight="1"/>
+    <row r="127" spans="1:17" ht="15.75" customHeight="1"/>
+    <row r="128" spans="1:17" ht="15.75" customHeight="1"/>
+    <row r="129" ht="15.75" customHeight="1"/>
+    <row r="130" ht="15.75" customHeight="1"/>
+    <row r="131" ht="15.75" customHeight="1"/>
+    <row r="132" ht="15.75" customHeight="1"/>
+    <row r="133" ht="15.75" customHeight="1"/>
+    <row r="134" ht="15.75" customHeight="1"/>
+    <row r="135" ht="15.75" customHeight="1"/>
+    <row r="136" ht="15.75" customHeight="1"/>
+    <row r="137" ht="15.75" customHeight="1"/>
+    <row r="138" ht="15.75" customHeight="1"/>
+    <row r="139" ht="15.75" customHeight="1"/>
+    <row r="140" ht="15.75" customHeight="1"/>
+    <row r="141" ht="15.75" customHeight="1"/>
+    <row r="142" ht="15.75" customHeight="1"/>
+    <row r="143" ht="15.75" customHeight="1"/>
+    <row r="144" ht="15.75" customHeight="1"/>
+    <row r="145" ht="15.75" customHeight="1"/>
+    <row r="146" ht="15.75" customHeight="1"/>
+    <row r="147" ht="15.75" customHeight="1"/>
+    <row r="148" ht="15.75" customHeight="1"/>
+    <row r="149" ht="15.75" customHeight="1"/>
+    <row r="150" ht="15.75" customHeight="1"/>
+    <row r="151" ht="15.75" customHeight="1"/>
+    <row r="152" ht="15.75" customHeight="1"/>
+    <row r="153" ht="15.75" customHeight="1"/>
+    <row r="154" ht="15.75" customHeight="1"/>
+    <row r="155" ht="15.75" customHeight="1"/>
+    <row r="156" ht="15.75" customHeight="1"/>
+    <row r="157" ht="15.75" customHeight="1"/>
+    <row r="158" ht="15.75" customHeight="1"/>
+    <row r="159" ht="15.75" customHeight="1"/>
+    <row r="160" ht="15.75" customHeight="1"/>
+    <row r="161" ht="15.75" customHeight="1"/>
+    <row r="162" ht="15.75" customHeight="1"/>
+    <row r="163" ht="15.75" customHeight="1"/>
+    <row r="164" ht="15.75" customHeight="1"/>
+    <row r="165" ht="15.75" customHeight="1"/>
+    <row r="166" ht="15.75" customHeight="1"/>
+    <row r="167" ht="15.75" customHeight="1"/>
+    <row r="168" ht="15.75" customHeight="1"/>
+    <row r="169" ht="15.75" customHeight="1"/>
+    <row r="170" ht="15.75" customHeight="1"/>
+    <row r="171" ht="15.75" customHeight="1"/>
+    <row r="172" ht="15.75" customHeight="1"/>
+    <row r="173" ht="15.75" customHeight="1"/>
+    <row r="174" ht="15.75" customHeight="1"/>
+    <row r="175" ht="15.75" customHeight="1"/>
+    <row r="176" ht="15.75" customHeight="1"/>
+    <row r="177" ht="15.75" customHeight="1"/>
+    <row r="178" ht="15.75" customHeight="1"/>
+    <row r="179" ht="15.75" customHeight="1"/>
+    <row r="180" ht="15.75" customHeight="1"/>
+    <row r="181" ht="15.75" customHeight="1"/>
+    <row r="182" ht="15.75" customHeight="1"/>
+    <row r="183" ht="15.75" customHeight="1"/>
+    <row r="184" ht="15.75" customHeight="1"/>
+    <row r="185" ht="15.75" customHeight="1"/>
+    <row r="186" ht="15.75" customHeight="1"/>
+    <row r="187" ht="15.75" customHeight="1"/>
+    <row r="188" ht="15.75" customHeight="1"/>
+    <row r="189" ht="15.75" customHeight="1"/>
+    <row r="190" ht="15.75" customHeight="1"/>
+    <row r="191" ht="15.75" customHeight="1"/>
+    <row r="192" ht="15.75" customHeight="1"/>
+    <row r="193" ht="15.75" customHeight="1"/>
+    <row r="194" ht="15.75" customHeight="1"/>
+    <row r="195" ht="15.75" customHeight="1"/>
+    <row r="196" ht="15.75" customHeight="1"/>
+    <row r="197" ht="15.75" customHeight="1"/>
+    <row r="198" ht="15.75" customHeight="1"/>
+    <row r="199" ht="15.75" customHeight="1"/>
+    <row r="200" ht="15.75" customHeight="1"/>
+    <row r="201" ht="15.75" customHeight="1"/>
+    <row r="202" ht="15.75" customHeight="1"/>
+    <row r="203" ht="15.75" customHeight="1"/>
+    <row r="204" ht="15.75" customHeight="1"/>
+    <row r="205" ht="15.75" customHeight="1"/>
+    <row r="206" ht="15.75" customHeight="1"/>
+    <row r="207" ht="15.75" customHeight="1"/>
+    <row r="208" ht="15.75" customHeight="1"/>
+    <row r="209" ht="15.75" customHeight="1"/>
+    <row r="210" ht="15.75" customHeight="1"/>
+    <row r="211" ht="15.75" customHeight="1"/>
+    <row r="212" ht="15.75" customHeight="1"/>
+    <row r="213" ht="15.75" customHeight="1"/>
+    <row r="214" ht="15.75" customHeight="1"/>
+    <row r="215" ht="15.75" customHeight="1"/>
+    <row r="216" ht="15.75" customHeight="1"/>
+    <row r="217" ht="15.75" customHeight="1"/>
+    <row r="218" ht="15.75" customHeight="1"/>
+    <row r="219" ht="15.75" customHeight="1"/>
+    <row r="220" ht="15.75" customHeight="1"/>
+    <row r="221" ht="15.75" customHeight="1"/>
+    <row r="222" ht="15.75" customHeight="1"/>
+    <row r="223" ht="15.75" customHeight="1"/>
+    <row r="224" ht="15.75" customHeight="1"/>
+    <row r="225" ht="15.75" customHeight="1"/>
+    <row r="226" ht="15.75" customHeight="1"/>
+    <row r="227" ht="15.75" customHeight="1"/>
+    <row r="228" ht="15.75" customHeight="1"/>
+    <row r="229" ht="15.75" customHeight="1"/>
+    <row r="230" ht="15.75" customHeight="1"/>
+    <row r="231" ht="15.75" customHeight="1"/>
+    <row r="232" ht="15.75" customHeight="1"/>
+    <row r="233" ht="15.75" customHeight="1"/>
+    <row r="234" ht="15.75" customHeight="1"/>
+    <row r="235" ht="15.75" customHeight="1"/>
+    <row r="236" ht="15.75" customHeight="1"/>
+    <row r="237" ht="15.75" customHeight="1"/>
+    <row r="238" ht="15.75" customHeight="1"/>
+    <row r="239" ht="15.75" customHeight="1"/>
+    <row r="240" ht="15.75" customHeight="1"/>
+    <row r="241" ht="15.75" customHeight="1"/>
+    <row r="242" ht="15.75" customHeight="1"/>
+    <row r="243" ht="15.75" customHeight="1"/>
+    <row r="244" ht="15.75" customHeight="1"/>
+    <row r="245" ht="15.75" customHeight="1"/>
+    <row r="246" ht="15.75" customHeight="1"/>
+    <row r="247" ht="15.75" customHeight="1"/>
+    <row r="248" ht="15.75" customHeight="1"/>
+    <row r="249" ht="15.75" customHeight="1"/>
+    <row r="250" ht="15.75" customHeight="1"/>
+    <row r="251" ht="15.75" customHeight="1"/>
+    <row r="252" ht="15.75" customHeight="1"/>
+    <row r="253" ht="15.75" customHeight="1"/>
+    <row r="254" ht="15.75" customHeight="1"/>
+    <row r="255" ht="15.75" customHeight="1"/>
+    <row r="256" ht="15.75" customHeight="1"/>
+    <row r="257" ht="15.75" customHeight="1"/>
+    <row r="258" ht="15.75" customHeight="1"/>
+    <row r="259" ht="15.75" customHeight="1"/>
+    <row r="260" ht="15.75" customHeight="1"/>
+    <row r="261" ht="15.75" customHeight="1"/>
+    <row r="262" ht="15.75" customHeight="1"/>
+    <row r="263" ht="15.75" customHeight="1"/>
+    <row r="264" ht="15.75" customHeight="1"/>
+    <row r="265" ht="15.75" customHeight="1"/>
+    <row r="266" ht="15.75" customHeight="1"/>
+    <row r="267" ht="15.75" customHeight="1"/>
+    <row r="268" ht="15.75" customHeight="1"/>
+    <row r="269" ht="15.75" customHeight="1"/>
+    <row r="270" ht="15.75" customHeight="1"/>
+    <row r="271" ht="15.75" customHeight="1"/>
+    <row r="272" ht="15.75" customHeight="1"/>
+    <row r="273" ht="15.75" customHeight="1"/>
+    <row r="274" ht="15.75" customHeight="1"/>
+    <row r="275" ht="15.75" customHeight="1"/>
+    <row r="276" ht="15.75" customHeight="1"/>
+    <row r="277" ht="15.75" customHeight="1"/>
+    <row r="278" ht="15.75" customHeight="1"/>
+    <row r="279" ht="15.75" customHeight="1"/>
+    <row r="280" ht="15.75" customHeight="1"/>
+    <row r="281" ht="15.75" customHeight="1"/>
+    <row r="282" ht="15.75" customHeight="1"/>
+    <row r="283" ht="15.75" customHeight="1"/>
+    <row r="284" ht="15.75" customHeight="1"/>
+    <row r="285" ht="15.75" customHeight="1"/>
+    <row r="286" ht="15.75" customHeight="1"/>
+    <row r="287" ht="15.75" customHeight="1"/>
+    <row r="288" ht="15.75" customHeight="1"/>
+    <row r="289" ht="15.75" customHeight="1"/>
+    <row r="290" ht="15.75" customHeight="1"/>
+    <row r="291" ht="15.75" customHeight="1"/>
+    <row r="292" ht="15.75" customHeight="1"/>
+    <row r="293" ht="15.75" customHeight="1"/>
+    <row r="294" ht="15.75" customHeight="1"/>
+    <row r="295" ht="15.75" customHeight="1"/>
+    <row r="296" ht="15.75" customHeight="1"/>
+    <row r="297" ht="15.75" customHeight="1"/>
+    <row r="298" ht="15.75" customHeight="1"/>
+    <row r="299" ht="15.75" customHeight="1"/>
+    <row r="300" ht="15.75" customHeight="1"/>
+    <row r="301" ht="15.75" customHeight="1"/>
+    <row r="302" ht="15.75" customHeight="1"/>
+    <row r="303" ht="15.75" customHeight="1"/>
+    <row r="304" ht="15.75" customHeight="1"/>
+    <row r="305" ht="15.75" customHeight="1"/>
+    <row r="306" ht="15.75" customHeight="1"/>
+    <row r="307" ht="15.75" customHeight="1"/>
+    <row r="308" ht="15.75" customHeight="1"/>
+    <row r="309" ht="15.75" customHeight="1"/>
+    <row r="310" ht="15.75" customHeight="1"/>
+    <row r="311" ht="15.75" customHeight="1"/>
+    <row r="312" ht="15.75" customHeight="1"/>
+    <row r="313" ht="15.75" customHeight="1"/>
+    <row r="314" ht="15.75" customHeight="1"/>
+    <row r="315" ht="15.75" customHeight="1"/>
+    <row r="316" ht="15.75" customHeight="1"/>
+    <row r="317" ht="15.75" customHeight="1"/>
+    <row r="318" ht="15.75" customHeight="1"/>
+    <row r="319" ht="15.75" customHeight="1"/>
+    <row r="320" ht="15.75" customHeight="1"/>
+    <row r="321" ht="15.75" customHeight="1"/>
+    <row r="322" ht="15.75" customHeight="1"/>
+    <row r="323" ht="15.75" customHeight="1"/>
+    <row r="324" ht="15.75" customHeight="1"/>
+    <row r="325" ht="15.75" customHeight="1"/>
+    <row r="326" ht="15.75" customHeight="1"/>
+    <row r="327" ht="15.75" customHeight="1"/>
+    <row r="328" ht="15.75" customHeight="1"/>
+    <row r="329" ht="15.75" customHeight="1"/>
+    <row r="330" ht="15.75" customHeight="1"/>
+    <row r="331" ht="15.75" customHeight="1"/>
+    <row r="332" ht="15.75" customHeight="1"/>
+    <row r="333" ht="15.75" customHeight="1"/>
+    <row r="334" ht="15.75" customHeight="1"/>
+    <row r="335" ht="15.75" customHeight="1"/>
+    <row r="336" ht="15.75" customHeight="1"/>
+    <row r="337" ht="15.75" customHeight="1"/>
+    <row r="338" ht="15.75" customHeight="1"/>
+    <row r="339" ht="15.75" customHeight="1"/>
+    <row r="340" ht="15.75" customHeight="1"/>
+    <row r="341" ht="15.75" customHeight="1"/>
+    <row r="342" ht="15.75" customHeight="1"/>
+    <row r="343" ht="15.75" customHeight="1"/>
+    <row r="344" ht="15.75" customHeight="1"/>
+    <row r="345" ht="15.75" customHeight="1"/>
+    <row r="346" ht="15.75" customHeight="1"/>
+    <row r="347" ht="15.75" customHeight="1"/>
+    <row r="348" ht="15.75" customHeight="1"/>
+    <row r="349" ht="15.75" customHeight="1"/>
+    <row r="350" ht="15.75" customHeight="1"/>
+    <row r="351" ht="15.75" customHeight="1"/>
+    <row r="352" ht="15.75" customHeight="1"/>
+    <row r="353" ht="15.75" customHeight="1"/>
+    <row r="354" ht="15.75" customHeight="1"/>
+    <row r="355" ht="15.75" customHeight="1"/>
+    <row r="356" ht="15.75" customHeight="1"/>
+    <row r="357" ht="15.75" customHeight="1"/>
+    <row r="358" ht="15.75" customHeight="1"/>
+    <row r="359" ht="15.75" customHeight="1"/>
+    <row r="360" ht="15.75" customHeight="1"/>
+    <row r="361" ht="15.75" customHeight="1"/>
+    <row r="362" ht="15.75" customHeight="1"/>
+    <row r="363" ht="15.75" customHeight="1"/>
+    <row r="364" ht="15.75" customHeight="1"/>
+    <row r="365" ht="15.75" customHeight="1"/>
+    <row r="366" ht="15.75" customHeight="1"/>
+    <row r="367" ht="15.75" customHeight="1"/>
+    <row r="368" ht="15.75" customHeight="1"/>
+    <row r="369" ht="15.75" customHeight="1"/>
+    <row r="370" ht="15.75" customHeight="1"/>
+    <row r="371" ht="15.75" customHeight="1"/>
+    <row r="372" ht="15.75" customHeight="1"/>
+    <row r="373" ht="15.75" customHeight="1"/>
+    <row r="374" ht="15.75" customHeight="1"/>
+    <row r="375" ht="15.75" customHeight="1"/>
+    <row r="376" ht="15.75" customHeight="1"/>
+    <row r="377" ht="15.75" customHeight="1"/>
+    <row r="378" ht="15.75" customHeight="1"/>
+    <row r="379" ht="15.75" customHeight="1"/>
+    <row r="380" ht="15.75" customHeight="1"/>
+    <row r="381" ht="15.75" customHeight="1"/>
+    <row r="382" ht="15.75" customHeight="1"/>
+    <row r="383" ht="15.75" customHeight="1"/>
+    <row r="384" ht="15.75" customHeight="1"/>
+    <row r="385" ht="15.75" customHeight="1"/>
+    <row r="386" ht="15.75" customHeight="1"/>
+    <row r="387" ht="15.75" customHeight="1"/>
+    <row r="388" ht="15.75" customHeight="1"/>
+    <row r="389" ht="15.75" customHeight="1"/>
+    <row r="390" ht="15.75" customHeight="1"/>
+    <row r="391" ht="15.75" customHeight="1"/>
+    <row r="392" ht="15.75" customHeight="1"/>
+    <row r="393" ht="15.75" customHeight="1"/>
+    <row r="394" ht="15.75" customHeight="1"/>
+    <row r="395" ht="15.75" customHeight="1"/>
+    <row r="396" ht="15.75" customHeight="1"/>
+    <row r="397" ht="15.75" customHeight="1"/>
+    <row r="398" ht="15.75" customHeight="1"/>
+    <row r="399" ht="15.75" customHeight="1"/>
+    <row r="400" ht="15.75" customHeight="1"/>
+    <row r="401" ht="15.75" customHeight="1"/>
+    <row r="402" ht="15.75" customHeight="1"/>
+    <row r="403" ht="15.75" customHeight="1"/>
+    <row r="404" ht="15.75" customHeight="1"/>
+    <row r="405" ht="15.75" customHeight="1"/>
+    <row r="406" ht="15.75" customHeight="1"/>
+    <row r="407" ht="15.75" customHeight="1"/>
+    <row r="408" ht="15.75" customHeight="1"/>
+    <row r="409" ht="15.75" customHeight="1"/>
+    <row r="410" ht="15.75" customHeight="1"/>
+    <row r="411" ht="15.75" customHeight="1"/>
+    <row r="412" ht="15.75" customHeight="1"/>
+    <row r="413" ht="15.75" customHeight="1"/>
+    <row r="414" ht="15.75" customHeight="1"/>
+    <row r="415" ht="15.75" customHeight="1"/>
+    <row r="416" ht="15.75" customHeight="1"/>
+    <row r="417" ht="15.75" customHeight="1"/>
+    <row r="418" ht="15.75" customHeight="1"/>
+    <row r="419" ht="15.75" customHeight="1"/>
+    <row r="420" ht="15.75" customHeight="1"/>
+    <row r="421" ht="15.75" customHeight="1"/>
+    <row r="422" ht="15.75" customHeight="1"/>
+    <row r="423" ht="15.75" customHeight="1"/>
+    <row r="424" ht="15.75" customHeight="1"/>
+    <row r="425" ht="15.75" customHeight="1"/>
+    <row r="426" ht="15.75" customHeight="1"/>
+    <row r="427" ht="15.75" customHeight="1"/>
+    <row r="428" ht="15.75" customHeight="1"/>
+    <row r="429" ht="15.75" customHeight="1"/>
+    <row r="430" ht="15.75" customHeight="1"/>
+    <row r="431" ht="15.75" customHeight="1"/>
+    <row r="432" ht="15.75" customHeight="1"/>
+    <row r="433" ht="15.75" customHeight="1"/>
+    <row r="434" ht="15.75" customHeight="1"/>
+    <row r="435" ht="15.75" customHeight="1"/>
+    <row r="436" ht="15.75" customHeight="1"/>
+    <row r="437" ht="15.75" customHeight="1"/>
+    <row r="438" ht="15.75" customHeight="1"/>
+    <row r="439" ht="15.75" customHeight="1"/>
+    <row r="440" ht="15.75" customHeight="1"/>
+    <row r="441" ht="15.75" customHeight="1"/>
+    <row r="442" ht="15.75" customHeight="1"/>
+    <row r="443" ht="15.75" customHeight="1"/>
+    <row r="444" ht="15.75" customHeight="1"/>
+    <row r="445" ht="15.75" customHeight="1"/>
+    <row r="446" ht="15.75" customHeight="1"/>
+    <row r="447" ht="15.75" customHeight="1"/>
+    <row r="448" ht="15.75" customHeight="1"/>
+    <row r="449" ht="15.75" customHeight="1"/>
+    <row r="450" ht="15.75" customHeight="1"/>
+    <row r="451" ht="15.75" customHeight="1"/>
+    <row r="452" ht="15.75" customHeight="1"/>
+    <row r="453" ht="15.75" customHeight="1"/>
+    <row r="454" ht="15.75" customHeight="1"/>
+    <row r="455" ht="15.75" customHeight="1"/>
+    <row r="456" ht="15.75" customHeight="1"/>
+    <row r="457" ht="15.75" customHeight="1"/>
+    <row r="458" ht="15.75" customHeight="1"/>
+    <row r="459" ht="15.75" customHeight="1"/>
+    <row r="460" ht="15.75" customHeight="1"/>
+    <row r="461" ht="15.75" customHeight="1"/>
+    <row r="462" ht="15.75" customHeight="1"/>
+    <row r="463" ht="15.75" customHeight="1"/>
+    <row r="464" ht="15.75" customHeight="1"/>
+    <row r="465" ht="15.75" customHeight="1"/>
+    <row r="466" ht="15.75" customHeight="1"/>
+    <row r="467" ht="15.75" customHeight="1"/>
+    <row r="468" ht="15.75" customHeight="1"/>
+    <row r="469" ht="15.75" customHeight="1"/>
+    <row r="470" ht="15.75" customHeight="1"/>
+    <row r="471" ht="15.75" customHeight="1"/>
+    <row r="472" ht="15.75" customHeight="1"/>
+    <row r="473" ht="15.75" customHeight="1"/>
+    <row r="474" ht="15.75" customHeight="1"/>
+    <row r="475" ht="15.75" customHeight="1"/>
+    <row r="476" ht="15.75" customHeight="1"/>
+    <row r="477" ht="15.75" customHeight="1"/>
+    <row r="478" ht="15.75" customHeight="1"/>
+    <row r="479" ht="15.75" customHeight="1"/>
+    <row r="480" ht="15.75" customHeight="1"/>
+    <row r="481" ht="15.75" customHeight="1"/>
+    <row r="482" ht="15.75" customHeight="1"/>
+    <row r="483" ht="15.75" customHeight="1"/>
+    <row r="484" ht="15.75" customHeight="1"/>
+    <row r="485" ht="15.75" customHeight="1"/>
+    <row r="486" ht="15.75" customHeight="1"/>
+    <row r="487" ht="15.75" customHeight="1"/>
+    <row r="488" ht="15.75" customHeight="1"/>
+    <row r="489" ht="15.75" customHeight="1"/>
+    <row r="490" ht="15.75" customHeight="1"/>
+    <row r="491" ht="15.75" customHeight="1"/>
+    <row r="492" ht="15.75" customHeight="1"/>
+    <row r="493" ht="15.75" customHeight="1"/>
+    <row r="494" ht="15.75" customHeight="1"/>
+    <row r="495" ht="15.75" customHeight="1"/>
+    <row r="496" ht="15.75" customHeight="1"/>
+    <row r="497" ht="15.75" customHeight="1"/>
+    <row r="498" ht="15.75" customHeight="1"/>
+    <row r="499" ht="15.75" customHeight="1"/>
+    <row r="500" ht="15.75" customHeight="1"/>
+    <row r="501" ht="15.75" customHeight="1"/>
+    <row r="502" ht="15.75" customHeight="1"/>
+    <row r="503" ht="15.75" customHeight="1"/>
+    <row r="504" ht="15.75" customHeight="1"/>
+    <row r="505" ht="15.75" customHeight="1"/>
+    <row r="506" ht="15.75" customHeight="1"/>
+    <row r="507" ht="15.75" customHeight="1"/>
+    <row r="508" ht="15.75" customHeight="1"/>
+    <row r="509" ht="15.75" customHeight="1"/>
+    <row r="510" ht="15.75" customHeight="1"/>
+    <row r="511" ht="15.75" customHeight="1"/>
+    <row r="512" ht="15.75" customHeight="1"/>
+    <row r="513" ht="15.75" customHeight="1"/>
+    <row r="514" ht="15.75" customHeight="1"/>
+    <row r="515" ht="15.75" customHeight="1"/>
+    <row r="516" ht="15.75" customHeight="1"/>
+    <row r="517" ht="15.75" customHeight="1"/>
+    <row r="518" ht="15.75" customHeight="1"/>
+    <row r="519" ht="15.75" customHeight="1"/>
+    <row r="520" ht="15.75" customHeight="1"/>
+    <row r="521" ht="15.75" customHeight="1"/>
+    <row r="522" ht="15.75" customHeight="1"/>
+    <row r="523" ht="15.75" customHeight="1"/>
+    <row r="524" ht="15.75" customHeight="1"/>
+    <row r="525" ht="15.75" customHeight="1"/>
+    <row r="526" ht="15.75" customHeight="1"/>
+    <row r="527" ht="15.75" customHeight="1"/>
+    <row r="528" ht="15.75" customHeight="1"/>
+    <row r="529" ht="15.75" customHeight="1"/>
+    <row r="530" ht="15.75" customHeight="1"/>
+    <row r="531" ht="15.75" customHeight="1"/>
+    <row r="532" ht="15.75" customHeight="1"/>
+    <row r="533" ht="15.75" customHeight="1"/>
+    <row r="534" ht="15.75" customHeight="1"/>
+    <row r="535" ht="15.75" customHeight="1"/>
+    <row r="536" ht="15.75" customHeight="1"/>
+    <row r="537" ht="15.75" customHeight="1"/>
+    <row r="538" ht="15.75" customHeight="1"/>
+    <row r="539" ht="15.75" customHeight="1"/>
+    <row r="540" ht="15.75" customHeight="1"/>
+    <row r="541" ht="15.75" customHeight="1"/>
+    <row r="542" ht="15.75" customHeight="1"/>
+    <row r="543" ht="15.75" customHeight="1"/>
+    <row r="544" ht="15.75" customHeight="1"/>
+    <row r="545" ht="15.75" customHeight="1"/>
+    <row r="546" ht="15.75" customHeight="1"/>
+    <row r="547" ht="15.75" customHeight="1"/>
+    <row r="548" ht="15.75" customHeight="1"/>
+    <row r="549" ht="15.75" customHeight="1"/>
+    <row r="550" ht="15.75" customHeight="1"/>
+    <row r="551" ht="15.75" customHeight="1"/>
+    <row r="552" ht="15.75" customHeight="1"/>
+    <row r="553" ht="15.75" customHeight="1"/>
+    <row r="554" ht="15.75" customHeight="1"/>
+    <row r="555" ht="15.75" customHeight="1"/>
+    <row r="556" ht="15.75" customHeight="1"/>
+    <row r="557" ht="15.75" customHeight="1"/>
+    <row r="558" ht="15.75" customHeight="1"/>
+    <row r="559" ht="15.75" customHeight="1"/>
+    <row r="560" ht="15.75" customHeight="1"/>
+    <row r="561" ht="15.75" customHeight="1"/>
+    <row r="562" ht="15.75" customHeight="1"/>
+    <row r="563" ht="15.75" customHeight="1"/>
+    <row r="564" ht="15.75" customHeight="1"/>
+    <row r="565" ht="15.75" customHeight="1"/>
+    <row r="566" ht="15.75" customHeight="1"/>
+    <row r="567" ht="15.75" customHeight="1"/>
+    <row r="568" ht="15.75" customHeight="1"/>
+    <row r="569" ht="15.75" customHeight="1"/>
+    <row r="570" ht="15.75" customHeight="1"/>
+    <row r="571" ht="15.75" customHeight="1"/>
+    <row r="572" ht="15.75" customHeight="1"/>
+    <row r="573" ht="15.75" customHeight="1"/>
+    <row r="574" ht="15.75" customHeight="1"/>
+    <row r="575" ht="15.75" customHeight="1"/>
+    <row r="576" ht="15.75" customHeight="1"/>
+    <row r="577" ht="15.75" customHeight="1"/>
+    <row r="578" ht="15.75" customHeight="1"/>
+    <row r="579" ht="15.75" customHeight="1"/>
+    <row r="580" ht="15.75" customHeight="1"/>
+    <row r="581" ht="15.75" customHeight="1"/>
+    <row r="582" ht="15.75" customHeight="1"/>
+    <row r="583" ht="15.75" customHeight="1"/>
+    <row r="584" ht="15.75" customHeight="1"/>
+    <row r="585" ht="15.75" customHeight="1"/>
+    <row r="586" ht="15.75" customHeight="1"/>
+    <row r="587" ht="15.75" customHeight="1"/>
+    <row r="588" ht="15.75" customHeight="1"/>
+    <row r="589" ht="15.75" customHeight="1"/>
+    <row r="590" ht="15.75" customHeight="1"/>
+    <row r="591" ht="15.75" customHeight="1"/>
+    <row r="592" ht="15.75" customHeight="1"/>
+    <row r="593" ht="15.75" customHeight="1"/>
+    <row r="594" ht="15.75" customHeight="1"/>
+    <row r="595" ht="15.75" customHeight="1"/>
+    <row r="596" ht="15.75" customHeight="1"/>
+    <row r="597" ht="15.75" customHeight="1"/>
+    <row r="598" ht="15.75" customHeight="1"/>
+    <row r="599" ht="15.75" customHeight="1"/>
+    <row r="600" ht="15.75" customHeight="1"/>
+    <row r="601" ht="15.75" customHeight="1"/>
+    <row r="602" ht="15.75" customHeight="1"/>
+    <row r="603" ht="15.75" customHeight="1"/>
+    <row r="604" ht="15.75" customHeight="1"/>
+    <row r="605" ht="15.75" customHeight="1"/>
+    <row r="606" ht="15.75" customHeight="1"/>
+    <row r="607" ht="15.75" customHeight="1"/>
+    <row r="608" ht="15.75" customHeight="1"/>
+    <row r="609" ht="15.75" customHeight="1"/>
+    <row r="610" ht="15.75" customHeight="1"/>
+    <row r="611" ht="15.75" customHeight="1"/>
+    <row r="612" ht="15.75" customHeight="1"/>
+    <row r="613" ht="15.75" customHeight="1"/>
+    <row r="614" ht="15.75" customHeight="1"/>
+    <row r="615" ht="15.75" customHeight="1"/>
+    <row r="616" ht="15.75" customHeight="1"/>
+    <row r="617" ht="15.75" customHeight="1"/>
+    <row r="618" ht="15.75" customHeight="1"/>
+    <row r="619" ht="15.75" customHeight="1"/>
+    <row r="620" ht="15.75" customHeight="1"/>
+    <row r="621" ht="15.75" customHeight="1"/>
+    <row r="622" ht="15.75" customHeight="1"/>
+    <row r="623" ht="15.75" customHeight="1"/>
+    <row r="624" ht="15.75" customHeight="1"/>
+    <row r="625" ht="15.75" customHeight="1"/>
+    <row r="626" ht="15.75" customHeight="1"/>
+    <row r="627" ht="15.75" customHeight="1"/>
+    <row r="628" ht="15.75" customHeight="1"/>
+    <row r="629" ht="15.75" customHeight="1"/>
+    <row r="630" ht="15.75" customHeight="1"/>
+    <row r="631" ht="15.75" customHeight="1"/>
+    <row r="632" ht="15.75" customHeight="1"/>
+    <row r="633" ht="15.75" customHeight="1"/>
+    <row r="634" ht="15.75" customHeight="1"/>
+    <row r="635" ht="15.75" customHeight="1"/>
+    <row r="636" ht="15.75" customHeight="1"/>
+    <row r="637" ht="15.75" customHeight="1"/>
+    <row r="638" ht="15.75" customHeight="1"/>
+    <row r="639" ht="15.75" customHeight="1"/>
+    <row r="640" ht="15.75" customHeight="1"/>
+    <row r="641" ht="15.75" customHeight="1"/>
+    <row r="642" ht="15.75" customHeight="1"/>
+    <row r="643" ht="15.75" customHeight="1"/>
+    <row r="644" ht="15.75" customHeight="1"/>
+    <row r="645" ht="15.75" customHeight="1"/>
+    <row r="646" ht="15.75" customHeight="1"/>
+    <row r="647" ht="15.75" customHeight="1"/>
+    <row r="648" ht="15.75" customHeight="1"/>
+    <row r="649" ht="15.75" customHeight="1"/>
+    <row r="650" ht="15.75" customHeight="1"/>
+    <row r="651" ht="15.75" customHeight="1"/>
+    <row r="652" ht="15.75" customHeight="1"/>
+    <row r="653" ht="15.75" customHeight="1"/>
+    <row r="654" ht="15.75" customHeight="1"/>
+    <row r="655" ht="15.75" customHeight="1"/>
+    <row r="656" ht="15.75" customHeight="1"/>
+    <row r="657" ht="15.75" customHeight="1"/>
+    <row r="658" ht="15.75" customHeight="1"/>
+    <row r="659" ht="15.75" customHeight="1"/>
+    <row r="660" ht="15.75" customHeight="1"/>
+    <row r="661" ht="15.75" customHeight="1"/>
+    <row r="662" ht="15.75" customHeight="1"/>
+    <row r="663" ht="15.75" customHeight="1"/>
+    <row r="664" ht="15.75" customHeight="1"/>
+    <row r="665" ht="15.75" customHeight="1"/>
+    <row r="666" ht="15.75" customHeight="1"/>
+    <row r="667" ht="15.75" customHeight="1"/>
+    <row r="668" ht="15.75" customHeight="1"/>
+    <row r="669" ht="15.75" customHeight="1"/>
+    <row r="670" ht="15.75" customHeight="1"/>
+    <row r="671" ht="15.75" customHeight="1"/>
+    <row r="672" ht="15.75" customHeight="1"/>
+    <row r="673" ht="15.75" customHeight="1"/>
+    <row r="674" ht="15.75" customHeight="1"/>
+    <row r="675" ht="15.75" customHeight="1"/>
+    <row r="676" ht="15.75" customHeight="1"/>
+    <row r="677" ht="15.75" customHeight="1"/>
+    <row r="678" ht="15.75" customHeight="1"/>
+    <row r="679" ht="15.75" customHeight="1"/>
+    <row r="680" ht="15.75" customHeight="1"/>
+    <row r="681" ht="15.75" customHeight="1"/>
+    <row r="682" ht="15.75" customHeight="1"/>
+    <row r="683" ht="15.75" customHeight="1"/>
+    <row r="684" ht="15.75" customHeight="1"/>
+    <row r="685" ht="15.75" customHeight="1"/>
+    <row r="686" ht="15.75" customHeight="1"/>
+    <row r="687" ht="15.75" customHeight="1"/>
+    <row r="688" ht="15.75" customHeight="1"/>
+    <row r="689" ht="15.75" customHeight="1"/>
+    <row r="690" ht="15.75" customHeight="1"/>
+    <row r="691" ht="15.75" customHeight="1"/>
+    <row r="692" ht="15.75" customHeight="1"/>
+    <row r="693" ht="15.75" customHeight="1"/>
+    <row r="694" ht="15.75" customHeight="1"/>
+    <row r="695" ht="15.75" customHeight="1"/>
+    <row r="696" ht="15.75" customHeight="1"/>
+    <row r="697" ht="15.75" customHeight="1"/>
+    <row r="698" ht="15.75" customHeight="1"/>
+    <row r="699" ht="15.75" customHeight="1"/>
+    <row r="700" ht="15.75" customHeight="1"/>
+    <row r="701" ht="15.75" customHeight="1"/>
+    <row r="702" ht="15.75" customHeight="1"/>
+    <row r="703" ht="15.75" customHeight="1"/>
+    <row r="704" ht="15.75" customHeight="1"/>
+    <row r="705" ht="15.75" customHeight="1"/>
+    <row r="706" ht="15.75" customHeight="1"/>
+    <row r="707" ht="15.75" customHeight="1"/>
+    <row r="708" ht="15.75" customHeight="1"/>
+    <row r="709" ht="15.75" customHeight="1"/>
+    <row r="710" ht="15.75" customHeight="1"/>
+    <row r="711" ht="15.75" customHeight="1"/>
+    <row r="712" ht="15.75" customHeight="1"/>
+    <row r="713" ht="15.75" customHeight="1"/>
+    <row r="714" ht="15.75" customHeight="1"/>
+    <row r="715" ht="15.75" customHeight="1"/>
+    <row r="716" ht="15.75" customHeight="1"/>
+    <row r="717" ht="15.75" customHeight="1"/>
+    <row r="718" ht="15.75" customHeight="1"/>
+    <row r="719" ht="15.75" customHeight="1"/>
+    <row r="720" ht="15.75" customHeight="1"/>
+    <row r="721" ht="15.75" customHeight="1"/>
+    <row r="722" ht="15.75" customHeight="1"/>
+    <row r="723" ht="15.75" customHeight="1"/>
+    <row r="724" ht="15.75" customHeight="1"/>
+    <row r="725" ht="15.75" customHeight="1"/>
+    <row r="726" ht="15.75" customHeight="1"/>
+    <row r="727" ht="15.75" customHeight="1"/>
+    <row r="728" ht="15.75" customHeight="1"/>
+    <row r="729" ht="15.75" customHeight="1"/>
+    <row r="730" ht="15.75" customHeight="1"/>
+    <row r="731" ht="15.75" customHeight="1"/>
+    <row r="732" ht="15.75" customHeight="1"/>
+    <row r="733" ht="15.75" customHeight="1"/>
+    <row r="734" ht="15.75" customHeight="1"/>
+    <row r="735" ht="15.75" customHeight="1"/>
+    <row r="736" ht="15.75" customHeight="1"/>
+    <row r="737" ht="15.75" customHeight="1"/>
+    <row r="738" ht="15.75" customHeight="1"/>
+    <row r="739" ht="15.75" customHeight="1"/>
+    <row r="740" ht="15.75" customHeight="1"/>
+    <row r="741" ht="15.75" customHeight="1"/>
+    <row r="742" ht="15.75" customHeight="1"/>
+    <row r="743" ht="15.75" customHeight="1"/>
+    <row r="744" ht="15.75" customHeight="1"/>
+    <row r="745" ht="15.75" customHeight="1"/>
+    <row r="746" ht="15.75" customHeight="1"/>
+    <row r="747" ht="15.75" customHeight="1"/>
+    <row r="748" ht="15.75" customHeight="1"/>
+    <row r="749" ht="15.75" customHeight="1"/>
+    <row r="750" ht="15.75" customHeight="1"/>
+    <row r="751" ht="15.75" customHeight="1"/>
+    <row r="752" ht="15.75" customHeight="1"/>
+    <row r="753" ht="15.75" customHeight="1"/>
+    <row r="754" ht="15.75" customHeight="1"/>
+    <row r="755" ht="15.75" customHeight="1"/>
+    <row r="756" ht="15.75" customHeight="1"/>
+    <row r="757" ht="15.75" customHeight="1"/>
+    <row r="758" ht="15.75" customHeight="1"/>
+    <row r="759" ht="15.75" customHeight="1"/>
+    <row r="760" ht="15.75" customHeight="1"/>
+    <row r="761" ht="15.75" customHeight="1"/>
+    <row r="762" ht="15.75" customHeight="1"/>
+    <row r="763" ht="15.75" customHeight="1"/>
+    <row r="764" ht="15.75" customHeight="1"/>
+    <row r="765" ht="15.75" customHeight="1"/>
+    <row r="766" ht="15.75" customHeight="1"/>
+    <row r="767" ht="15.75" customHeight="1"/>
+    <row r="768" ht="15.75" customHeight="1"/>
+    <row r="769" ht="15.75" customHeight="1"/>
+    <row r="770" ht="15.75" customHeight="1"/>
+    <row r="771" ht="15.75" customHeight="1"/>
+    <row r="772" ht="15.75" customHeight="1"/>
+    <row r="773" ht="15.75" customHeight="1"/>
+    <row r="774" ht="15.75" customHeight="1"/>
+    <row r="775" ht="15.75" customHeight="1"/>
+    <row r="776" ht="15.75" customHeight="1"/>
+    <row r="777" ht="15.75" customHeight="1"/>
+    <row r="778" ht="15.75" customHeight="1"/>
+    <row r="779" ht="15.75" customHeight="1"/>
+    <row r="780" ht="15.75" customHeight="1"/>
+    <row r="781" ht="15.75" customHeight="1"/>
+    <row r="782" ht="15.75" customHeight="1"/>
+    <row r="783" ht="15.75" customHeight="1"/>
+    <row r="784" ht="15.75" customHeight="1"/>
+    <row r="785" ht="15.75" customHeight="1"/>
+    <row r="786" ht="15.75" customHeight="1"/>
+    <row r="787" ht="15.75" customHeight="1"/>
+    <row r="788" ht="15.75" customHeight="1"/>
+    <row r="789" ht="15.75" customHeight="1"/>
+    <row r="790" ht="15.75" customHeight="1"/>
+    <row r="791" ht="15.75" customHeight="1"/>
+    <row r="792" ht="15.75" customHeight="1"/>
+    <row r="793" ht="15.75" customHeight="1"/>
+    <row r="794" ht="15.75" customHeight="1"/>
+    <row r="795" ht="15.75" customHeight="1"/>
+    <row r="796" ht="15.75" customHeight="1"/>
+    <row r="797" ht="15.75" customHeight="1"/>
+    <row r="798" ht="15.75" customHeight="1"/>
+    <row r="799" ht="15.75" customHeight="1"/>
+    <row r="800" ht="15.75" customHeight="1"/>
+    <row r="801" ht="15.75" customHeight="1"/>
+    <row r="802" ht="15.75" customHeight="1"/>
+    <row r="803" ht="15.75" customHeight="1"/>
+    <row r="804" ht="15.75" customHeight="1"/>
+    <row r="805" ht="15.75" customHeight="1"/>
+    <row r="806" ht="15.75" customHeight="1"/>
+    <row r="807" ht="15.75" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="G4:Q11 G13:Q16 G23:Q25">
@@ -16038,16 +16027,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:U118"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="6.1640625" customWidth="1"/>
+    <col min="1" max="1" width="6.1328125" customWidth="1"/>
     <col min="2" max="9" width="20.6640625" customWidth="1"/>
-    <col min="10" max="11" width="11.1640625" customWidth="1"/>
+    <col min="10" max="11" width="11.1328125" customWidth="1"/>
     <col min="12" max="12" width="20.6640625" customWidth="1"/>
     <col min="13" max="13" width="5.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:15" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:15" ht="13.9">
       <c r="B2" s="34" t="s">
         <v>52</v>
       </c>
@@ -16062,7 +16051,7 @@
       <c r="K2" s="35"/>
       <c r="L2" s="35"/>
     </row>
-    <row r="3" spans="2:15" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:15" ht="13.15">
       <c r="B3" s="106" t="s">
         <v>136</v>
       </c>
@@ -16077,7 +16066,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="4" spans="2:15" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:15">
       <c r="B4" s="97" t="s">
         <v>393</v>
       </c>
@@ -16109,7 +16098,7 @@
       </c>
       <c r="J4" s="305"/>
     </row>
-    <row r="5" spans="2:15" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:15">
       <c r="B5" s="187" t="s">
         <v>105</v>
       </c>
@@ -16137,7 +16126,7 @@
       </c>
       <c r="J5" s="305"/>
     </row>
-    <row r="6" spans="2:15" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:15" ht="13.25" customHeight="1">
       <c r="B6" s="136" t="s">
         <v>194</v>
       </c>
@@ -16170,7 +16159,7 @@
       <c r="J6" s="305"/>
       <c r="N6" s="135"/>
     </row>
-    <row r="7" spans="2:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:15" ht="12.75" customHeight="1">
       <c r="B7" s="318" t="s">
         <v>430</v>
       </c>
@@ -16200,7 +16189,7 @@
       <c r="N7" s="304"/>
       <c r="O7" s="304"/>
     </row>
-    <row r="8" spans="2:15" ht="14" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:15" ht="13.15">
       <c r="B8" s="136" t="s">
         <v>426</v>
       </c>
@@ -16217,7 +16206,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>7.502223151381795</v>
+        <v>7.5479008441329798</v>
       </c>
       <c r="G8" s="294" t="str">
         <f>Market_currency</f>
@@ -16235,14 +16224,14 @@
       <c r="N8" s="304"/>
       <c r="O8" s="304"/>
     </row>
-    <row r="9" spans="2:15" ht="14" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:15" ht="13.15" thickBot="1">
       <c r="B9" s="189" t="str">
         <f>"*"&amp;Thesis!E15</f>
         <v>*CNY/HKD</v>
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>1.1200000000000001</v>
+        <v>1.1268191807746888</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16261,13 +16250,13 @@
       <c r="N9" s="304"/>
       <c r="O9" s="304"/>
     </row>
-    <row r="10" spans="2:15" ht="14" thickTop="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:15" ht="13.5" thickTop="1">
       <c r="B10" s="107" t="s">
         <v>427</v>
       </c>
       <c r="C10" s="283">
         <f>C8*Exchange_Rate</f>
-        <v>202924.76974680435</v>
+        <v>204160.28821873784</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16283,13 +16272,13 @@
       <c r="N10" s="304"/>
       <c r="O10" s="304"/>
     </row>
-    <row r="11" spans="2:15" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:15" ht="13.15">
       <c r="B11" s="136" t="s">
         <v>425</v>
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>73.2448294520552</v>
+        <v>73.690784570666622</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16299,7 +16288,7 @@
       <c r="I11" s="307"/>
       <c r="J11" s="307"/>
     </row>
-    <row r="13" spans="2:15" ht="16" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:15" ht="13.9">
       <c r="B13" s="34" t="s">
         <v>428</v>
       </c>
@@ -16314,7 +16303,7 @@
       <c r="K13" s="35"/>
       <c r="L13" s="35"/>
     </row>
-    <row r="14" spans="2:15" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:15" ht="13.15">
       <c r="B14" s="106" t="s">
         <v>399</v>
       </c>
@@ -16332,7 +16321,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="15" spans="2:15" x14ac:dyDescent="0.15">
+    <row r="15" spans="2:15">
       <c r="B15" s="139" t="s">
         <v>421</v>
       </c>
@@ -16357,7 +16346,7 @@
       </c>
       <c r="J15" s="126"/>
     </row>
-    <row r="16" spans="2:15" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:15" ht="13.25" customHeight="1">
       <c r="B16" s="114" t="s">
         <v>422</v>
       </c>
@@ -16373,7 +16362,7 @@
         <v>4.5189945606143193E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:21" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:21" ht="13.25" customHeight="1">
       <c r="B17" s="308" t="s">
         <v>549</v>
       </c>
@@ -16392,7 +16381,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="18" spans="1:21" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:21" ht="13.25" customHeight="1">
       <c r="B18" s="308" t="s">
         <v>423</v>
       </c>
@@ -16412,17 +16401,17 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>85.747183560275744</v>
+        <v>86.269259940291761</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:21">
       <c r="L19" s="275"/>
     </row>
-    <row r="20" spans="1:21" ht="14" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:21" ht="13.15">
       <c r="A20" s="121" t="s">
         <v>399</v>
       </c>
@@ -16461,7 +16450,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:21">
       <c r="A21" s="302" t="str">
         <f t="shared" ref="A21:A50" si="0">IF($C$15&lt;B21,"",IF(B21&gt;=$F$15,"II","I"))</f>
         <v>I</v>
@@ -16510,7 +16499,7 @@
         <v>8157.2549933715836</v>
       </c>
     </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:21">
       <c r="A22" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -16559,7 +16548,7 @@
         <v>7949.5393033263272</v>
       </c>
     </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:21">
       <c r="A23" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -16616,7 +16605,7 @@
       <c r="T23" s="275"/>
       <c r="U23" s="275"/>
     </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:21">
       <c r="A24" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -16673,7 +16662,7 @@
       <c r="T24" s="275"/>
       <c r="U24" s="275"/>
     </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:21">
       <c r="A25" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -16730,7 +16719,7 @@
       <c r="T25" s="275"/>
       <c r="U25" s="275"/>
     </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:21">
       <c r="A26" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -16779,7 +16768,7 @@
         <v>7170.239309531351</v>
       </c>
     </row>
-    <row r="27" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:21">
       <c r="A27" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -16828,7 +16817,7 @@
         <v>6987.6569080765539</v>
       </c>
     </row>
-    <row r="28" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:21">
       <c r="A28" s="302" t="str">
         <f t="shared" si="0"/>
         <v>II</v>
@@ -16877,7 +16866,7 @@
         <v>7375.6702045582388</v>
       </c>
     </row>
-    <row r="29" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:21">
       <c r="A29" s="302" t="str">
         <f t="shared" si="0"/>
         <v>II</v>
@@ -16926,7 +16915,7 @@
         <v>7187.8567271898155</v>
       </c>
     </row>
-    <row r="30" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:21">
       <c r="A30" s="302" t="str">
         <f t="shared" si="0"/>
         <v>II</v>
@@ -16975,7 +16964,7 @@
         <v>7004.8257172179692</v>
       </c>
     </row>
-    <row r="31" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:21">
       <c r="A31" s="302" t="str">
         <f t="shared" si="0"/>
         <v>II</v>
@@ -17024,7 +17013,7 @@
         <v>6826.4553942746488</v>
       </c>
     </row>
-    <row r="32" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:21">
       <c r="A32" s="302" t="str">
         <f t="shared" si="0"/>
         <v>II</v>
@@ -17073,7 +17062,7 @@
         <v>6652.6270789973723</v>
       </c>
     </row>
-    <row r="33" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:21">
       <c r="A33" s="302" t="str">
         <f t="shared" si="0"/>
         <v>II</v>
@@ -17130,7 +17119,7 @@
       <c r="T33" s="275"/>
       <c r="U33" s="275"/>
     </row>
-    <row r="34" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:21">
       <c r="A34" s="302" t="str">
         <f t="shared" si="0"/>
         <v>II</v>
@@ -17187,7 +17176,7 @@
       <c r="T34" s="275"/>
       <c r="U34" s="275"/>
     </row>
-    <row r="35" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:21">
       <c r="A35" s="302" t="str">
         <f t="shared" si="0"/>
         <v>II</v>
@@ -17244,7 +17233,7 @@
       <c r="T35" s="275"/>
       <c r="U35" s="275"/>
     </row>
-    <row r="36" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:21">
       <c r="A36" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17293,7 +17282,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:21">
       <c r="A37" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17342,7 +17331,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:21">
       <c r="A38" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17391,7 +17380,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:21">
       <c r="A39" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17440,7 +17429,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:21">
       <c r="A40" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17489,7 +17478,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:21">
       <c r="A41" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17538,7 +17527,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:21">
       <c r="A42" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17587,7 +17576,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:21">
       <c r="A43" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17636,7 +17625,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:21">
       <c r="A44" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17685,7 +17674,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:21">
       <c r="A45" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17734,7 +17723,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:21">
       <c r="A46" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17783,7 +17772,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:21">
       <c r="A47" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17840,7 +17829,7 @@
       <c r="T47" s="275"/>
       <c r="U47" s="275"/>
     </row>
-    <row r="48" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:21">
       <c r="A48" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17897,7 +17886,7 @@
       <c r="T48" s="275"/>
       <c r="U48" s="275"/>
     </row>
-    <row r="49" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:21">
       <c r="A49" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17954,7 +17943,7 @@
       <c r="T49" s="275"/>
       <c r="U49" s="275"/>
     </row>
-    <row r="50" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:21">
       <c r="A50" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -18011,7 +18000,7 @@
       <c r="T50" s="275"/>
       <c r="U50" s="275"/>
     </row>
-    <row r="51" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:21">
       <c r="A51" s="315" t="s">
         <v>418</v>
       </c>
@@ -18057,7 +18046,7 @@
         <v>86626.169676326026</v>
       </c>
     </row>
-    <row r="52" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:21" ht="13.15">
       <c r="G52" s="111"/>
       <c r="H52" s="111"/>
       <c r="I52" s="111"/>
@@ -18070,10 +18059,10 @@
         <v>193551.45580149288</v>
       </c>
     </row>
-    <row r="53" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:21">
       <c r="C53" s="111"/>
     </row>
-    <row r="54" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:21" ht="13.15">
       <c r="B54" s="115" t="s">
         <v>108</v>
       </c>
@@ -18088,7 +18077,7 @@
       <c r="K54" s="113"/>
       <c r="L54" s="113"/>
     </row>
-    <row r="55" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:21" ht="13.15">
       <c r="A55" s="125">
         <f>L52</f>
         <v>193551.45580149288</v>
@@ -18120,7 +18109,7 @@
       <c r="K55" s="123"/>
       <c r="L55" s="123"/>
     </row>
-    <row r="56" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:21" ht="13.15">
       <c r="A56" s="131">
         <v>1</v>
       </c>
@@ -18147,7 +18136,7 @@
       <c r="K56" s="295"/>
       <c r="L56" s="295"/>
     </row>
-    <row r="57" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:21" ht="13.15">
       <c r="A57" s="131">
         <v>2</v>
       </c>
@@ -18173,7 +18162,7 @@
       <c r="K57" s="295"/>
       <c r="L57" s="295"/>
     </row>
-    <row r="58" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:21" ht="13.15">
       <c r="A58" s="131">
         <v>3</v>
       </c>
@@ -18187,7 +18176,7 @@
         <v>137410.48563829702</v>
       </c>
       <c r="E58" s="118">
-        <v>145081.34778975247</v>
+        <v>145081.34778975241</v>
       </c>
       <c r="F58" s="118">
         <v>165518.64009880446</v>
@@ -18199,7 +18188,7 @@
       <c r="K58" s="295"/>
       <c r="L58" s="295"/>
     </row>
-    <row r="59" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:21" ht="13.15">
       <c r="A59" s="131">
         <v>4</v>
       </c>
@@ -18225,7 +18214,7 @@
       <c r="K59" s="295"/>
       <c r="L59" s="295"/>
     </row>
-    <row r="60" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:21" ht="13.15">
       <c r="A60" s="131">
         <v>5</v>
       </c>
@@ -18251,7 +18240,7 @@
       <c r="K60" s="295"/>
       <c r="L60" s="295"/>
     </row>
-    <row r="61" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:21" ht="13.15">
       <c r="A61" s="131">
         <v>6</v>
       </c>
@@ -18277,7 +18266,7 @@
       <c r="K61" s="295"/>
       <c r="L61" s="295"/>
     </row>
-    <row r="62" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:21" ht="13.15">
       <c r="A62" s="131">
         <v>7</v>
       </c>
@@ -18303,7 +18292,7 @@
       <c r="K62" s="295"/>
       <c r="L62" s="295"/>
     </row>
-    <row r="63" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:21" ht="13.15">
       <c r="A63" s="131">
         <v>8</v>
       </c>
@@ -18329,7 +18318,7 @@
       <c r="K63" s="295"/>
       <c r="L63" s="295"/>
     </row>
-    <row r="64" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:21" ht="13.15">
       <c r="A64" s="131">
         <v>9</v>
       </c>
@@ -18355,7 +18344,7 @@
       <c r="K64" s="295"/>
       <c r="L64" s="295"/>
     </row>
-    <row r="65" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:21" ht="13.15">
       <c r="A65" s="131">
         <v>10</v>
       </c>
@@ -18381,7 +18370,7 @@
       <c r="K65" s="295"/>
       <c r="L65" s="295"/>
     </row>
-    <row r="66" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:21" ht="13.15">
       <c r="A66" s="131">
         <v>15</v>
       </c>
@@ -18416,7 +18405,7 @@
       <c r="T66" s="275"/>
       <c r="U66" s="275"/>
     </row>
-    <row r="67" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:21" ht="13.15">
       <c r="A67" s="132">
         <v>20</v>
       </c>
@@ -18451,7 +18440,7 @@
       <c r="T67" s="275"/>
       <c r="U67" s="275"/>
     </row>
-    <row r="68" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:21" ht="13.15">
       <c r="A68" s="132">
         <v>25</v>
       </c>
@@ -18486,7 +18475,7 @@
       <c r="T68" s="275"/>
       <c r="U68" s="275"/>
     </row>
-    <row r="69" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:21" ht="13.15">
       <c r="A69" s="132">
         <v>30</v>
       </c>
@@ -18521,7 +18510,7 @@
       <c r="T69" s="275"/>
       <c r="U69" s="275"/>
     </row>
-    <row r="70" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:21">
       <c r="C70" s="275"/>
       <c r="D70" s="111"/>
       <c r="E70" s="111"/>
@@ -18542,7 +18531,7 @@
       <c r="T70" s="275"/>
       <c r="U70" s="275"/>
     </row>
-    <row r="71" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:21" ht="13.15">
       <c r="B71" s="115" t="s">
         <v>109</v>
       </c>
@@ -18566,7 +18555,7 @@
       <c r="T71" s="275"/>
       <c r="U71" s="275"/>
     </row>
-    <row r="72" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:21" ht="13.15">
       <c r="B72" s="124">
         <f>B55</f>
         <v>0</v>
@@ -18594,29 +18583,29 @@
       <c r="K72" s="124"/>
       <c r="L72" s="124"/>
     </row>
-    <row r="73" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:21" ht="13.15">
       <c r="A73" s="131">
         <v>0</v>
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>73.2448294520552</v>
+        <v>73.690784570666622</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>73.2448294520552</v>
+        <v>73.690784570666622</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>73.2448294520552</v>
+        <v>73.690784570666622</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>73.2448294520552</v>
+        <v>73.690784570666622</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>73.2448294520552</v>
+        <v>73.690784570666622</v>
       </c>
       <c r="G73" s="296"/>
       <c r="H73" s="296"/>
@@ -18625,29 +18614,29 @@
       <c r="K73" s="296"/>
       <c r="L73" s="296"/>
     </row>
-    <row r="74" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:21" ht="13.15">
       <c r="A74" s="131">
         <v>1</v>
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>58.734905418083464</v>
+        <v>59.092516076860392</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>59.759559063417498</v>
+        <v>60.123408381514935</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>60.271885886084505</v>
+        <v>60.638854533842199</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>61.296539531418546</v>
+        <v>61.669746838496756</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>63.858173644753627</v>
+        <v>64.246977600133121</v>
       </c>
       <c r="G74" s="296"/>
       <c r="H74" s="296"/>
@@ -18656,29 +18645,29 @@
       <c r="K74" s="296"/>
       <c r="L74" s="296"/>
     </row>
-    <row r="75" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:21" ht="13.15">
       <c r="A75" s="131">
         <v>2</v>
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>58.67117989092776</v>
+        <v>59.028402553374654</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>60.674042352421544</v>
+        <v>61.043459551646791</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>61.689877749737597</v>
+        <v>62.065479917901797</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>63.750356877508018</v>
+        <v>64.138504384649664</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>69.069603306907595</v>
+        <v>69.490137334573518</v>
       </c>
       <c r="G75" s="296"/>
       <c r="H75" s="296"/>
@@ -18687,29 +18676,29 @@
       <c r="K75" s="296"/>
       <c r="L75" s="296"/>
     </row>
-    <row r="76" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:21" ht="13.15">
       <c r="A76" s="131">
         <v>3</v>
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>58.611762149990049</v>
+        <v>58.968623044297047</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>61.543760725180633</v>
+        <v>61.918473251912054</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>63.051678793618876</v>
+        <v>63.435572361334316</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>66.152695538015209</v>
+        <v>66.555469814449708</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>74.414659370655272</v>
+        <v>74.867737062204725</v>
       </c>
       <c r="G76" s="296"/>
       <c r="H76" s="296"/>
@@ -18718,29 +18707,29 @@
       <c r="K76" s="296"/>
       <c r="L76" s="296"/>
     </row>
-    <row r="77" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:21" ht="13.15">
       <c r="A77" s="131">
         <v>4</v>
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>58.556360992938551</v>
+        <v>58.912884574294601</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>62.370905471301164</v>
+        <v>62.750654113702787</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>64.359515693570145</v>
+        <v>64.751372097218237</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>68.504635485364858</v>
+        <v>68.921729675792406</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>79.896768153986173</v>
+        <v>80.38322396233923</v>
       </c>
       <c r="G77" s="296"/>
       <c r="H77" s="296"/>
@@ -18749,29 +18738,29 @@
       <c r="K77" s="296"/>
       <c r="L77" s="296"/>
     </row>
-    <row r="78" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:21" ht="13.15">
       <c r="A78" s="131">
         <v>5</v>
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>58.260217053455243</v>
+        <v>58.614937546366058</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>62.903195456373034</v>
+        <v>63.28618497523248</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>65.356149729865251</v>
+        <v>65.754074193923799</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>70.537686181703577</v>
+        <v>70.96715871161544</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>85.223613531916598</v>
+        <v>85.742502127404407</v>
       </c>
       <c r="G78" s="296"/>
       <c r="H78" s="296"/>
@@ -18780,29 +18769,29 @@
       <c r="K78" s="296"/>
       <c r="L78" s="296"/>
     </row>
-    <row r="79" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:21" ht="13.15">
       <c r="A79" s="131">
         <v>6</v>
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>58.212052866517347</v>
+        <v>58.566480109162448</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>63.651343005116026</v>
+        <v>64.038887660922811</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>66.562388919748628</v>
+        <v>66.967657636569072</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>72.791978468272774</v>
+        <v>73.235176379096345</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>90.990460378287054</v>
+        <v>91.544460733726055</v>
       </c>
       <c r="G79" s="296"/>
       <c r="H79" s="296"/>
@@ -18811,30 +18800,30 @@
       <c r="K79" s="296"/>
       <c r="L79" s="296"/>
     </row>
-    <row r="80" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:21" ht="13.15">
       <c r="A80" s="131">
         <f t="shared" ref="A80" si="12">A62</f>
         <v>7</v>
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>57.939183835346888</v>
+        <v>58.291949700088992</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>64.12095422979138</v>
+        <v>64.511358139022164</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>67.471729611416649</v>
+        <v>67.882534898381977</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>74.735084906228778</v>
+        <v>75.190113526038857</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>96.601759402994418</v>
+        <v>97.189924457031921</v>
       </c>
       <c r="G80" s="296"/>
       <c r="H80" s="296"/>
@@ -18843,29 +18832,29 @@
       <c r="K80" s="296"/>
       <c r="L80" s="296"/>
     </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:12" ht="13.15">
       <c r="A81" s="131">
         <v>8</v>
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>57.89731126396299</v>
+        <v>58.249822185282085</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>64.797649279013839</v>
+        <v>65.192173282771407</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>68.584263585083164</v>
+        <v>69.00184259551672</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>76.895783660043477</v>
+        <v>77.363967811462388</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>102.66813346886734</v>
+        <v>103.29323397058526</v>
       </c>
       <c r="G81" s="296"/>
       <c r="H81" s="296"/>
@@ -18874,30 +18863,30 @@
       <c r="K81" s="296"/>
       <c r="L81" s="296"/>
     </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:12" ht="13.15">
       <c r="A82" s="131">
         <f t="shared" ref="A82" si="13">A64</f>
         <v>9</v>
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>57.645718471659833</v>
+        <v>57.996697556610783</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>65.211147609162722</v>
+        <v>65.60818921994111</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>69.413483369267055</v>
+        <v>69.836111129352659</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>78.7527962827875</v>
+        <v>79.232286956327286</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>108.57886000871775</v>
+        <v>109.23994828970798</v>
       </c>
       <c r="G82" s="296"/>
       <c r="H82" s="296"/>
@@ -18906,30 +18895,30 @@
       <c r="K82" s="296"/>
       <c r="L82" s="296"/>
     </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:12" ht="13.15">
       <c r="A83" s="131">
         <f t="shared" ref="A83:A87" si="14">A65</f>
         <v>10</v>
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>57.609315651519637</v>
+        <v>57.960073095924827</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>65.823214293617653</v>
+        <v>66.223982505616988</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>70.439591501835608</v>
+        <v>70.868466776966187</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>80.823787312899867</v>
+        <v>81.315887327704914</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>114.96031859214759</v>
+        <v>115.66026073000086</v>
       </c>
       <c r="G83" s="296"/>
       <c r="H83" s="296"/>
@@ -18938,30 +18927,30 @@
       <c r="K83" s="296"/>
       <c r="L83" s="296"/>
     </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:12" ht="13.15">
       <c r="A84" s="131">
         <f t="shared" si="14"/>
         <v>15</v>
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>56.905788354600645</v>
+        <v>57.252262334882964</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>67.837584844139684</v>
+        <v>68.250617660541891</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>74.329199353987448</v>
+        <v>74.781756717588081</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>89.801974860099051</v>
+        <v>90.348739056969649</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>148.42527369008917</v>
+        <v>149.32896902296895</v>
       </c>
       <c r="G84" s="296"/>
       <c r="H84" s="296"/>
@@ -18970,30 +18959,30 @@
       <c r="K84" s="296"/>
       <c r="L84" s="296"/>
     </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:12" ht="13.15">
       <c r="A85" s="132">
         <f t="shared" si="14"/>
         <v>20</v>
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>56.490868810852767</v>
+        <v>56.834816530978145</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>69.52380534706144</v>
+        <v>69.947104808495268</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>77.648966971261444</v>
+        <v>78.121736920140791</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>98.075637020143006</v>
+        <v>98.672775858029709</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>186.8236346261065</v>
+        <v>187.96112046315989</v>
       </c>
       <c r="G85" s="296"/>
       <c r="H85" s="296"/>
@@ -19002,30 +18991,30 @@
       <c r="K85" s="296"/>
       <c r="L85" s="296"/>
     </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:12" ht="13.15">
       <c r="A86" s="132">
         <f t="shared" si="14"/>
         <v>25</v>
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>56.025935309470363</v>
+        <v>56.367052256743833</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>70.635372004506763</v>
+        <v>71.065439299851505</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>80.145931556867353</v>
+        <v>80.633904410119229</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>105.27129560288341</v>
+        <v>105.91224559850998</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>230.08071551755432</v>
+        <v>231.48157443887928</v>
       </c>
       <c r="G86" s="296"/>
       <c r="H86" s="296"/>
@@ -19034,30 +19023,30 @@
       <c r="K86" s="296"/>
       <c r="L86" s="296"/>
     </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:12" ht="13.15">
       <c r="A87" s="132">
         <f t="shared" si="14"/>
         <v>30</v>
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>55.755277666610304</v>
+        <v>56.094746700138501</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>71.592763185564252</v>
+        <v>72.028659609065897</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>82.301954049522635</v>
+        <v>82.803053962713534</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>111.92175395506852</v>
+        <v>112.60319562724695</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>279.64896848868631</v>
+        <v>281.3516264079538</v>
       </c>
       <c r="G87" s="296"/>
       <c r="H87" s="296"/>
@@ -19066,7 +19055,7 @@
       <c r="K87" s="296"/>
       <c r="L87" s="296"/>
     </row>
-    <row r="89" spans="1:12" ht="14" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:12" ht="13.15">
       <c r="B89" s="153" t="s">
         <v>101</v>
       </c>
@@ -19089,7 +19078,7 @@
       <c r="K89" s="323"/>
       <c r="L89" s="323"/>
     </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:12">
       <c r="B90" s="120" t="str">
         <f>Scenarios!B29</f>
         <v>Snowball Scenario</v>
@@ -19104,7 +19093,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>148.42527369008917</v>
+        <v>149.32896902296895</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19117,7 +19106,7 @@
       <c r="K90" s="297"/>
       <c r="L90" s="297"/>
     </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:12">
       <c r="B91" s="120" t="str">
         <f>Scenarios!B22</f>
         <v>Optimistic</v>
@@ -19132,7 +19121,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>89.801974860099051</v>
+        <v>90.348739056969649</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19145,7 +19134,7 @@
       <c r="K91" s="297"/>
       <c r="L91" s="297"/>
     </row>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:12">
       <c r="B92" s="120" t="str">
         <f>Scenarios!B23</f>
         <v>Base</v>
@@ -19160,7 +19149,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>74.329199353987448</v>
+        <v>74.781756717588081</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19173,7 +19162,7 @@
       <c r="K92" s="297"/>
       <c r="L92" s="297"/>
     </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:12">
       <c r="B93" s="120" t="str">
         <f>Scenarios!B24</f>
         <v>Pessimistic</v>
@@ -19188,7 +19177,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>67.837584844139684</v>
+        <v>68.250617660541891</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19201,7 +19190,7 @@
       <c r="K93" s="297"/>
       <c r="L93" s="297"/>
     </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:12">
       <c r="B94" s="120" t="str">
         <f>Scenarios!B30</f>
         <v>Devil's advocate</v>
@@ -19216,7 +19205,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>56.905788354600645</v>
+        <v>57.252262334882964</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19229,7 +19218,7 @@
       <c r="K94" s="297"/>
       <c r="L94" s="297"/>
     </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:12">
       <c r="B95" s="141"/>
       <c r="C95" s="141"/>
       <c r="D95" s="141"/>
@@ -19242,16 +19231,16 @@
       <c r="K95" s="142"/>
       <c r="L95" s="142"/>
     </row>
-    <row r="105" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="105" spans="3:3">
       <c r="C105" s="112"/>
     </row>
-    <row r="106" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="106" spans="3:3">
       <c r="C106" s="112"/>
     </row>
-    <row r="107" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="107" spans="3:3">
       <c r="C107" s="112"/>
     </row>
-    <row r="114" spans="3:21" x14ac:dyDescent="0.15">
+    <row r="114" spans="3:21">
       <c r="C114" s="275"/>
       <c r="M114" s="275"/>
       <c r="N114" s="275"/>
@@ -19263,7 +19252,7 @@
       <c r="T114" s="275"/>
       <c r="U114" s="275"/>
     </row>
-    <row r="115" spans="3:21" x14ac:dyDescent="0.15">
+    <row r="115" spans="3:21">
       <c r="C115" s="275"/>
       <c r="M115" s="275"/>
       <c r="N115" s="275"/>
@@ -19275,7 +19264,7 @@
       <c r="T115" s="275"/>
       <c r="U115" s="275"/>
     </row>
-    <row r="116" spans="3:21" x14ac:dyDescent="0.15">
+    <row r="116" spans="3:21">
       <c r="C116" s="275"/>
       <c r="M116" s="275"/>
       <c r="N116" s="275"/>
@@ -19287,7 +19276,7 @@
       <c r="T116" s="275"/>
       <c r="U116" s="275"/>
     </row>
-    <row r="117" spans="3:21" x14ac:dyDescent="0.15">
+    <row r="117" spans="3:21">
       <c r="C117" s="275"/>
       <c r="M117" s="275"/>
       <c r="N117" s="275"/>
@@ -19299,7 +19288,7 @@
       <c r="T117" s="275"/>
       <c r="U117" s="275"/>
     </row>
-    <row r="118" spans="3:21" x14ac:dyDescent="0.15">
+    <row r="118" spans="3:21">
       <c r="C118" s="275"/>
       <c r="M118" s="275"/>
       <c r="N118" s="275"/>
@@ -19339,14 +19328,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
   <dimension ref="B2:G67"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="2.6640625" customWidth="1"/>
     <col min="2" max="2" width="22.6640625" customWidth="1"/>
     <col min="3" max="7" width="20.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:7" ht="13.9">
       <c r="B2" s="34" t="s">
         <v>122</v>
       </c>
@@ -19356,7 +19345,7 @@
       <c r="F2" s="35"/>
       <c r="G2" s="35"/>
     </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:7" ht="13.15">
       <c r="B3" s="145" t="s">
         <v>125</v>
       </c>
@@ -19365,7 +19354,7 @@
       </c>
       <c r="E3" s="97"/>
     </row>
-    <row r="4" spans="2:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:7" ht="12.75" customHeight="1">
       <c r="B4" s="139" t="s">
         <v>123</v>
       </c>
@@ -19386,14 +19375,14 @@
       <c r="F4" s="469"/>
       <c r="G4" s="469"/>
     </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:7">
       <c r="C5" s="445"/>
       <c r="D5" s="469"/>
       <c r="E5" s="469"/>
       <c r="F5" s="469"/>
       <c r="G5" s="469"/>
     </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:7" ht="13.15">
       <c r="B6" s="145" t="s">
         <v>91</v>
       </c>
@@ -19406,7 +19395,7 @@
       <c r="F6" s="469"/>
       <c r="G6" s="469"/>
     </row>
-    <row r="7" spans="2:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:7" ht="12.75" customHeight="1">
       <c r="B7" s="97" t="s">
         <v>232</v>
       </c>
@@ -19419,7 +19408,7 @@
       <c r="F7" s="469"/>
       <c r="G7" s="469"/>
     </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:7">
       <c r="B8" s="97" t="s">
         <v>63</v>
       </c>
@@ -19432,7 +19421,7 @@
       <c r="F8" s="469"/>
       <c r="G8" s="469"/>
     </row>
-    <row r="9" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:7">
       <c r="B9" s="97" t="s">
         <v>54</v>
       </c>
@@ -19445,14 +19434,14 @@
       <c r="F9" s="469"/>
       <c r="G9" s="469"/>
     </row>
-    <row r="10" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:7">
       <c r="C10" s="448"/>
       <c r="D10" s="469"/>
       <c r="E10" s="469"/>
       <c r="F10" s="469"/>
       <c r="G10" s="469"/>
     </row>
-    <row r="11" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:7" ht="13.15">
       <c r="B11" s="145" t="s">
         <v>321</v>
       </c>
@@ -19462,7 +19451,7 @@
       <c r="F11" s="469"/>
       <c r="G11" s="469"/>
     </row>
-    <row r="12" spans="2:7" ht="14" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:7">
       <c r="B12" s="114" t="s">
         <v>121</v>
       </c>
@@ -19475,7 +19464,7 @@
       <c r="F12" s="469"/>
       <c r="G12" s="469"/>
     </row>
-    <row r="13" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:7">
       <c r="B13" s="135" t="s">
         <v>127</v>
       </c>
@@ -19488,7 +19477,7 @@
       <c r="F13" s="469"/>
       <c r="G13" s="469"/>
     </row>
-    <row r="14" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:7">
       <c r="B14" s="97" t="s">
         <v>63</v>
       </c>
@@ -19501,7 +19490,7 @@
       <c r="F14" s="469"/>
       <c r="G14" s="469"/>
     </row>
-    <row r="16" spans="2:7" ht="16" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:7" ht="13.9">
       <c r="B16" s="34" t="s">
         <v>453</v>
       </c>
@@ -19511,7 +19500,7 @@
       <c r="F16" s="35"/>
       <c r="G16" s="35"/>
     </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:7" ht="13.15">
       <c r="B17" s="106" t="s">
         <v>126</v>
       </c>
@@ -19519,7 +19508,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="18" spans="2:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:7" ht="12.75" customHeight="1">
       <c r="B18" s="139" t="s">
         <v>111</v>
       </c>
@@ -19531,18 +19520,18 @@
       </c>
       <c r="F18" s="319"/>
     </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:7">
       <c r="E19" s="319"/>
       <c r="F19" s="319"/>
     </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:7" ht="13.15">
       <c r="B20" s="106" t="s">
         <v>450</v>
       </c>
       <c r="E20" s="319"/>
       <c r="F20" s="319"/>
     </row>
-    <row r="21" spans="2:7" ht="14" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:7" ht="13.15">
       <c r="B21" s="153" t="s">
         <v>436</v>
       </c>
@@ -19563,7 +19552,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="22" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:7">
       <c r="B22" s="302" t="s">
         <v>445</v>
       </c>
@@ -19576,7 +19565,7 @@
       </c>
       <c r="E22" s="326">
         <f>DCF!E91</f>
-        <v>89.801974860099051</v>
+        <v>90.348739056969649</v>
       </c>
       <c r="F22" s="328">
         <f>1-F23-F24</f>
@@ -19587,7 +19576,7 @@
         <v>0.15999999999999995</v>
       </c>
     </row>
-    <row r="23" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:7">
       <c r="B23" s="302" t="s">
         <v>437</v>
       </c>
@@ -19600,7 +19589,7 @@
       </c>
       <c r="E23" s="326">
         <f>DCF!E92</f>
-        <v>74.329199353987448</v>
+        <v>74.781756717588081</v>
       </c>
       <c r="F23" s="327">
         <v>0.55000000000000004</v>
@@ -19610,7 +19599,7 @@
         <v>0.44</v>
       </c>
     </row>
-    <row r="24" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:7">
       <c r="B24" s="302" t="s">
         <v>446</v>
       </c>
@@ -19623,7 +19612,7 @@
       </c>
       <c r="E24" s="326">
         <f>DCF!E93</f>
-        <v>67.837584844139684</v>
+        <v>68.250617660541891</v>
       </c>
       <c r="F24" s="327">
         <v>0.25</v>
@@ -19633,13 +19622,13 @@
         <v>0.19999999999999998</v>
       </c>
     </row>
-    <row r="25" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:7">
       <c r="B25" s="141" t="s">
         <v>451</v>
       </c>
       <c r="C25" s="441">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>75.800850827747837</v>
+        <v>76.262368421202851</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19647,12 +19636,12 @@
       </c>
       <c r="G25" s="149"/>
     </row>
-    <row r="27" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:7" ht="13.15">
       <c r="B27" s="106" t="s">
         <v>452</v>
       </c>
     </row>
-    <row r="28" spans="2:7" ht="14" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:7" ht="13.15">
       <c r="B28" s="153" t="s">
         <v>436</v>
       </c>
@@ -19673,7 +19662,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="29" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:7">
       <c r="B29" s="302" t="s">
         <v>444</v>
       </c>
@@ -19686,7 +19675,7 @@
       </c>
       <c r="E29" s="326">
         <f>DCF!E90</f>
-        <v>148.42527369008917</v>
+        <v>149.32896902296895</v>
       </c>
       <c r="F29" s="327">
         <v>0.15</v>
@@ -19696,7 +19685,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="30" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:7">
       <c r="B30" s="315" t="s">
         <v>447</v>
       </c>
@@ -19709,7 +19698,7 @@
       </c>
       <c r="E30" s="326">
         <f>DCF!E94</f>
-        <v>56.905788354600645</v>
+        <v>57.252262334882964</v>
       </c>
       <c r="F30" s="327">
         <v>0.05</v>
@@ -19719,16 +19708,16 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="31" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:7">
       <c r="E31" s="329"/>
       <c r="F31" s="329"/>
     </row>
-    <row r="32" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:7" ht="13.15">
       <c r="B32" s="145" t="s">
         <v>456</v>
       </c>
     </row>
-    <row r="33" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:7">
       <c r="B33" s="97" t="s">
         <v>458</v>
       </c>
@@ -19748,13 +19737,13 @@
         <v>3</v>
       </c>
     </row>
-    <row r="34" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:7">
       <c r="B34" s="97" t="s">
         <v>233</v>
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>78.25</v>
+        <v>78.45</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19765,16 +19754,16 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>6.025755964683787E-2</v>
-      </c>
-    </row>
-    <row r="35" spans="2:7" x14ac:dyDescent="0.15">
+        <v>6.1359469686947478E-2</v>
+      </c>
+    </row>
+    <row r="35" spans="2:7">
       <c r="B35" s="97" t="s">
         <v>434</v>
       </c>
       <c r="C35" s="320">
         <f>DCF!C11</f>
-        <v>73.2448294520552</v>
+        <v>73.690784570666622</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19785,16 +19774,16 @@
       </c>
       <c r="F35" s="330">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>8.4577006278761663E-2</v>
-      </c>
-    </row>
-    <row r="36" spans="2:7" x14ac:dyDescent="0.15">
+        <v>8.4391458452010168E-2</v>
+      </c>
+    </row>
+    <row r="36" spans="2:7">
       <c r="B36" s="97" t="s">
         <v>435</v>
       </c>
       <c r="C36" s="321">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>85.749761133441666</v>
+        <v>86.271853207151764</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -19807,7 +19796,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="38" spans="2:7" ht="16" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:7" ht="13.9">
       <c r="B38" s="34" t="s">
         <v>411</v>
       </c>
@@ -19817,7 +19806,7 @@
       <c r="F38" s="35"/>
       <c r="G38" s="35"/>
     </row>
-    <row r="39" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:7" ht="13.15">
       <c r="B39" s="414" t="str">
         <f>IF(DCF!F14="II","2","1")&amp;"-stage DCF"</f>
         <v>2-stage DCF</v>
@@ -19826,7 +19815,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="40" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:7">
       <c r="B40" t="s">
         <v>550</v>
       </c>
@@ -19838,7 +19827,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="41" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:7">
       <c r="B41" s="97" t="s">
         <v>400</v>
       </c>
@@ -19848,7 +19837,7 @@
       </c>
       <c r="E41" s="97"/>
     </row>
-    <row r="43" spans="2:7" ht="16" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:7" ht="13.9">
       <c r="B43" s="34" t="s">
         <v>276</v>
       </c>
@@ -19858,7 +19847,7 @@
       <c r="F43" s="35"/>
       <c r="G43" s="35"/>
     </row>
-    <row r="44" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:7" ht="13.15">
       <c r="B44" s="106" t="s">
         <v>249</v>
       </c>
@@ -19866,7 +19855,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="45" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:7">
       <c r="B45" s="139" t="s">
         <v>111</v>
       </c>
@@ -19879,7 +19868,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="46" spans="2:7" ht="14" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:7">
       <c r="B46" s="114" t="s">
         <v>112</v>
       </c>
@@ -19891,13 +19880,13 @@
         <v>252</v>
       </c>
     </row>
-    <row r="47" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:7">
       <c r="B47" s="97" t="s">
         <v>96</v>
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>85.747183560275744</v>
+        <v>86.269259940291761</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -19907,7 +19896,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="49" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="49" spans="2:7" ht="13.15">
       <c r="B49" s="106" t="s">
         <v>277</v>
       </c>
@@ -19919,7 +19908,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="50" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="50" spans="2:7">
       <c r="B50" s="97" t="s">
         <v>250</v>
       </c>
@@ -19929,7 +19918,7 @@
       </c>
       <c r="E50" s="126"/>
     </row>
-    <row r="51" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:7">
       <c r="B51" s="97" t="s">
         <v>246</v>
       </c>
@@ -19941,7 +19930,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="52" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:7">
       <c r="B52" s="97" t="s">
         <v>245</v>
       </c>
@@ -19951,7 +19940,7 @@
       </c>
       <c r="E52" s="221"/>
     </row>
-    <row r="53" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="53" spans="2:7">
       <c r="B53" s="97" t="s">
         <v>237</v>
       </c>
@@ -19964,10 +19953,10 @@
       </c>
       <c r="F53" s="249">
         <f>BS!D89/C36</f>
-        <v>8.7489726527716166E-2</v>
-      </c>
-    </row>
-    <row r="55" spans="2:7" ht="16" x14ac:dyDescent="0.25">
+        <v>8.7489726527716194E-2</v>
+      </c>
+    </row>
+    <row r="55" spans="2:7" ht="13.9">
       <c r="B55" s="34" t="s">
         <v>107</v>
       </c>
@@ -19977,12 +19966,12 @@
       <c r="F55" s="35"/>
       <c r="G55" s="35"/>
     </row>
-    <row r="56" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:7" ht="13.15">
       <c r="B56" s="106" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="57" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="57" spans="2:7">
       <c r="B57" s="220" t="s">
         <v>248</v>
       </c>
@@ -19992,7 +19981,7 @@
       </c>
       <c r="D57" s="126"/>
     </row>
-    <row r="58" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:7">
       <c r="B58" s="97" t="s">
         <v>333</v>
       </c>
@@ -20005,13 +19994,13 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="60" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="60" spans="2:7" ht="13.15">
       <c r="B60" s="106" t="s">
         <v>473</v>
       </c>
       <c r="E60" s="413"/>
     </row>
-    <row r="61" spans="2:7" ht="14" x14ac:dyDescent="0.2">
+    <row r="61" spans="2:7" ht="13.15">
       <c r="B61" s="153" t="s">
         <v>462</v>
       </c>
@@ -20032,57 +20021,57 @@
         <v>461</v>
       </c>
     </row>
-    <row r="62" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:7" ht="13.15">
       <c r="B62" s="302" t="s">
         <v>312</v>
       </c>
       <c r="C62" s="119">
         <f>PV(F62, Holding_Period, -C58, 0)</f>
-        <v>4.318449719619883</v>
+        <v>4.3184497196198821</v>
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>39.516018955503078</v>
+        <v>39.756614381175936</v>
       </c>
       <c r="E62" s="332">
         <f>C62+D62</f>
-        <v>43.834468675122963</v>
+        <v>44.075064100795821</v>
       </c>
       <c r="F62" s="301">
         <f>Thesis!E22</f>
-        <v>0.29465259038036601</v>
+        <v>0.29465259038036606</v>
       </c>
       <c r="G62" s="440">
         <f>(1-E62/C36)</f>
-        <v>0.48880943695098067</v>
-      </c>
-    </row>
-    <row r="63" spans="2:7" x14ac:dyDescent="0.15">
+        <v>0.48911420744648981</v>
+      </c>
+    </row>
+    <row r="63" spans="2:7" ht="13.15">
       <c r="B63" s="302" t="s">
         <v>313</v>
       </c>
       <c r="C63" s="119">
         <f>PV(F63, Holding_Period, -C58, 0)</f>
-        <v>4.9654493155550261</v>
+        <v>4.9654493155550243</v>
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>49.530547947114343</v>
+        <v>49.83211737597216</v>
       </c>
       <c r="E63" s="332">
         <f>C63+D63</f>
-        <v>54.49599726266937</v>
+        <v>54.797566691527187</v>
       </c>
       <c r="F63" s="301">
         <f>Thesis!E23</f>
-        <v>0.20075184365903001</v>
+        <v>0.20075184365903009</v>
       </c>
       <c r="G63" s="440">
         <f>(1-E63/C36)</f>
-        <v>0.36447639570839108</v>
-      </c>
-    </row>
-    <row r="65" spans="2:7" ht="14" x14ac:dyDescent="0.2">
+        <v>0.36482682758709328</v>
+      </c>
+    </row>
+    <row r="65" spans="2:7" ht="13.15">
       <c r="B65" s="153" t="s">
         <v>463</v>
       </c>
@@ -20103,7 +20092,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="66" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="66" spans="2:7" ht="13.15">
       <c r="B66" s="302" t="s">
         <v>315</v>
       </c>
@@ -20113,11 +20102,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>61.462032490931094</v>
+        <v>61.836247410873455</v>
       </c>
       <c r="E66" s="332">
         <f>C66+D66</f>
-        <v>67.155775868146307</v>
+        <v>67.529990788088668</v>
       </c>
       <c r="F66" s="301">
         <f>Thesis!E24</f>
@@ -20125,10 +20114,10 @@
       </c>
       <c r="G66" s="440">
         <f>(1-E66/C36)</f>
-        <v>0.21684008234565055</v>
-      </c>
-    </row>
-    <row r="67" spans="2:7" x14ac:dyDescent="0.15">
+        <v>0.21724191288740546</v>
+      </c>
+    </row>
+    <row r="67" spans="2:7" ht="13.15">
       <c r="B67" s="302" t="s">
         <v>314</v>
       </c>
@@ -20138,11 +20127,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>69.508996133668688</v>
+        <v>69.932205428403179</v>
       </c>
       <c r="E67" s="332">
         <f>C67+D67</f>
-        <v>75.674201669797</v>
+        <v>76.097410964531491</v>
       </c>
       <c r="F67" s="301">
         <f>Thesis!E25</f>
@@ -20150,7 +20139,7 @@
       </c>
       <c r="G67" s="440">
         <f>(1-E67/C36)</f>
-        <v>0.11749956303627862</v>
+        <v>0.11793466657300034</v>
       </c>
     </row>
   </sheetData>
@@ -20169,7 +20158,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:J167"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.4"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="343" customWidth="1"/>
     <col min="2" max="2" width="32.6640625" style="343" customWidth="1"/>
@@ -20178,7 +20167,7 @@
     <col min="7" max="16384" width="9" style="343"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:10" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" ht="13.9">
       <c r="A2" s="345" t="s">
         <v>334</v>
       </c>
@@ -20192,7 +20181,7 @@
       <c r="I2" s="346"/>
       <c r="J2" s="346"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10">
       <c r="E3" s="435" t="s">
         <v>542</v>
       </c>
@@ -20201,7 +20190,7 @@
         <v>46038</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10">
       <c r="B4" s="422" t="s">
         <v>534</v>
       </c>
@@ -20218,7 +20207,7 @@
         <v>INT</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10">
       <c r="B5" s="343" t="s">
         <v>364</v>
       </c>
@@ -20234,7 +20223,7 @@
         <v>Y</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10">
       <c r="B6" s="350" t="s">
         <v>336</v>
       </c>
@@ -20244,7 +20233,7 @@
       </c>
       <c r="E6" s="354"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10">
       <c r="B7" s="343" t="s">
         <v>366</v>
       </c>
@@ -20255,16 +20244,16 @@
       <c r="D7" s="354"/>
       <c r="E7" s="354"/>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10">
       <c r="B8" s="351" t="s">
         <v>365</v>
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>78.25</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+        <v>78.45</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
       <c r="B9" s="351" t="s">
         <v>361</v>
       </c>
@@ -20273,43 +20262,43 @@
         <v>2770499587</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10">
       <c r="B10" s="351" t="s">
         <v>367</v>
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>216791.59268274999</v>
+        <v>217345.69260014998</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>529</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>6.025755964683787E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+        <v>6.1359469686947478E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
       <c r="D11" s="349"/>
       <c r="E11" s="349"/>
     </row>
-    <row r="12" spans="1:10" ht="24.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="474" t="s">
+    <row r="12" spans="1:10" ht="24.5" customHeight="1">
+      <c r="B12" s="471" t="s">
         <v>498</v>
       </c>
-      <c r="C12" s="474"/>
-      <c r="D12" s="474"/>
-      <c r="E12" s="474"/>
-      <c r="F12" s="474"/>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="C12" s="471"/>
+      <c r="D12" s="471"/>
+      <c r="E12" s="471"/>
+      <c r="F12" s="471"/>
+    </row>
+    <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
         <v>370</v>
       </c>
       <c r="C14" s="348"/>
       <c r="D14" s="349"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10">
       <c r="B15" s="343" t="s">
         <v>337</v>
       </c>
@@ -20325,7 +20314,7 @@
         <v>CNY/HKD</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10">
       <c r="B16" s="343" t="s">
         <v>338</v>
       </c>
@@ -20338,10 +20327,10 @@
       </c>
       <c r="E16" s="425">
         <f>Exchange_Rate</f>
-        <v>1.1200000000000001</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+        <v>1.1268191807746888</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
       <c r="B17" s="343" t="s">
         <v>535</v>
       </c>
@@ -20357,14 +20346,14 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:6">
       <c r="B18" s="343" t="str">
         <f>"预期股权价值 ("&amp;C7&amp;") :"</f>
         <v>预期股权价值 (HKD) :</v>
       </c>
       <c r="C18" s="359">
         <f>C125</f>
-        <v>85.749761133441666</v>
+        <v>86.271853207151764</v>
       </c>
       <c r="D18" s="350" t="s">
         <v>362</v>
@@ -20374,7 +20363,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:6">
       <c r="B19" s="350" t="s">
         <v>335</v>
       </c>
@@ -20390,11 +20379,11 @@
         <v>46081</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:6">
       <c r="D20" s="349"/>
       <c r="E20" s="349"/>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:6">
       <c r="B21" s="347" t="s">
         <v>493</v>
       </c>
@@ -20410,45 +20399,45 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:6">
       <c r="B22" s="343" t="s">
         <v>340</v>
       </c>
       <c r="C22" s="364">
         <f>E140</f>
-        <v>43.834468675122963</v>
+        <v>44.075064100795821</v>
       </c>
       <c r="D22" s="365" t="s">
         <v>440</v>
       </c>
       <c r="E22" s="366">
         <f>Thesis!E22</f>
-        <v>0.29465259038036601</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+        <v>0.29465259038036606</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
       <c r="B23" s="343" t="s">
         <v>341</v>
       </c>
       <c r="C23" s="367">
         <f>E141</f>
-        <v>54.49599726266937</v>
+        <v>54.797566691527187</v>
       </c>
       <c r="D23" s="365" t="s">
         <v>441</v>
       </c>
       <c r="E23" s="368">
         <f>Thesis!E23</f>
-        <v>0.20075184365903001</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+        <v>0.20075184365903009</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
       <c r="B24" s="343" t="s">
         <v>343</v>
       </c>
       <c r="C24" s="367">
         <f>E144</f>
-        <v>67.155775868146307</v>
+        <v>67.529990788088668</v>
       </c>
       <c r="D24" s="365" t="s">
         <v>443</v>
@@ -20458,13 +20447,13 @@
         <v>0.1174</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:6">
       <c r="B25" s="343" t="s">
         <v>342</v>
       </c>
       <c r="C25" s="367">
         <f>E145</f>
-        <v>75.674201669797</v>
+        <v>76.097410964531491</v>
       </c>
       <c r="D25" s="365" t="s">
         <v>442</v>
@@ -20474,7 +20463,7 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" ht="13.9">
       <c r="A27" s="345" t="s">
         <v>345</v>
       </c>
@@ -20484,25 +20473,25 @@
       <c r="E27" s="345"/>
       <c r="F27" s="345"/>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="474" t="s">
+    <row r="29" spans="1:6">
+      <c r="B29" s="471" t="s">
         <v>499</v>
       </c>
-      <c r="C29" s="474"/>
-      <c r="D29" s="474"/>
-      <c r="E29" s="474"/>
-      <c r="F29" s="474"/>
-    </row>
-    <row r="30" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B30" s="477" t="s">
+      <c r="C29" s="471"/>
+      <c r="D29" s="471"/>
+      <c r="E29" s="471"/>
+      <c r="F29" s="471"/>
+    </row>
+    <row r="30" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B30" s="472" t="s">
         <v>500</v>
       </c>
-      <c r="C30" s="477"/>
-      <c r="D30" s="477"/>
-      <c r="E30" s="477"/>
-      <c r="F30" s="477"/>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C30" s="472"/>
+      <c r="D30" s="472"/>
+      <c r="E30" s="472"/>
+      <c r="F30" s="472"/>
+    </row>
+    <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
         <v>371</v>
       </c>
@@ -20511,7 +20500,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:6">
       <c r="B33" s="470" t="s">
         <v>501</v>
       </c>
@@ -20520,7 +20509,7 @@
       <c r="E33" s="470"/>
       <c r="F33" s="470"/>
     </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:6">
       <c r="B34" s="372" t="s">
         <v>197</v>
       </c>
@@ -20533,11 +20522,11 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="35" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:6">
       <c r="B35" s="372"/>
       <c r="C35" s="374"/>
     </row>
-    <row r="36" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:6" ht="24.5" customHeight="1">
       <c r="B36" s="470" t="s">
         <v>502</v>
       </c>
@@ -20546,7 +20535,7 @@
       <c r="E36" s="470"/>
       <c r="F36" s="470"/>
     </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:6">
       <c r="B37" s="372" t="s">
         <v>199</v>
       </c>
@@ -20559,7 +20548,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="38" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:6">
       <c r="B38" s="375" t="s">
         <v>200</v>
       </c>
@@ -20572,7 +20561,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="40" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:6">
       <c r="B40" s="470" t="s">
         <v>503</v>
       </c>
@@ -20581,7 +20570,7 @@
       <c r="E40" s="470"/>
       <c r="F40" s="470"/>
     </row>
-    <row r="41" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:6">
       <c r="B41" s="372" t="s">
         <v>202</v>
       </c>
@@ -20594,7 +20583,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="43" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:6">
       <c r="B43" s="470" t="s">
         <v>504</v>
       </c>
@@ -20603,7 +20592,7 @@
       <c r="E43" s="470"/>
       <c r="F43" s="470"/>
     </row>
-    <row r="44" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:6">
       <c r="B44" s="372" t="s">
         <v>267</v>
       </c>
@@ -20618,7 +20607,7 @@
       <c r="E44" s="371"/>
       <c r="F44" s="371"/>
     </row>
-    <row r="45" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:6">
       <c r="B45" s="372" t="s">
         <v>268</v>
       </c>
@@ -20633,7 +20622,7 @@
       <c r="E45" s="371"/>
       <c r="F45" s="371"/>
     </row>
-    <row r="46" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:6">
       <c r="B46" s="372" t="s">
         <v>203</v>
       </c>
@@ -20646,12 +20635,12 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="48" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:6">
       <c r="B48" s="343" t="s">
         <v>505</v>
       </c>
     </row>
-    <row r="49" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="49" spans="2:6">
       <c r="B49" s="372" t="s">
         <v>223</v>
       </c>
@@ -20664,7 +20653,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="51" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="51" spans="2:6">
       <c r="B51" s="470" t="s">
         <v>506</v>
       </c>
@@ -20673,7 +20662,7 @@
       <c r="E51" s="470"/>
       <c r="F51" s="470"/>
     </row>
-    <row r="52" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="52" spans="2:6">
       <c r="B52" s="372" t="s">
         <v>496</v>
       </c>
@@ -20686,16 +20675,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="54" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="54" spans="2:6">
       <c r="B54" s="470" t="s">
         <v>507</v>
       </c>
-      <c r="C54" s="476"/>
-      <c r="D54" s="476"/>
-      <c r="E54" s="476"/>
-      <c r="F54" s="476"/>
-    </row>
-    <row r="55" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="C54" s="473"/>
+      <c r="D54" s="473"/>
+      <c r="E54" s="473"/>
+      <c r="F54" s="473"/>
+    </row>
+    <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
         <v>207</v>
       </c>
@@ -20708,25 +20697,25 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="57" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B57" s="474" t="s">
+    <row r="57" spans="2:6">
+      <c r="B57" s="471" t="s">
         <v>508</v>
       </c>
-      <c r="C57" s="474"/>
-      <c r="D57" s="474"/>
-      <c r="E57" s="474"/>
-      <c r="F57" s="474"/>
-    </row>
-    <row r="58" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B58" s="474" t="s">
+      <c r="C57" s="471"/>
+      <c r="D57" s="471"/>
+      <c r="E57" s="471"/>
+      <c r="F57" s="471"/>
+    </row>
+    <row r="58" spans="2:6">
+      <c r="B58" s="471" t="s">
         <v>509</v>
       </c>
-      <c r="C58" s="474"/>
-      <c r="D58" s="474"/>
-      <c r="E58" s="474"/>
-      <c r="F58" s="474"/>
-    </row>
-    <row r="60" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="C58" s="471"/>
+      <c r="D58" s="471"/>
+      <c r="E58" s="471"/>
+      <c r="F58" s="471"/>
+    </row>
+    <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
         <v>372</v>
       </c>
@@ -20739,7 +20728,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="61" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="61" spans="2:6">
       <c r="B61" s="372" t="s">
         <v>213</v>
       </c>
@@ -20752,23 +20741,23 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="62" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="62" spans="2:6">
       <c r="B62" s="377" t="s">
         <v>302</v>
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>4.3243586177853198E-2</v>
+        <v>4.3395960904822804E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
-    <row r="63" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="63" spans="2:6">
       <c r="B63" s="377" t="s">
         <v>332</v>
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>3.0159744408945685E-2</v>
+        <v>3.0082855321861054E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>373</v>
@@ -20778,7 +20767,7 @@
         <v>0.78113118553795446</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:6">
       <c r="B65" s="369" t="s">
         <v>376</v>
       </c>
@@ -20789,7 +20778,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:6">
       <c r="B66" s="372" t="s">
         <v>326</v>
       </c>
@@ -20802,7 +20791,7 @@
         <v>0.18355873621409211</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:6">
       <c r="B67" s="382" t="str">
         <f>Normalized_FCF!B116</f>
         <v>Pre-tax Profit/Sales</v>
@@ -20816,7 +20805,7 @@
         <v>0.18071047355490921</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:6">
       <c r="B68" s="382" t="str">
         <f>Normalized_FCF!B117</f>
         <v>Sales/Total Assets</v>
@@ -20830,7 +20819,7 @@
         <v>0.59902736076457896</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:6">
       <c r="B69" s="382" t="str">
         <f>Normalized_FCF!B118</f>
         <v>Total Assets/Equity</v>
@@ -20844,7 +20833,7 @@
         <v>1.6956845985056004</v>
       </c>
     </row>
-    <row r="71" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:6" ht="13.9">
       <c r="A71" s="345" t="s">
         <v>476</v>
       </c>
@@ -20854,43 +20843,43 @@
       <c r="E71" s="345"/>
       <c r="F71" s="345"/>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:6">
       <c r="A72" s="385"/>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="474" t="s">
+      <c r="B73" s="471" t="s">
         <v>510</v>
       </c>
-      <c r="C73" s="474"/>
-      <c r="D73" s="474"/>
-      <c r="E73" s="474"/>
-      <c r="F73" s="474"/>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B74" s="477" t="s">
+      <c r="C73" s="471"/>
+      <c r="D73" s="471"/>
+      <c r="E73" s="471"/>
+      <c r="F73" s="471"/>
+    </row>
+    <row r="74" spans="1:6">
+      <c r="B74" s="472" t="s">
         <v>479</v>
       </c>
-      <c r="C74" s="477"/>
-      <c r="D74" s="477"/>
-      <c r="E74" s="477"/>
-      <c r="F74" s="477"/>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C74" s="472"/>
+      <c r="D74" s="472"/>
+      <c r="E74" s="472"/>
+      <c r="F74" s="472"/>
+    </row>
+    <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B77" s="474" t="s">
+    <row r="77" spans="1:6">
+      <c r="B77" s="471" t="s">
         <v>511</v>
       </c>
-      <c r="C77" s="474"/>
-      <c r="D77" s="474"/>
-      <c r="E77" s="474"/>
-      <c r="F77" s="474"/>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C77" s="471"/>
+      <c r="D77" s="471"/>
+      <c r="E77" s="471"/>
+      <c r="F77" s="471"/>
+    </row>
+    <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
         <v>215</v>
       </c>
@@ -20903,20 +20892,20 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:6">
       <c r="B79" s="372" t="s">
         <v>234</v>
       </c>
       <c r="C79" s="387">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-12.770144477195332</v>
+        <v>-12.847896194792556</v>
       </c>
       <c r="D79" s="343" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:6">
       <c r="B80" s="382" t="s">
         <v>309</v>
       </c>
@@ -20925,7 +20914,7 @@
         <v>0.45303827785506334</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:6">
       <c r="B81" s="382" t="s">
         <v>311</v>
       </c>
@@ -20934,12 +20923,12 @@
         <v>2.1271064799169817</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:6">
       <c r="B83" s="343" t="s">
         <v>512</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:6">
       <c r="B84" s="343" t="s">
         <v>224</v>
       </c>
@@ -20952,7 +20941,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:6">
       <c r="B85" s="382" t="s">
         <v>481</v>
       </c>
@@ -20965,25 +20954,25 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:6">
       <c r="B86" s="372" t="s">
         <v>235</v>
       </c>
       <c r="C86" s="387">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>18.256367328050825</v>
+        <v>18.367522211175022</v>
       </c>
       <c r="D86" s="343" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:6">
       <c r="B88" s="343" t="s">
         <v>513</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:6">
       <c r="B89" s="343" t="s">
         <v>217</v>
       </c>
@@ -20996,33 +20985,33 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:6">
       <c r="B90" s="372" t="s">
         <v>236</v>
       </c>
       <c r="C90" s="387">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>2.0160003005263039</v>
+        <v>2.028274827750514</v>
       </c>
       <c r="D90" s="343" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:6">
       <c r="B92" s="372" t="s">
         <v>480</v>
       </c>
       <c r="C92" s="387">
         <f>DCF!F8</f>
-        <v>7.502223151381795</v>
+        <v>7.5479008441329798</v>
       </c>
       <c r="D92" s="343" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="94" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:6" ht="13.9">
       <c r="A94" s="345" t="s">
         <v>482</v>
       </c>
@@ -21032,49 +21021,49 @@
       <c r="E94" s="345"/>
       <c r="F94" s="345"/>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:6">
       <c r="A95" s="385"/>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="474" t="s">
+      <c r="B96" s="471" t="s">
         <v>514</v>
       </c>
-      <c r="C96" s="474"/>
-      <c r="D96" s="474"/>
-      <c r="E96" s="474"/>
-      <c r="F96" s="474"/>
-    </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C96" s="471"/>
+      <c r="D96" s="471"/>
+      <c r="E96" s="471"/>
+      <c r="F96" s="471"/>
+    </row>
+    <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="477" t="s">
+      <c r="B97" s="472" t="s">
         <v>515</v>
       </c>
-      <c r="C97" s="477"/>
-      <c r="D97" s="477"/>
-      <c r="E97" s="477"/>
-      <c r="F97" s="477"/>
-    </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C97" s="472"/>
+      <c r="D97" s="472"/>
+      <c r="E97" s="472"/>
+      <c r="F97" s="472"/>
+    </row>
+    <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="477" t="s">
+      <c r="B98" s="472" t="s">
         <v>516</v>
       </c>
-      <c r="C98" s="477"/>
-      <c r="D98" s="477"/>
-      <c r="E98" s="477"/>
-      <c r="F98" s="477"/>
-    </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C98" s="472"/>
+      <c r="D98" s="472"/>
+      <c r="E98" s="472"/>
+      <c r="F98" s="472"/>
+    </row>
+    <row r="99" spans="1:6">
       <c r="A99" s="385"/>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:6">
       <c r="A100" s="385"/>
       <c r="B100" s="369" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:6">
       <c r="A101" s="385"/>
       <c r="B101" s="372" t="s">
         <v>212</v>
@@ -21084,7 +21073,7 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:6">
       <c r="A102" s="385"/>
       <c r="B102" s="382" t="s">
         <v>318</v>
@@ -21094,7 +21083,7 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:6">
       <c r="A103" s="385"/>
       <c r="B103" s="382" t="s">
         <v>317</v>
@@ -21104,7 +21093,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:6">
       <c r="A104" s="385"/>
       <c r="B104" s="372" t="s">
         <v>535</v>
@@ -21113,97 +21102,97 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:6">
       <c r="A105" s="385"/>
       <c r="C105" s="392"/>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:6">
       <c r="A106" s="385"/>
       <c r="B106" s="393" t="s">
         <v>375</v>
       </c>
       <c r="C106" s="392"/>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="474" t="s">
+      <c r="B107" s="471" t="s">
         <v>517</v>
       </c>
-      <c r="C107" s="474"/>
-      <c r="D107" s="474"/>
-      <c r="E107" s="474"/>
-      <c r="F107" s="474"/>
-    </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C107" s="471"/>
+      <c r="D107" s="471"/>
+      <c r="E107" s="471"/>
+      <c r="F107" s="471"/>
+    </row>
+    <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="474" t="s">
+      <c r="B108" s="471" t="s">
         <v>536</v>
       </c>
-      <c r="C108" s="474"/>
-      <c r="D108" s="474"/>
-      <c r="E108" s="474"/>
-      <c r="F108" s="474"/>
-    </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C108" s="471"/>
+      <c r="D108" s="471"/>
+      <c r="E108" s="471"/>
+      <c r="F108" s="471"/>
+    </row>
+    <row r="109" spans="1:6">
       <c r="A109" s="385"/>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:6">
       <c r="A110" s="385"/>
       <c r="B110" s="369" t="s">
         <v>489</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:6">
       <c r="A111" s="385"/>
       <c r="B111" s="375" t="s">
         <v>486</v>
       </c>
       <c r="C111" s="394">
         <f>BS!D47</f>
-        <v>3.6148050867765735</v>
+        <v>3.6368140236979967</v>
       </c>
       <c r="D111" s="343" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:6">
       <c r="A112" s="385"/>
       <c r="B112" s="372" t="s">
         <v>377</v>
       </c>
       <c r="C112" s="394">
         <f>DCF!C11</f>
-        <v>73.2448294520552</v>
+        <v>73.690784570666622</v>
       </c>
       <c r="D112" s="343" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:6">
       <c r="A113" s="385"/>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="474" t="s">
+      <c r="B114" s="471" t="s">
         <v>518</v>
       </c>
-      <c r="C114" s="474"/>
-      <c r="D114" s="474"/>
-      <c r="E114" s="474"/>
-      <c r="F114" s="474"/>
-    </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C114" s="471"/>
+      <c r="D114" s="471"/>
+      <c r="E114" s="471"/>
+      <c r="F114" s="471"/>
+    </row>
+    <row r="115" spans="1:6">
       <c r="A115" s="385"/>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:6">
       <c r="A116" s="385"/>
       <c r="B116" s="369" t="s">
         <v>490</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:6">
       <c r="A117" s="385"/>
       <c r="B117" s="342" t="s">
         <v>378</v>
@@ -21221,7 +21210,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:6">
       <c r="A118" s="385"/>
       <c r="B118" s="395" t="str">
         <f>DCF!B90</f>
@@ -21237,14 +21226,14 @@
       </c>
       <c r="E118" s="398" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>148.43 HKD</v>
+        <v>149.33 HKD</v>
       </c>
       <c r="F118" s="399">
         <f>DCF!F90</f>
         <v>0.15</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:6">
       <c r="A119" s="385"/>
       <c r="B119" s="400" t="str">
         <f>DCF!B91</f>
@@ -21260,14 +21249,14 @@
       </c>
       <c r="E119" s="398" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>89.8 HKD</v>
+        <v>90.35 HKD</v>
       </c>
       <c r="F119" s="403">
         <f>DCF!F91</f>
         <v>0.15999999999999995</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:6">
       <c r="B120" s="400" t="str">
         <f>DCF!B92</f>
         <v>Base</v>
@@ -21282,14 +21271,14 @@
       </c>
       <c r="E120" s="398" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>74.33 HKD</v>
+        <v>74.78 HKD</v>
       </c>
       <c r="F120" s="403">
         <f>DCF!F92</f>
         <v>0.44</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:6">
       <c r="B121" s="400" t="str">
         <f>DCF!B93</f>
         <v>Pessimistic</v>
@@ -21304,14 +21293,14 @@
       </c>
       <c r="E121" s="398" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>67.84 HKD</v>
+        <v>68.25 HKD</v>
       </c>
       <c r="F121" s="403">
         <f>DCF!F93</f>
         <v>0.19999999999999998</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:6">
       <c r="B122" s="400" t="str">
         <f>DCF!B94</f>
         <v>Devil's advocate</v>
@@ -21326,14 +21315,14 @@
       </c>
       <c r="E122" s="398" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>56.91 HKD</v>
+        <v>57.25 HKD</v>
       </c>
       <c r="F122" s="403">
         <f>DCF!F94</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:6">
       <c r="B124" s="470" t="s">
         <v>519</v>
       </c>
@@ -21342,29 +21331,29 @@
       <c r="E124" s="470"/>
       <c r="F124" s="470"/>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:6">
       <c r="B125" s="372" t="s">
         <v>218</v>
       </c>
       <c r="C125" s="404">
         <f>Scenarios!C36</f>
-        <v>85.749761133441666</v>
+        <v>86.271853207151764</v>
       </c>
       <c r="D125" s="343" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B127" s="472" t="s">
+    <row r="127" spans="1:6">
+      <c r="B127" s="475" t="s">
         <v>520</v>
       </c>
-      <c r="C127" s="472"/>
-      <c r="D127" s="472"/>
-      <c r="E127" s="472"/>
-      <c r="F127" s="472"/>
-    </row>
-    <row r="129" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+      <c r="C127" s="475"/>
+      <c r="D127" s="475"/>
+      <c r="E127" s="475"/>
+      <c r="F127" s="475"/>
+    </row>
+    <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
         <v>492</v>
       </c>
@@ -21374,30 +21363,30 @@
       <c r="E129" s="345"/>
       <c r="F129" s="345"/>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B131" s="473" t="s">
+    <row r="131" spans="1:6">
+      <c r="B131" s="476" t="s">
         <v>521</v>
       </c>
-      <c r="C131" s="473"/>
-      <c r="D131" s="473"/>
-      <c r="E131" s="473"/>
-      <c r="F131" s="473"/>
-    </row>
-    <row r="132" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B132" s="474" t="s">
+      <c r="C131" s="476"/>
+      <c r="D131" s="476"/>
+      <c r="E131" s="476"/>
+      <c r="F131" s="476"/>
+    </row>
+    <row r="132" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B132" s="471" t="s">
         <v>522</v>
       </c>
-      <c r="C132" s="474"/>
-      <c r="D132" s="474"/>
-      <c r="E132" s="474"/>
-      <c r="F132" s="474"/>
-    </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C132" s="471"/>
+      <c r="D132" s="471"/>
+      <c r="E132" s="471"/>
+      <c r="F132" s="471"/>
+    </row>
+    <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:6">
       <c r="B135" s="343" t="s">
         <v>382</v>
       </c>
@@ -21406,7 +21395,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:6">
       <c r="B136" s="343" t="s">
         <v>383</v>
       </c>
@@ -21419,14 +21408,14 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:6">
       <c r="B138" s="369" t="s">
         <v>493</v>
       </c>
       <c r="C138" s="407"/>
       <c r="D138" s="407"/>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:6">
       <c r="B139" s="340" t="s">
         <v>462</v>
       </c>
@@ -21445,49 +21434,49 @@
         <v>495</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:6">
       <c r="B140" s="408" t="s">
         <v>312</v>
       </c>
       <c r="C140" s="409">
         <f>Scenarios!C62</f>
-        <v>4.318449719619883</v>
+        <v>4.3184497196198821</v>
       </c>
       <c r="D140" s="409">
         <f>Scenarios!D62</f>
-        <v>39.516018955503078</v>
+        <v>39.756614381175936</v>
       </c>
       <c r="E140" s="410">
         <f>Scenarios!E62</f>
-        <v>43.834468675122963</v>
+        <v>44.075064100795821</v>
       </c>
       <c r="F140" s="411">
         <f>E22</f>
-        <v>0.29465259038036601</v>
-      </c>
-    </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.2">
+        <v>0.29465259038036606</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6">
       <c r="B141" s="408" t="s">
         <v>313</v>
       </c>
       <c r="C141" s="409">
         <f>Scenarios!C63</f>
-        <v>4.9654493155550261</v>
+        <v>4.9654493155550243</v>
       </c>
       <c r="D141" s="409">
         <f>Scenarios!D63</f>
-        <v>49.530547947114343</v>
+        <v>49.83211737597216</v>
       </c>
       <c r="E141" s="410">
         <f>Scenarios!E63</f>
-        <v>54.49599726266937</v>
+        <v>54.797566691527187</v>
       </c>
       <c r="F141" s="411">
         <f>Scenarios!F63</f>
-        <v>0.20075184365903001</v>
-      </c>
-    </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.2">
+        <v>0.20075184365903009</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6">
       <c r="B143" s="340" t="s">
         <v>463</v>
       </c>
@@ -21506,7 +21495,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:6">
       <c r="B144" s="408" t="s">
         <v>315</v>
       </c>
@@ -21516,18 +21505,18 @@
       </c>
       <c r="D144" s="409">
         <f>Scenarios!D66</f>
-        <v>61.462032490931094</v>
+        <v>61.836247410873455</v>
       </c>
       <c r="E144" s="410">
         <f>Scenarios!E66</f>
-        <v>67.155775868146307</v>
+        <v>67.529990788088668</v>
       </c>
       <c r="F144" s="411">
         <f>E24</f>
         <v>0.1174</v>
       </c>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:6">
       <c r="B145" s="408" t="s">
         <v>314</v>
       </c>
@@ -21537,18 +21526,18 @@
       </c>
       <c r="D145" s="409">
         <f>Scenarios!D67</f>
-        <v>69.508996133668688</v>
+        <v>69.932205428403179</v>
       </c>
       <c r="E145" s="410">
         <f>Scenarios!E67</f>
-        <v>75.674201669797</v>
+        <v>76.097410964531491</v>
       </c>
       <c r="F145" s="411">
         <f>Scenarios!F67</f>
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="147" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:6" ht="13.9">
       <c r="A147" s="345" t="s">
         <v>475</v>
       </c>
@@ -21558,50 +21547,50 @@
       <c r="E147" s="345"/>
       <c r="F147" s="345"/>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B149" s="475" t="s">
+    <row r="149" spans="1:6">
+      <c r="B149" s="477" t="s">
         <v>523</v>
       </c>
-      <c r="C149" s="474"/>
-      <c r="D149" s="474"/>
-      <c r="E149" s="474"/>
-      <c r="F149" s="474"/>
-    </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C149" s="471"/>
+      <c r="D149" s="471"/>
+      <c r="E149" s="471"/>
+      <c r="F149" s="471"/>
+    </row>
+    <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B152" s="476" t="s">
+    <row r="152" spans="1:6">
+      <c r="B152" s="473" t="s">
         <v>524</v>
       </c>
-      <c r="C152" s="476"/>
-      <c r="D152" s="476"/>
-      <c r="E152" s="476"/>
-      <c r="F152" s="476"/>
-    </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C152" s="473"/>
+      <c r="D152" s="473"/>
+      <c r="E152" s="473"/>
+      <c r="F152" s="473"/>
+    </row>
+    <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:6">
       <c r="B154" s="412" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:6">
       <c r="B155" s="412" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:6">
       <c r="B157" s="343" t="s">
         <v>525</v>
       </c>
     </row>
-    <row r="158" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:6" ht="24.5" customHeight="1">
       <c r="B158" s="470" t="s">
         <v>439</v>
       </c>
@@ -21610,57 +21599,60 @@
       <c r="E158" s="470"/>
       <c r="F158" s="470"/>
     </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:6">
       <c r="B160" s="343" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="161" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B161" s="471" t="s">
+    <row r="161" spans="2:6">
+      <c r="B161" s="474" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="471"/>
-      <c r="D161" s="471"/>
-      <c r="E161" s="471"/>
-      <c r="F161" s="471"/>
-    </row>
-    <row r="162" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B162" s="471" t="s">
+      <c r="C161" s="474"/>
+      <c r="D161" s="474"/>
+      <c r="E161" s="474"/>
+      <c r="F161" s="474"/>
+    </row>
+    <row r="162" spans="2:6">
+      <c r="B162" s="474" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="471"/>
-      <c r="D162" s="471"/>
-      <c r="E162" s="471"/>
-      <c r="F162" s="471"/>
-    </row>
-    <row r="164" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="C162" s="474"/>
+      <c r="D162" s="474"/>
+      <c r="E162" s="474"/>
+      <c r="F162" s="474"/>
+    </row>
+    <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
         <v>527</v>
       </c>
     </row>
-    <row r="165" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="165" spans="2:6">
       <c r="B165" s="412" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="166" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="166" spans="2:6">
       <c r="B166" s="412" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="167" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="167" spans="2:6">
       <c r="B167" s="412" t="s">
         <v>392</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21675,15 +21667,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">
